--- a/RegistrationsFile.xlsx
+++ b/RegistrationsFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B024E9D3-242D-4870-873C-C431681761B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759A7478-2463-4CD7-AA2B-6280442280BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>MODEL</t>
   </si>
@@ -83,42 +83,6 @@
   </si>
   <si>
     <t>FASTTAG</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
   </si>
   <si>
     <t>MBHKWD13SSJ679296</t>
@@ -141,8 +105,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="173" formatCode="[$-409]d/mmm/yy;@"/>
-    <numFmt numFmtId="174" formatCode="[$-409]dd/mmm/yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d/mmm/yy;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]dd/mmm/yy;@"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -627,18 +591,33 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -686,7 +665,10 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -697,7 +679,7 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
       </font>
-      <numFmt numFmtId="173" formatCode="[$-409]d/mmm/yy;@"/>
+      <numFmt numFmtId="164" formatCode="[$-409]d/mmm/yy;@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -710,7 +692,6 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
       </font>
-      <numFmt numFmtId="174" formatCode="[$-409]dd/mmm/yy;@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -723,7 +704,7 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
       </font>
-      <numFmt numFmtId="174" formatCode="[$-409]dd/mmm/yy;@"/>
+      <numFmt numFmtId="165" formatCode="[$-409]dd/mmm/yy;@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -760,18 +741,7 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
+      <numFmt numFmtId="165" formatCode="[$-409]dd/mmm/yy;@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -835,6 +805,18 @@
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -849,7 +831,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}" name="Table1" displayName="Table1" ref="A1:K14" totalsRowShown="0" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}" name="Table1" displayName="Table1" ref="A1:K14" totalsRowShown="0" headerRowDxfId="0" dataDxfId="12">
   <autoFilter ref="A1:K14" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{C5FAA5C2-D683-4836-A3E6-7F0D524EA103}" name="S.NO" dataDxfId="11"/>
@@ -857,12 +839,12 @@
     <tableColumn id="3" xr3:uid="{FEB1AC79-EE4D-4B04-897E-D273DA0BD281}" name="NAME" dataDxfId="9"/>
     <tableColumn id="4" xr3:uid="{46EC1EFE-3607-4207-9FFE-5A3770FFFEBE}" name="MODEL" dataDxfId="8"/>
     <tableColumn id="5" xr3:uid="{A59F05B7-1065-40C0-933C-37EC1B135DA9}" name="REG NUM" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{2644077D-C310-4539-8493-451624D59384}" name="DATE OF REG" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{68F85EFD-E504-4A37-8955-E3793B2B502F}" name="DSE" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{4BC0389E-5375-4903-8F62-68D2E2F55714}" name="RC RECEIVING" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{D51CD378-2BA3-4701-925C-15F60470BF35}" name="DATE" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{E25E943D-8510-40D9-8CDC-3CDFEFC2F5A3}" name="FASTTAG" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{DECCBC09-99A2-4DE7-A638-3BE4CE06C3B6}" name="DATED" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{2644077D-C310-4539-8493-451624D59384}" name="DATE OF REG" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{68F85EFD-E504-4A37-8955-E3793B2B502F}" name="DSE" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{4BC0389E-5375-4903-8F62-68D2E2F55714}" name="RC RECEIVING" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{D51CD378-2BA3-4701-925C-15F60470BF35}" name="DATE" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{E25E943D-8510-40D9-8CDC-3CDFEFC2F5A3}" name="FASTTAG" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{DECCBC09-99A2-4DE7-A638-3BE4CE06C3B6}" name="DATED" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1181,39 +1163,39 @@
     <col min="11" max="11" width="15.140625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="H1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>37</v>
+      <c r="K1" s="10" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1221,10 +1203,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>5</v>
@@ -1245,15 +1227,15 @@
         <v>45961</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="K2" s="4">
         <v>45960</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>21</v>
+      <c r="A3" s="11">
+        <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>2</v>
@@ -1276,15 +1258,15 @@
       <c r="H3" s="5"/>
       <c r="I3" s="6"/>
       <c r="J3" s="5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="K3" s="4">
         <v>45961</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>22</v>
+      <c r="A4" s="11">
+        <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>11</v>
@@ -1307,15 +1289,15 @@
       <c r="H4" s="5"/>
       <c r="I4" s="6"/>
       <c r="J4" s="5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="K4" s="4">
         <v>45961</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>23</v>
+      <c r="A5" s="11">
+        <v>4</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -1329,8 +1311,8 @@
       <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>24</v>
+      <c r="A6" s="11">
+        <v>5</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1344,8 +1326,8 @@
       <c r="K6" s="4"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>25</v>
+      <c r="A7" s="11">
+        <v>6</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1359,8 +1341,8 @@
       <c r="K7" s="4"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>26</v>
+      <c r="A8" s="11">
+        <v>7</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1374,8 +1356,8 @@
       <c r="K8" s="4"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>27</v>
+      <c r="A9" s="11">
+        <v>8</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1389,8 +1371,8 @@
       <c r="K9" s="4"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>28</v>
+      <c r="A10" s="11">
+        <v>9</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1404,8 +1386,8 @@
       <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>29</v>
+      <c r="A11" s="11">
+        <v>10</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1419,8 +1401,8 @@
       <c r="K11" s="4"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>30</v>
+      <c r="A12" s="11">
+        <v>11</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1434,8 +1416,8 @@
       <c r="K12" s="4"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>31</v>
+      <c r="A13" s="11">
+        <v>12</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1449,8 +1431,8 @@
       <c r="K13" s="4"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>32</v>
+      <c r="A14" s="11">
+        <v>13</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>

--- a/RegistrationsFile.xlsx
+++ b/RegistrationsFile.xlsx
@@ -1,26 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759A7478-2463-4CD7-AA2B-6280442280BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CC8F47-D75F-4049-8F9B-D4046BA6696B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="541" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
   </bookViews>
   <sheets>
-    <sheet name="upload file format" sheetId="1" r:id="rId1"/>
+    <sheet name="Registrations" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
   <si>
     <t>MODEL</t>
   </si>
@@ -98,6 +110,132 @@
   </si>
   <si>
     <t>DATED</t>
+  </si>
+  <si>
+    <t>JK01BC3687</t>
+  </si>
+  <si>
+    <t>JAVID ZARGER</t>
+  </si>
+  <si>
+    <t>HURAT MAJID BASU</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSJ656652</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSK478255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOOR UL QAMRAIN	</t>
+  </si>
+  <si>
+    <t>IGNIS DELTA</t>
+  </si>
+  <si>
+    <t>VALLEY MOTORS</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSG472790</t>
+  </si>
+  <si>
+    <t>BASIT MUSHTAQ</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSK690097</t>
+  </si>
+  <si>
+    <t>NAZIR AH TANTRAY</t>
+  </si>
+  <si>
+    <t>FRONX DELTA 6AB</t>
+  </si>
+  <si>
+    <t>JK03Q3597</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSG473603</t>
+  </si>
+  <si>
+    <t>MEHRU NISA</t>
+  </si>
+  <si>
+    <t>AMIR</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSJ476642</t>
+  </si>
+  <si>
+    <t>SHAFAYATUL HUSSAIN</t>
+  </si>
+  <si>
+    <t>UMAR BASHIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>JK04K3263</t>
+  </si>
+  <si>
+    <t>OWAIS BIN AHAD</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSH639821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUNEER </t>
+  </si>
+  <si>
+    <t>RC GIVEN TO CUSTOMER / 6006291739</t>
+  </si>
+  <si>
+    <t>MOHD IBRAHIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRONX DELTA+ </t>
+  </si>
+  <si>
+    <t>T1025JK4831A</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSF606290</t>
+  </si>
+  <si>
+    <t>JK05P5971</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSC528451</t>
+  </si>
+  <si>
+    <t>PARVAZE AHMAD MIR</t>
+  </si>
+  <si>
+    <t>FRONX DELTA+(O)</t>
+  </si>
+  <si>
+    <t>JK01BC5074</t>
+  </si>
+  <si>
+    <t> TAWAF BILAL</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSJ670717</t>
+  </si>
+  <si>
+    <t>ISHFAQ SOFI</t>
+  </si>
+  <si>
+    <t>JK01BC5276</t>
+  </si>
+  <si>
+    <t>JK01BC5245</t>
+  </si>
+  <si>
+    <t>JK18E1471</t>
+  </si>
+  <si>
+    <t>JK13K2036</t>
   </si>
 </sst>
 </file>
@@ -591,7 +729,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -616,9 +754,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -666,9 +801,6 @@
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="13">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -817,6 +949,9 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -831,20 +966,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}" name="Table1" displayName="Table1" ref="A1:K14" totalsRowShown="0" headerRowDxfId="0" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}" name="Table1" displayName="Table1" ref="A1:K14" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A1:K14" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K14">
+    <sortCondition ref="F1:F14"/>
+  </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{C5FAA5C2-D683-4836-A3E6-7F0D524EA103}" name="S.NO" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{95A0C0B2-6AB7-4A1B-AFD7-55FD6A2B913B}" name="CHASSIS" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{FEB1AC79-EE4D-4B04-897E-D273DA0BD281}" name="NAME" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{46EC1EFE-3607-4207-9FFE-5A3770FFFEBE}" name="MODEL" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{A59F05B7-1065-40C0-933C-37EC1B135DA9}" name="REG NUM" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{2644077D-C310-4539-8493-451624D59384}" name="DATE OF REG" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{68F85EFD-E504-4A37-8955-E3793B2B502F}" name="DSE" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{4BC0389E-5375-4903-8F62-68D2E2F55714}" name="RC RECEIVING" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{D51CD378-2BA3-4701-925C-15F60470BF35}" name="DATE" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{E25E943D-8510-40D9-8CDC-3CDFEFC2F5A3}" name="FASTTAG" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{DECCBC09-99A2-4DE7-A638-3BE4CE06C3B6}" name="DATED" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{C5FAA5C2-D683-4836-A3E6-7F0D524EA103}" name="S.NO" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{95A0C0B2-6AB7-4A1B-AFD7-55FD6A2B913B}" name="CHASSIS" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{FEB1AC79-EE4D-4B04-897E-D273DA0BD281}" name="NAME" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{46EC1EFE-3607-4207-9FFE-5A3770FFFEBE}" name="MODEL" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{A59F05B7-1065-40C0-933C-37EC1B135DA9}" name="REG NUM" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{2644077D-C310-4539-8493-451624D59384}" name="DATE OF REG" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{68F85EFD-E504-4A37-8955-E3793B2B502F}" name="DSE" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{4BC0389E-5375-4903-8F62-68D2E2F55714}" name="RC RECEIVING" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{D51CD378-2BA3-4701-925C-15F60470BF35}" name="DATE" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{E25E943D-8510-40D9-8CDC-3CDFEFC2F5A3}" name="FASTTAG" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{DECCBC09-99A2-4DE7-A638-3BE4CE06C3B6}" name="DATED" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1147,7 +1285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB93731C-EBB7-48FC-A9AD-B376A1D45265}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
@@ -1157,7 +1295,7 @@
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" style="3" customWidth="1"/>
     <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="8" width="20.140625" customWidth="1"/>
+    <col min="8" max="8" width="34.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.28515625" style="3" customWidth="1"/>
     <col min="10" max="10" width="22.28515625" customWidth="1"/>
     <col min="11" max="11" width="15.140625" style="2" customWidth="1"/>
@@ -1200,91 +1338,91 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F2" s="6">
-        <v>45960</v>
+        <v>45934</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="I2" s="6">
-        <v>45961</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="4">
-        <v>45960</v>
-      </c>
+        <v>45962</v>
+      </c>
+      <c r="J2" s="5"/>
+      <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
-        <v>2</v>
+      <c r="A3" s="5">
+        <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F3" s="6">
-        <v>45961</v>
+        <v>45941</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="6"/>
+        <v>27</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="6">
+        <v>45962</v>
+      </c>
       <c r="J3" s="5" t="s">
         <v>23</v>
       </c>
       <c r="K3" s="4">
-        <v>45961</v>
+        <v>45973</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
-        <v>3</v>
+      <c r="A4" s="5">
+        <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="F4" s="6">
-        <v>45961</v>
+        <v>45941</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="6"/>
@@ -1292,158 +1430,335 @@
         <v>23</v>
       </c>
       <c r="K4" s="4">
-        <v>45961</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="4"/>
+      <c r="A5" s="5">
+        <v>13</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="6">
+        <v>45959</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" s="6">
+        <v>45962</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="4">
+        <v>45959</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
+      <c r="A6" s="5">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="4"/>
+      <c r="E6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="6">
+        <v>45960</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="6">
+        <v>45961</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="4">
+        <v>45960</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="5"/>
+      <c r="A7" s="5">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="6">
+        <v>45961</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="H7" s="5"/>
       <c r="I7" s="6"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="4"/>
+      <c r="J7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="4">
+        <v>45961</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="5"/>
+      <c r="A8" s="5">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="6">
+        <v>45961</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="H8" s="5"/>
       <c r="I8" s="6"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="4"/>
+      <c r="J8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="4">
+        <v>45961</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="5"/>
+      <c r="A9" s="5">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="6">
+        <v>45961</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="H9" s="5"/>
       <c r="I9" s="6"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="4"/>
+      <c r="J9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="5"/>
+      <c r="A10" s="5">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="6">
+        <v>45961</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="H10" s="5"/>
       <c r="I10" s="6"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="4"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="5"/>
+      <c r="A11" s="5">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="6">
+        <v>45962</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="H11" s="5"/>
       <c r="I11" s="6"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="4"/>
+      <c r="J11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="5"/>
+      <c r="A12" s="5">
+        <v>9</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="6">
+        <v>45962</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="H12" s="5"/>
       <c r="I12" s="6"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="4"/>
+      <c r="J12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="4"/>
+      <c r="A13" s="5">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="6">
+        <v>45962</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="6">
+        <v>45962</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="4"/>
+      <c r="A14" s="5">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="6">
+        <v>45962</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="6">
+        <v>45962</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="4">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="22" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J22" t="s">
+        <v>46</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -1453,4 +1768,13 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C8F1167-DDBD-48E7-B937-E6DB0DAB49C3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/RegistrationsFile.xlsx
+++ b/RegistrationsFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CC8F47-D75F-4049-8F9B-D4046BA6696B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F09E26-6010-4BD0-939F-038F678A9FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="541" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="82">
   <si>
     <t>MODEL</t>
   </si>
@@ -160,9 +160,6 @@
     <t>MEHRU NISA</t>
   </si>
   <si>
-    <t>AMIR</t>
-  </si>
-  <si>
     <t>MA3NFG81SSJ476642</t>
   </si>
   <si>
@@ -236,6 +233,51 @@
   </si>
   <si>
     <t>JK13K2036</t>
+  </si>
+  <si>
+    <t>MOHD AYOUB</t>
+  </si>
+  <si>
+    <t>BALENO DELTA</t>
+  </si>
+  <si>
+    <t>MBHHWB13SSJB10784</t>
+  </si>
+  <si>
+    <t>AMIR FAROOQ</t>
+  </si>
+  <si>
+    <t>IRFAN NAZIR</t>
+  </si>
+  <si>
+    <t>JK13K2096</t>
+  </si>
+  <si>
+    <t>JK04K3984</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSJ670543</t>
+  </si>
+  <si>
+    <t>SUHAIL NABI KUMAR</t>
+  </si>
+  <si>
+    <t>MANZOOR PAUL</t>
+  </si>
+  <si>
+    <t>RC GIVEN TO CUSTOMER / JAVED ZARGER</t>
+  </si>
+  <si>
+    <t>JK01BC4708</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSJ669517</t>
+  </si>
+  <si>
+    <t>RC GIVEN TO CUSTOMER / 7006780805</t>
+  </si>
+  <si>
+    <t>NAVEED AHMAD CHUCK</t>
   </si>
 </sst>
 </file>
@@ -729,7 +771,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -754,6 +796,15 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -966,10 +1017,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}" name="Table1" displayName="Table1" ref="A1:K14" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K14" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K14">
-    <sortCondition ref="F1:F14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}" name="Table1" displayName="Table1" ref="A1:K27" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K27" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K15">
+    <sortCondition ref="F1:F15"/>
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{C5FAA5C2-D683-4836-A3E6-7F0D524EA103}" name="S.NO" dataDxfId="10"/>
@@ -1283,9 +1334,41 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{2BDD89B5-8142-45C9-9BB1-1720B4DD822F}">
+  <we:reference id="wa200004935" version="6.0.0.0" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200004935" version="6.0.0.0" store="wa200004935" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_FORMULABOT_CLASSIFY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_SENTIMENT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_INFO</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_FREEFORM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_INFER</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB93731C-EBB7-48FC-A9AD-B376A1D45265}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
@@ -1294,8 +1377,8 @@
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="8" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.28515625" style="3" customWidth="1"/>
     <col min="10" max="10" width="22.28515625" customWidth="1"/>
     <col min="11" max="11" width="15.140625" style="2" customWidth="1"/>
@@ -1338,28 +1421,28 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" s="6">
         <v>45934</v>
       </c>
       <c r="G2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="I2" s="6">
         <v>45962</v>
@@ -1369,7 +1452,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>29</v>
@@ -1404,7 +1487,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>30</v>
@@ -1416,7 +1499,7 @@
         <v>32</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F4" s="6">
         <v>45941</v>
@@ -1435,28 +1518,28 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F5" s="6">
         <v>45959</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I5" s="6">
         <v>45962</v>
@@ -1470,7 +1553,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>21</v>
@@ -1505,7 +1588,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>2</v>
@@ -1525,8 +1608,12 @@
       <c r="G7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6"/>
+      <c r="H7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="6">
+        <v>45964</v>
+      </c>
       <c r="J7" s="5" t="s">
         <v>23</v>
       </c>
@@ -1536,7 +1623,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>11</v>
@@ -1567,7 +1654,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>34</v>
@@ -1579,7 +1666,7 @@
         <v>32</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F9" s="6">
         <v>45961</v>
@@ -1598,71 +1685,71 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F10" s="6">
         <v>45961</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
+      <c r="J10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="4">
+        <v>45961</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="F11" s="6">
-        <v>45962</v>
+        <v>45961</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="6"/>
-      <c r="J11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="4">
-        <v>45962</v>
-      </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>32</v>
@@ -1674,10 +1761,14 @@
         <v>45962</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" s="12">
+        <v>45964</v>
+      </c>
       <c r="J12" s="5" t="s">
         <v>23</v>
       </c>
@@ -1687,32 +1778,28 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F13" s="6">
         <v>45962</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" s="6">
-        <v>45962</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="6"/>
       <c r="J13" s="5" t="s">
         <v>23</v>
       </c>
@@ -1722,28 +1809,28 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F14" s="6">
         <v>45962</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I14" s="6">
         <v>45962</v>
@@ -1755,9 +1842,240 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="22" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J22" t="s">
-        <v>46</v>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="6">
+        <v>45962</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" s="6">
+        <v>45962</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" s="4">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="6">
+        <v>45960</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="12">
+        <v>45964</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="4">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="6">
+        <v>45953</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" s="12">
+        <v>45964</v>
+      </c>
+      <c r="J17" s="11"/>
+      <c r="K17" s="13"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="13"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="13"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="13"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="13"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="13"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="13"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="13"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="13"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="13"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J28" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/RegistrationsFile.xlsx
+++ b/RegistrationsFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F09E26-6010-4BD0-939F-038F678A9FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CFDE81-69A5-49BA-9162-4B6B20143715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="541" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="87">
   <si>
     <t>MODEL</t>
   </si>
@@ -278,6 +278,21 @@
   </si>
   <si>
     <t>NAVEED AHMAD CHUCK</t>
+  </si>
+  <si>
+    <t>JK13K1762</t>
+  </si>
+  <si>
+    <t>RC GIVEN TO INAYAT DAR</t>
+  </si>
+  <si>
+    <t>MOHD MAQBOOL SOFI</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSK681873</t>
+  </si>
+  <si>
+    <t>INAYAT DAR</t>
   </si>
 </sst>
 </file>
@@ -771,7 +786,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -796,15 +811,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1352,6 +1358,9 @@
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
   <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
     <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
       <we:customFunctionIdList>
         <we:customFunctionIds>_xldudf_FORMULABOT_CLASSIFY</we:customFunctionIds>
@@ -1766,7 +1775,7 @@
       <c r="H12" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="6">
         <v>45964</v>
       </c>
       <c r="J12" s="5" t="s">
@@ -1896,13 +1905,13 @@
       <c r="F16" s="6">
         <v>45960</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="6">
         <v>45964</v>
       </c>
       <c r="J16" s="5" t="s">
@@ -1931,147 +1940,163 @@
       <c r="F17" s="6">
         <v>45953</v>
       </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11" t="s">
+      <c r="G17" s="5"/>
+      <c r="H17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="6">
         <v>45964</v>
       </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="13"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="4"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="13"/>
+      <c r="B18" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="6">
+        <v>45946</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I18" s="6">
+        <v>45964</v>
+      </c>
+      <c r="J18" s="5"/>
+      <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="13"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="4"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="13"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="4"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="13"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="4"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="13"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="4"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="13"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="4"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="13"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="4"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="13"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="4"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="13"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="4"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="13"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="4"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J28" t="s">

--- a/RegistrationsFile.xlsx
+++ b/RegistrationsFile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CFDE81-69A5-49BA-9162-4B6B20143715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7EED69-65B0-42E2-8D61-E06D0AAE08F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="541" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
+    <workbookView xWindow="2205" yWindow="660" windowWidth="20040" windowHeight="11715" tabRatio="541" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Registrations" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="118">
   <si>
     <t>MODEL</t>
   </si>
@@ -293,6 +293,99 @@
   </si>
   <si>
     <t>INAYAT DAR</t>
+  </si>
+  <si>
+    <t>JK01BC3387</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSH474924</t>
+  </si>
+  <si>
+    <t>ZAHOOR AHMED</t>
+  </si>
+  <si>
+    <t>SAJAD VALLEY MOTORS / DRAWER</t>
+  </si>
+  <si>
+    <t>JK04K3353</t>
+  </si>
+  <si>
+    <t>IRFAN</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSF471935</t>
+  </si>
+  <si>
+    <t>BASHIR AHAMD MIR</t>
+  </si>
+  <si>
+    <t>RC GIVEN TO RM IRFAN</t>
+  </si>
+  <si>
+    <t>MBHHWB13SSKB32321</t>
+  </si>
+  <si>
+    <t>HASEENA BANO</t>
+  </si>
+  <si>
+    <t>MA3JJC74WSF247944</t>
+  </si>
+  <si>
+    <t>MOHAMMAD NABEEL GUROO</t>
+  </si>
+  <si>
+    <t>MBHHWB13SSB964894</t>
+  </si>
+  <si>
+    <t>UMER ALI</t>
+  </si>
+  <si>
+    <t>BALENO SIGMA</t>
+  </si>
+  <si>
+    <t>JIMNY ALPHA ALLGRIP PRO</t>
+  </si>
+  <si>
+    <t>BALENO ALPHA</t>
+  </si>
+  <si>
+    <t>JK13K2131</t>
+  </si>
+  <si>
+    <t>JK01BC5655</t>
+  </si>
+  <si>
+    <t>JK01BC5470</t>
+  </si>
+  <si>
+    <t>FAIZAN ASHRAF</t>
+  </si>
+  <si>
+    <t>JK01BC4972</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSJ679760</t>
+  </si>
+  <si>
+    <t> PARVAIZ AHMAD KHATANA</t>
+  </si>
+  <si>
+    <t>ABRAR</t>
+  </si>
+  <si>
+    <t>RC GIVEN TO ABRAR</t>
+  </si>
+  <si>
+    <t>JK01BC2301</t>
+  </si>
+  <si>
+    <t>BISMA FAROOQ WANI</t>
+  </si>
+  <si>
+    <t>MBHHWB13SSDA02468</t>
+  </si>
+  <si>
+    <t>NADEEM FAROOQ / 7006401858</t>
   </si>
 </sst>
 </file>
@@ -786,7 +879,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -812,6 +905,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -935,7 +1035,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1023,10 +1123,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}" name="Table1" displayName="Table1" ref="A1:K27" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K27" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K15">
-    <sortCondition ref="F1:F15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}" name="Table1" displayName="Table1" ref="A1:K26" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K26" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
+    <sortCondition ref="F1:F26"/>
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{C5FAA5C2-D683-4836-A3E6-7F0D524EA103}" name="S.NO" dataDxfId="10"/>
@@ -1377,14 +1477,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB93731C-EBB7-48FC-A9AD-B376A1D45265}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="31.5703125" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="5" max="5" width="19" style="13" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" style="3" customWidth="1"/>
     <col min="7" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37.7109375" bestFit="1" customWidth="1"/>
@@ -1406,7 +1506,7 @@
       <c r="D1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="9" t="s">
@@ -1430,654 +1530,768 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>46</v>
+        <v>102</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="F2" s="6">
-        <v>45934</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>49</v>
-      </c>
+        <v>45927</v>
+      </c>
+      <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="I2" s="6">
-        <v>45962</v>
+        <v>45965</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="F3" s="6">
-        <v>45941</v>
+        <v>45934</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I3" s="6">
         <v>45962</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="4">
-        <v>45973</v>
-      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="4"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>66</v>
+      <c r="E4" s="12" t="s">
+        <v>91</v>
       </c>
       <c r="F4" s="6">
-        <v>45941</v>
+        <v>45937</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="4">
-        <v>45962</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I4" s="6">
+        <v>45965</v>
+      </c>
+      <c r="J4" s="5"/>
+      <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>59</v>
+        <v>32</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>87</v>
       </c>
       <c r="F5" s="6">
-        <v>45959</v>
+        <v>45938</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="I5" s="6">
-        <v>45962</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="4">
-        <v>45959</v>
-      </c>
+        <v>45965</v>
+      </c>
+      <c r="J5" s="5"/>
+      <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>17</v>
+      <c r="E6" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="F6" s="6">
-        <v>45960</v>
+        <v>45941</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I6" s="6">
-        <v>45961</v>
+        <v>45962</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>23</v>
       </c>
       <c r="K6" s="4">
-        <v>45960</v>
+        <v>45973</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>3</v>
+        <v>32</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="F7" s="6">
-        <v>45961</v>
+        <v>45941</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="I7" s="6">
-        <v>45964</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="6"/>
       <c r="J7" s="5" t="s">
         <v>23</v>
       </c>
       <c r="K7" s="4">
-        <v>45961</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="F8" s="6">
-        <v>45961</v>
+        <v>45946</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="4">
-        <v>45961</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8" s="6">
+        <v>45964</v>
+      </c>
+      <c r="J8" s="5"/>
+      <c r="K8" s="4"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>65</v>
+        <v>12</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="F9" s="6">
-        <v>45961</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="4">
-        <v>45962</v>
-      </c>
+        <v>45953</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="6">
+        <v>45964</v>
+      </c>
+      <c r="J9" s="5"/>
+      <c r="K9" s="4"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>72</v>
+        <v>5</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="F10" s="6">
-        <v>45961</v>
+        <v>45958</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="4">
-        <v>45961</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I10" s="6">
+        <v>45965</v>
+      </c>
+      <c r="J10" s="5"/>
+      <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>39</v>
+        <v>12</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="F11" s="6">
-        <v>45961</v>
+        <v>45959</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
+        <v>62</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="6">
+        <v>45962</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="4">
+        <v>45959</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>64</v>
+        <v>5</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="F12" s="6">
-        <v>45962</v>
+        <v>45960</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="I12" s="6">
-        <v>45964</v>
+        <v>45961</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>23</v>
       </c>
       <c r="K12" s="4">
-        <v>45962</v>
+        <v>45960</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
+        <v>15</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>63</v>
+      <c r="E13" s="12" t="s">
+        <v>73</v>
       </c>
       <c r="F13" s="6">
-        <v>45962</v>
+        <v>45960</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13" s="6">
+        <v>45964</v>
+      </c>
       <c r="J13" s="5" t="s">
         <v>23</v>
       </c>
       <c r="K13" s="4">
-        <v>45962</v>
+        <v>45960</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>53</v>
+        <v>5</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="6">
-        <v>45962</v>
+        <v>45961</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="I14" s="6">
-        <v>45962</v>
+        <v>45964</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="4">
-        <v>45962</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
+        <v>7</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="6">
+        <v>45961</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="6">
-        <v>45962</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="6">
-        <v>45962</v>
-      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="6"/>
       <c r="J15" s="5" t="s">
         <v>23</v>
       </c>
       <c r="K15" s="4">
-        <v>45962</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="F16" s="6">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I16" s="6">
-        <v>45964</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="6"/>
       <c r="J16" s="5" t="s">
         <v>23</v>
       </c>
       <c r="K16" s="4">
-        <v>45960</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="F17" s="6">
-        <v>45953</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I17" s="6">
-        <v>45964</v>
-      </c>
-      <c r="J17" s="5"/>
-      <c r="K17" s="4"/>
+        <v>45961</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="4">
+        <v>45961</v>
+      </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>82</v>
+        <v>38</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="F18" s="6">
-        <v>45946</v>
+        <v>45961</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I18" s="6">
+        <v>14</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>11</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="6">
+        <v>45962</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="6">
         <v>45964</v>
       </c>
-      <c r="J18" s="5"/>
-      <c r="K18" s="4"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="4"/>
+      <c r="J19" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="5"/>
+      <c r="A20" s="5">
+        <v>12</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="6">
+        <v>45962</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="H20" s="5"/>
       <c r="I20" s="6"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="4"/>
+      <c r="J20" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="4"/>
+      <c r="A21" s="5">
+        <v>13</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="6">
+        <v>45962</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="6">
+        <v>45962</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="4"/>
+      <c r="A22" s="5">
+        <v>14</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="6">
+        <v>45962</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I22" s="6">
+        <v>45962</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="5"/>
+      <c r="A23" s="5">
+        <v>20</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" s="6">
+        <v>45965</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="H23" s="5"/>
       <c r="I23" s="6"/>
       <c r="J23" s="5"/>
       <c r="K23" s="4"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="5"/>
+      <c r="A24" s="5">
+        <v>21</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F24" s="6">
+        <v>45965</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="H24" s="5"/>
       <c r="I24" s="6"/>
       <c r="J24" s="5"/>
       <c r="K24" s="4"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="5"/>
+      <c r="A25" s="5">
+        <v>22</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="F25" s="6">
+        <v>45965</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="H25" s="5"/>
       <c r="I25" s="6"/>
       <c r="J25" s="5"/>
       <c r="K25" s="4"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
+      <c r="A26" s="5">
+        <v>25</v>
+      </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+      <c r="E26" s="12"/>
       <c r="F26" s="6"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -2086,20 +2300,7 @@
       <c r="K26" s="4"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="4"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J28" t="s">
+      <c r="J27" t="s">
         <v>45</v>
       </c>
     </row>

--- a/RegistrationsFile.xlsx
+++ b/RegistrationsFile.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7EED69-65B0-42E2-8D61-E06D0AAE08F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A656135F-E1F6-40E8-8A7A-E51E7969CE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="660" windowWidth="20040" windowHeight="11715" tabRatio="541" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="541" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Registrations" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Registrations" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="162">
   <si>
     <t>MODEL</t>
   </si>
@@ -106,9 +105,6 @@
     <t>FASTTAG ISSUED</t>
   </si>
   <si>
-    <t>RC RECEIVING</t>
-  </si>
-  <si>
     <t>DATED</t>
   </si>
   <si>
@@ -386,6 +382,141 @@
   </si>
   <si>
     <t>NADEEM FAROOQ / 7006401858</t>
+  </si>
+  <si>
+    <t>JK01BC5133</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSE470465</t>
+  </si>
+  <si>
+    <t>SUHAIL AHMAD BHAT</t>
+  </si>
+  <si>
+    <t>IGNIS SIGMA</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSJ666300</t>
+  </si>
+  <si>
+    <t>AB RASHID</t>
+  </si>
+  <si>
+    <t>JK01BC4676</t>
+  </si>
+  <si>
+    <t>JK13K1650</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSJ477668</t>
+  </si>
+  <si>
+    <t>IGNIS ZETA</t>
+  </si>
+  <si>
+    <t>PDF SENT TO SAJAD VALLEY MOTORS</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSJ679044</t>
+  </si>
+  <si>
+    <t>SAKEENA AKHTER</t>
+  </si>
+  <si>
+    <t>JK13K1988</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSJ679436</t>
+  </si>
+  <si>
+    <t>MBHHWB13SSKB38144</t>
+  </si>
+  <si>
+    <t>SHOWKAT AHMAD BHAT</t>
+  </si>
+  <si>
+    <t>WASEEM AHMAD MIR</t>
+  </si>
+  <si>
+    <t>JK03Q3278</t>
+  </si>
+  <si>
+    <t>ZUBAIR</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSJ668204</t>
+  </si>
+  <si>
+    <t>ZUBAIR AHMAD BHAT</t>
+  </si>
+  <si>
+    <t>JK18E1573</t>
+  </si>
+  <si>
+    <t>WASEEM BASHIR</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSJ476657</t>
+  </si>
+  <si>
+    <t>SAJAD AHMAD SHEIKH</t>
+  </si>
+  <si>
+    <t>ARSHID RASOOL DAR</t>
+  </si>
+  <si>
+    <t>JK04K4120</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSD552969</t>
+  </si>
+  <si>
+    <t>NASEER AHMED</t>
+  </si>
+  <si>
+    <t>FRONX DELTA</t>
+  </si>
+  <si>
+    <t>25BH8403Q</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSJ678040</t>
+  </si>
+  <si>
+    <t>WASEEM AHMAD WANI</t>
+  </si>
+  <si>
+    <t> FRONX DELTA+ 6AB</t>
+  </si>
+  <si>
+    <t>JK22D2625</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSG472861</t>
+  </si>
+  <si>
+    <t>SARDAR RAVINDER SINGH</t>
+  </si>
+  <si>
+    <t>JK13K1183</t>
+  </si>
+  <si>
+    <t>JK04K5411</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSC535347</t>
+  </si>
+  <si>
+    <t>MOHD YAQOOB DAR</t>
+  </si>
+  <si>
+    <t>JK13K2141</t>
+  </si>
+  <si>
+    <t>SALMAN KHALIQ / DRAWER</t>
+  </si>
+  <si>
+    <t>RC RECEIVED BY</t>
   </si>
 </sst>
 </file>
@@ -396,7 +527,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d/mmm/yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd/mmm/yy;@"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -527,12 +658,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -719,7 +844,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -834,6 +959,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -908,10 +1044,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1035,7 +1171,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1123,23 +1259,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}" name="Table1" displayName="Table1" ref="A1:K26" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K26" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-    <sortCondition ref="F1:F26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97E63F84-BDFB-4C38-B1FD-28318E0D1D3F}" name="Table13" displayName="Table13" ref="A1:K105" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K105" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K105">
+    <sortCondition ref="F1:F105"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{C5FAA5C2-D683-4836-A3E6-7F0D524EA103}" name="S.NO" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{95A0C0B2-6AB7-4A1B-AFD7-55FD6A2B913B}" name="CHASSIS" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{FEB1AC79-EE4D-4B04-897E-D273DA0BD281}" name="NAME" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{46EC1EFE-3607-4207-9FFE-5A3770FFFEBE}" name="MODEL" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{A59F05B7-1065-40C0-933C-37EC1B135DA9}" name="REG NUM" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{2644077D-C310-4539-8493-451624D59384}" name="DATE OF REG" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{68F85EFD-E504-4A37-8955-E3793B2B502F}" name="DSE" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{4BC0389E-5375-4903-8F62-68D2E2F55714}" name="RC RECEIVING" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{D51CD378-2BA3-4701-925C-15F60470BF35}" name="DATE" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{E25E943D-8510-40D9-8CDC-3CDFEFC2F5A3}" name="FASTTAG" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{DECCBC09-99A2-4DE7-A638-3BE4CE06C3B6}" name="DATED" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{DEBB3640-E433-4779-93BC-95B8FB492623}" name="S.NO" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{6ABB4EDF-0F58-40D7-979C-D37D8D91A6BC}" name="CHASSIS" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{285CC4F4-4CD1-4FFC-A101-ED051DA40438}" name="NAME" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{28DC8B59-EFA0-4502-86B0-033B0B60D615}" name="MODEL" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{3D7EC305-A438-47DE-A91A-6CB0CF4B1937}" name="REG NUM" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{9942893D-0703-456F-8072-CD136C7B4052}" name="DATE OF REG" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{3AD2B0D9-D7A5-46E0-B596-F6B7F1CDDEA6}" name="DSE" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{475221AE-3FDC-4CED-B76C-4DA1DD4F8AD9}" name="RC RECEIVED BY" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{F594ED7D-6966-47AC-A5C3-25754B73A3CC}" name="DATE" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{452E3ECD-E927-4EC7-A8A2-4A866233750E}" name="FASTTAG" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{CFEE5573-D700-4B26-B382-BCA8210C54C2}" name="DATED" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1445,6 +1581,9 @@
   <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </wetp:taskpane>
 </wetp:taskpanes>
 </file>
 
@@ -1475,16 +1614,28 @@
 </we:webextension>
 </file>
 
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{C28727D4-4370-4E3B-91EF-9F957BBDB335}">
+  <we:reference id="wa104381701" version="1.0.0.4" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA104381701" version="1.0.0.4" store="WA104381701" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB93731C-EBB7-48FC-A9AD-B376A1D45265}">
-  <dimension ref="A1:K27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE94C64E-9B39-47CE-ACCD-DD5031A70035}">
+  <dimension ref="A1:K106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="31.5703125" customWidth="1"/>
     <col min="3" max="3" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="19" style="13" customWidth="1"/>
+    <col min="5" max="5" width="19" style="12" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" style="3" customWidth="1"/>
     <col min="7" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37.7109375" bestFit="1" customWidth="1"/>
@@ -1516,7 +1667,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="I1" s="9" t="s">
         <v>19</v>
@@ -1525,31 +1676,31 @@
         <v>20</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>114</v>
+        <v>101</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="F2" s="6">
         <v>45927</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I2" s="6">
         <v>45965</v>
@@ -1559,28 +1710,28 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>46</v>
+      <c r="E3" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="F3" s="6">
         <v>45934</v>
       </c>
       <c r="G3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="I3" s="6">
         <v>45962</v>
@@ -1590,28 +1741,28 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>94</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>91</v>
+        <v>31</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>90</v>
       </c>
       <c r="F4" s="6">
         <v>45937</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I4" s="6">
         <v>45965</v>
@@ -1621,28 +1772,28 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>87</v>
+        <v>31</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="F5" s="6">
         <v>45938</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I5" s="6">
         <v>45965</v>
@@ -1652,28 +1803,28 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>26</v>
+      <c r="E6" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="F6" s="6">
         <v>45941</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I6" s="6">
         <v>45962</v>
@@ -1687,25 +1838,25 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>66</v>
+      <c r="E7" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="F7" s="6">
         <v>45941</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="6"/>
@@ -1718,57 +1869,59 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>82</v>
+        <v>126</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="F8" s="6">
-        <v>45946</v>
+        <v>45944</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="I8" s="6">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="4"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>78</v>
-      </c>
       <c r="F9" s="6">
-        <v>45953</v>
-      </c>
-      <c r="G9" s="5"/>
+        <v>45946</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>85</v>
+      </c>
       <c r="H9" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I9" s="6">
         <v>45964</v>
@@ -1778,316 +1931,310 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>109</v>
+        <v>151</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="F10" s="6">
-        <v>45958</v>
+        <v>45948</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I10" s="6">
-        <v>45965</v>
+        <v>14</v>
+      </c>
+      <c r="I10" s="3">
+        <v>45966</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="12" t="s">
-        <v>59</v>
+      <c r="E11" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="F11" s="6">
-        <v>45959</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>62</v>
-      </c>
+        <v>45953</v>
+      </c>
+      <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="I11" s="6">
-        <v>45962</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="4">
-        <v>45959</v>
-      </c>
+        <v>45964</v>
+      </c>
+      <c r="J11" s="5"/>
+      <c r="K11" s="4"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="F12" s="6">
-        <v>45960</v>
+        <v>45953</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I12" s="6">
-        <v>45961</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="4">
-        <v>45960</v>
-      </c>
+        <v>45965</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="4"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>73</v>
+        <v>5</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="F13" s="6">
-        <v>45960</v>
+        <v>45953</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="I13" s="6">
-        <v>45964</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13" s="4">
-        <v>45960</v>
-      </c>
+        <v>45966</v>
+      </c>
+      <c r="J13" s="5"/>
+      <c r="K13" s="4"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>4</v>
+        <v>129</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>3</v>
+      <c r="E14" s="5" t="s">
+        <v>130</v>
       </c>
       <c r="F14" s="6">
-        <v>45961</v>
+        <v>45954</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="I14" s="6">
-        <v>45964</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14" s="4">
-        <v>45961</v>
-      </c>
+        <v>45966</v>
+      </c>
+      <c r="J14" s="5"/>
+      <c r="K14" s="4"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>13</v>
+        <v>31</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="F15" s="6">
-        <v>45961</v>
+        <v>45954</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15" s="4">
-        <v>45961</v>
-      </c>
+      <c r="H15" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I15" s="6">
+        <v>45966</v>
+      </c>
+      <c r="J15" s="5"/>
+      <c r="K15" s="4"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>65</v>
+        <v>5</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="F16" s="6">
-        <v>45961</v>
+        <v>45958</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K16" s="4">
-        <v>45962</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="I16" s="6">
+        <v>45965</v>
+      </c>
+      <c r="J16" s="5"/>
+      <c r="K16" s="4"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>72</v>
+        <v>12</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="F17" s="6">
-        <v>45961</v>
+        <v>45959</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="6"/>
+        <v>61</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I17" s="6">
+        <v>45962</v>
+      </c>
       <c r="J17" s="5" t="s">
         <v>23</v>
       </c>
       <c r="K17" s="4">
-        <v>45961</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>39</v>
+        <v>5</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="F18" s="6">
+        <v>45960</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="6">
         <v>45961</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="J18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="4">
+        <v>45960</v>
+      </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>64</v>
+        <v>12</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="F19" s="6">
-        <v>45962</v>
+        <v>45960</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>76</v>
@@ -2099,226 +2246,1572 @@
         <v>23</v>
       </c>
       <c r="K19" s="4">
-        <v>45962</v>
+        <v>45960</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>63</v>
+        <v>120</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="F20" s="6">
-        <v>45962</v>
+        <v>45960</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K20" s="4">
-        <v>45962</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" s="6">
+        <v>45965</v>
+      </c>
+      <c r="J20" s="5"/>
+      <c r="K20" s="4"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>53</v>
+        <v>5</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>3</v>
       </c>
       <c r="F21" s="6">
-        <v>45962</v>
+        <v>45961</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="I21" s="6">
-        <v>45962</v>
+        <v>45964</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>23</v>
       </c>
       <c r="K21" s="4">
-        <v>45962</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="6">
+        <v>45961</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F22" s="6">
-        <v>45962</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I22" s="6">
-        <v>45962</v>
-      </c>
+      <c r="H22" s="5"/>
+      <c r="I22" s="6"/>
       <c r="J22" s="5" t="s">
         <v>23</v>
       </c>
       <c r="K22" s="4">
-        <v>45962</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>105</v>
+        <v>31</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="F23" s="6">
-        <v>45965</v>
+        <v>45961</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="6"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="4"/>
+      <c r="J23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K23" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>106</v>
+        <v>67</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="F24" s="6">
-        <v>45965</v>
+        <v>45961</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="6"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="4"/>
+      <c r="J24" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" s="4">
+        <v>45961</v>
+      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>107</v>
+        <v>37</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="F25" s="6">
-        <v>45965</v>
+        <v>45961</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="6">
+        <v>45966</v>
+      </c>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="6"/>
+      <c r="B26" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F26" s="6">
+        <v>45961</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26" s="3">
+        <v>45966</v>
+      </c>
       <c r="J26" s="5"/>
       <c r="K26" s="4"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J27" t="s">
+      <c r="A27" s="5">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" s="6">
+        <v>45962</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I27" s="6">
+        <v>45964</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="4">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" s="6">
+        <v>45962</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H28" s="5"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" s="4">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" s="6">
+        <v>45962</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="6">
+        <v>45962</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K29" s="4">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" s="6">
+        <v>45962</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I30" s="6">
+        <v>45962</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K30" s="4">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F31" s="6">
+        <v>45965</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="4"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F32" s="6">
+        <v>45965</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H32" s="5"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="4"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F33" s="6">
+        <v>45965</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33" s="13"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="4"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F34" s="6">
+        <v>45966</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F35" s="6">
+        <v>45966</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H35" s="5"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="4"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F36" s="6">
+        <v>45966</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H36" s="5"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="4"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F37" s="6">
+        <v>45966</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H37" s="5"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="4"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="4"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="4"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="4"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="4"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="4"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="4"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>43</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="4"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="4"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
         <v>45</v>
       </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="4"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="4"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="4"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="4"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>49</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="4"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="4"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>51</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="4"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>52</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="4"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
+        <v>53</v>
+      </c>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="4"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>54</v>
+      </c>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="4"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
+        <v>55</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="4"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
+        <v>56</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="4"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="5">
+        <v>57</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="4"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>58</v>
+      </c>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="4"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>59</v>
+      </c>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="4"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="4"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
+        <v>61</v>
+      </c>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="4"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
+        <v>62</v>
+      </c>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="4"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>63</v>
+      </c>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="4"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>64</v>
+      </c>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="4"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>65</v>
+      </c>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="4"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>66</v>
+      </c>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="4"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>67</v>
+      </c>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="4"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>68</v>
+      </c>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="4"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>69</v>
+      </c>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="4"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>70</v>
+      </c>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="4"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
+        <v>71</v>
+      </c>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="4"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>72</v>
+      </c>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="4"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>73</v>
+      </c>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="4"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
+        <v>74</v>
+      </c>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="6"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="4"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="5">
+        <v>75</v>
+      </c>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="4"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>76</v>
+      </c>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="6"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="4"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
+        <v>77</v>
+      </c>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="4"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
+        <v>78</v>
+      </c>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="6"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="4"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="5">
+        <v>79</v>
+      </c>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="4"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="5">
+        <v>80</v>
+      </c>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="5"/>
+      <c r="K81" s="4"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="5">
+        <v>81</v>
+      </c>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="4"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="5">
+        <v>82</v>
+      </c>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="6"/>
+      <c r="J83" s="5"/>
+      <c r="K83" s="4"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="5">
+        <v>83</v>
+      </c>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="4"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="5">
+        <v>84</v>
+      </c>
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="5"/>
+      <c r="K85" s="4"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="5">
+        <v>85</v>
+      </c>
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="6"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="4"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" s="5">
+        <v>86</v>
+      </c>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="6"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="4"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="5">
+        <v>87</v>
+      </c>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="6"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="4"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="5">
+        <v>88</v>
+      </c>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="5"/>
+      <c r="K89" s="4"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="5">
+        <v>89</v>
+      </c>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="4"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" s="5">
+        <v>90</v>
+      </c>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="6"/>
+      <c r="J91" s="5"/>
+      <c r="K91" s="4"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="5">
+        <v>91</v>
+      </c>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="6"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="4"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="5">
+        <v>92</v>
+      </c>
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="6"/>
+      <c r="J93" s="5"/>
+      <c r="K93" s="4"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" s="5">
+        <v>93</v>
+      </c>
+      <c r="B94" s="5"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="6"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="4"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="5">
+        <v>94</v>
+      </c>
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="6"/>
+      <c r="J95" s="5"/>
+      <c r="K95" s="4"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="5">
+        <v>95</v>
+      </c>
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="6"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="4"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="5">
+        <v>96</v>
+      </c>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+      <c r="I97" s="6"/>
+      <c r="J97" s="5"/>
+      <c r="K97" s="4"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="5">
+        <v>97</v>
+      </c>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="4"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="5">
+        <v>98</v>
+      </c>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="6"/>
+      <c r="J99" s="5"/>
+      <c r="K99" s="4"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="5">
+        <v>99</v>
+      </c>
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="6"/>
+      <c r="J100" s="5"/>
+      <c r="K100" s="4"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="5">
+        <v>100</v>
+      </c>
+      <c r="B101" s="5"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
+      <c r="I101" s="6"/>
+      <c r="J101" s="5"/>
+      <c r="K101" s="4"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="5">
+        <v>101</v>
+      </c>
+      <c r="B102" s="5"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
+      <c r="I102" s="6"/>
+      <c r="J102" s="5"/>
+      <c r="K102" s="4"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" s="5">
+        <v>102</v>
+      </c>
+      <c r="B103" s="5"/>
+      <c r="C103" s="5"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
+      <c r="I103" s="6"/>
+      <c r="J103" s="5"/>
+      <c r="K103" s="4"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" s="5">
+        <v>103</v>
+      </c>
+      <c r="B104" s="5"/>
+      <c r="C104" s="5"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="6"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="4"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" s="5">
+        <v>104</v>
+      </c>
+      <c r="E105"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J106" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="2" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C8F1167-DDBD-48E7-B937-E6DB0DAB49C3}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/RegistrationsFile.xlsx
+++ b/RegistrationsFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A656135F-E1F6-40E8-8A7A-E51E7969CE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236DE046-2420-43A1-898C-64A9614020F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="541" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="163">
   <si>
     <t>MODEL</t>
   </si>
@@ -517,6 +517,9 @@
   </si>
   <si>
     <t>RC RECEIVED BY</t>
+  </si>
+  <si>
+    <t>RC GIVEN TO ARSHID</t>
   </si>
 </sst>
 </file>
@@ -2732,8 +2735,12 @@
       <c r="G35" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="H35" s="5"/>
-      <c r="I35" s="6"/>
+      <c r="H35" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="I35" s="6">
+        <v>45966</v>
+      </c>
       <c r="J35" s="5"/>
       <c r="K35" s="4"/>
     </row>

--- a/RegistrationsFile.xlsx
+++ b/RegistrationsFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236DE046-2420-43A1-898C-64A9614020F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E73B8E-27AE-4074-81A3-43133994E23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="541" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="189">
   <si>
     <t>MODEL</t>
   </si>
@@ -441,9 +441,6 @@
     <t>JK03Q3278</t>
   </si>
   <si>
-    <t>ZUBAIR</t>
-  </si>
-  <si>
     <t>MBHKWD13SSJ668204</t>
   </si>
   <si>
@@ -520,6 +517,87 @@
   </si>
   <si>
     <t>RC GIVEN TO ARSHID</t>
+  </si>
+  <si>
+    <t>RC GIVEN TO FAIZAN ASHRAF</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSG473338</t>
+  </si>
+  <si>
+    <t>NAZIR AHMAD SOFI</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSG473683</t>
+  </si>
+  <si>
+    <t>UMER FAYAZ</t>
+  </si>
+  <si>
+    <t>IQBAL HABIB</t>
+  </si>
+  <si>
+    <t>Application No.</t>
+  </si>
+  <si>
+    <t>JK25110691581416</t>
+  </si>
+  <si>
+    <t>JK25110671591434</t>
+  </si>
+  <si>
+    <t>JK13K2194</t>
+  </si>
+  <si>
+    <t>JK13K2172</t>
+  </si>
+  <si>
+    <t>JK25110671640395</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSD466993</t>
+  </si>
+  <si>
+    <t>NAZIR AHMAD MIR</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>PRME CELESTIAL BLUE</t>
+  </si>
+  <si>
+    <t>GLISTENINGGREY</t>
+  </si>
+  <si>
+    <t>ZUBAIR PARRAY</t>
+  </si>
+  <si>
+    <t>JK25110581469622</t>
+  </si>
+  <si>
+    <t>JK01BC5501</t>
+  </si>
+  <si>
+    <t>MBHHWB13SSKB37632</t>
+  </si>
+  <si>
+    <t>SAMIA MASOOD</t>
+  </si>
+  <si>
+    <t>PRME GRANDEUR GREY</t>
+  </si>
+  <si>
+    <t>JK25110631690254</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSJ667222</t>
+  </si>
+  <si>
+    <t>RAM CHANDER</t>
+  </si>
+  <si>
+    <t>25BH2180Q</t>
   </si>
 </sst>
 </file>
@@ -1096,7 +1174,10 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="15">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1221,6 +1302,9 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <strike val="0"/>
@@ -1262,23 +1346,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97E63F84-BDFB-4C38-B1FD-28318E0D1D3F}" name="Table13" displayName="Table13" ref="A1:K105" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K105" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K105">
-    <sortCondition ref="F1:F105"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97E63F84-BDFB-4C38-B1FD-28318E0D1D3F}" name="Table13" displayName="Table13" ref="A1:M105" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+  <autoFilter ref="A1:M105" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M105">
+    <sortCondition ref="H1:H105"/>
   </sortState>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DEBB3640-E433-4779-93BC-95B8FB492623}" name="S.NO" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{6ABB4EDF-0F58-40D7-979C-D37D8D91A6BC}" name="CHASSIS" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{285CC4F4-4CD1-4FFC-A101-ED051DA40438}" name="NAME" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{28DC8B59-EFA0-4502-86B0-033B0B60D615}" name="MODEL" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{3D7EC305-A438-47DE-A91A-6CB0CF4B1937}" name="REG NUM" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{9942893D-0703-456F-8072-CD136C7B4052}" name="DATE OF REG" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{3AD2B0D9-D7A5-46E0-B596-F6B7F1CDDEA6}" name="DSE" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{475221AE-3FDC-4CED-B76C-4DA1DD4F8AD9}" name="RC RECEIVED BY" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{F594ED7D-6966-47AC-A5C3-25754B73A3CC}" name="DATE" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{452E3ECD-E927-4EC7-A8A2-4A866233750E}" name="FASTTAG" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{CFEE5573-D700-4B26-B382-BCA8210C54C2}" name="DATED" dataDxfId="0"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{DEBB3640-E433-4779-93BC-95B8FB492623}" name="S.NO" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{86C56767-9BFE-4154-9FC1-CEA7C183815E}" name="Application No." dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{6ABB4EDF-0F58-40D7-979C-D37D8D91A6BC}" name="CHASSIS" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{285CC4F4-4CD1-4FFC-A101-ED051DA40438}" name="NAME" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{28DC8B59-EFA0-4502-86B0-033B0B60D615}" name="MODEL" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{B25F5A6A-3B72-4772-B75C-D86670F35131}" name="Color" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{3D7EC305-A438-47DE-A91A-6CB0CF4B1937}" name="REG NUM" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{9942893D-0703-456F-8072-CD136C7B4052}" name="DATE OF REG" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{3AD2B0D9-D7A5-46E0-B596-F6B7F1CDDEA6}" name="DSE" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{475221AE-3FDC-4CED-B76C-4DA1DD4F8AD9}" name="RC RECEIVED BY" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{F594ED7D-6966-47AC-A5C3-25754B73A3CC}" name="DATE" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{452E3ECD-E927-4EC7-A8A2-4A866233750E}" name="FASTTAG" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{CFEE5573-D700-4B26-B382-BCA8210C54C2}" name="DATED" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1631,1249 +1717,1424 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE94C64E-9B39-47CE-ACCD-DD5031A70035}">
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:M106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.5703125" customWidth="1"/>
-    <col min="3" max="3" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="19" style="12" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="22.28515625" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5703125" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.85546875" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" customWidth="1"/>
+    <col min="7" max="7" width="19" style="12" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="22.28515625" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="M1" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="6">
+      <c r="H2" s="6">
         <v>45927</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5"/>
+      <c r="J2" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="I2" s="6">
+      <c r="K2" s="6">
         <v>45965</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" s="5"/>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="6">
+      <c r="H3" s="6">
         <v>45934</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="6">
+      <c r="K3" s="6">
         <v>45962</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" s="5"/>
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5"/>
+      <c r="G4" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F4" s="6">
+      <c r="H4" s="6">
         <v>45937</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="I4" s="6">
+      <c r="K4" s="6">
         <v>45965</v>
       </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" s="5"/>
+      <c r="M4" s="4"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5"/>
+      <c r="G5" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F5" s="6">
+      <c r="H5" s="6">
         <v>45938</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="I5" s="6">
+      <c r="K5" s="6">
         <v>45965</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="5"/>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5"/>
+      <c r="G6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="6">
+      <c r="H6" s="6">
         <v>45941</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="6">
+      <c r="K6" s="6">
         <v>45962</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="L6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="4">
+      <c r="M6" s="4">
         <v>45973</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="6">
+      <c r="H7" s="6">
         <v>45941</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="5"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="4">
+      <c r="M7" s="4">
         <v>45962</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5"/>
+      <c r="G8" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F8" s="6">
+      <c r="H8" s="6">
         <v>45944</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="I8" s="6">
+      <c r="K8" s="6">
         <v>45966</v>
       </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="4"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" s="5"/>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F9" s="6">
+      <c r="H9" s="6">
         <v>45946</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="I9" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="J9" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="I9" s="6">
+      <c r="K9" s="6">
         <v>45964</v>
       </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="4"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" s="5"/>
+      <c r="M9" s="4"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="5"/>
+      <c r="C10" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="F10" s="5"/>
+      <c r="G10" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="H10" s="6">
         <v>45948</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="J10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="6">
         <v>45966</v>
       </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" s="5"/>
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="5"/>
+      <c r="G11" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F11" s="6">
+      <c r="H11" s="6">
         <v>45953</v>
       </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5" t="s">
+      <c r="I11" s="5"/>
+      <c r="J11" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I11" s="6">
+      <c r="K11" s="6">
         <v>45964</v>
       </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="4"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" s="5"/>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="5"/>
+      <c r="G12" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="F12" s="6">
+      <c r="H12" s="6">
         <v>45953</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="I12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="J12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="6">
+      <c r="K12" s="6">
         <v>45965</v>
       </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" s="5"/>
+      <c r="M12" s="4"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5"/>
+      <c r="G13" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F13" s="6">
+      <c r="H13" s="6">
         <v>45953</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="J13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="6">
+      <c r="K13" s="6">
         <v>45966</v>
       </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" s="5"/>
+      <c r="M13" s="4"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F14" s="6">
+      <c r="H14" s="6">
         <v>45954</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="I14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="J14" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="I14" s="6">
+      <c r="K14" s="6">
         <v>45966</v>
       </c>
-      <c r="J14" s="5"/>
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" s="5"/>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="E15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="F15" s="6">
+      <c r="H15" s="6">
         <v>45954</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="I15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="I15" s="6">
+      <c r="J15" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="K15" s="6">
         <v>45966</v>
       </c>
-      <c r="J15" s="5"/>
-      <c r="K15" s="4"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="5"/>
+      <c r="M15" s="4"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="5"/>
+      <c r="C16" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F16" s="6">
+      <c r="H16" s="6">
         <v>45958</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="I16" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="J16" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="I16" s="6">
+      <c r="K16" s="6">
         <v>45965</v>
       </c>
-      <c r="J16" s="5"/>
-      <c r="K16" s="4"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16" s="5"/>
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="6">
+      <c r="H17" s="6">
         <v>45959</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="I17" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="J17" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="I17" s="6">
+      <c r="K17" s="6">
         <v>45962</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="L17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="4">
+      <c r="M17" s="4">
         <v>45959</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="6">
+      <c r="H18" s="6">
         <v>45960</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="I18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="J18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="6">
+      <c r="K18" s="6">
         <v>45961</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="L18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K18" s="4">
+      <c r="M18" s="4">
         <v>45960</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F19" s="6">
+      <c r="H19" s="6">
         <v>45960</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="I19" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="J19" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I19" s="6">
+      <c r="K19" s="6">
         <v>45964</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="L19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K19" s="4">
+      <c r="M19" s="4">
         <v>45960</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="F20" s="6">
+      <c r="H20" s="6">
         <v>45960</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="I20" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="J20" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I20" s="6">
+      <c r="K20" s="6">
         <v>45965</v>
       </c>
-      <c r="J20" s="5"/>
-      <c r="K20" s="4"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L20" s="5"/>
+      <c r="M20" s="4"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F21" s="6">
+      <c r="H21" s="6">
         <v>45961</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="I21" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="J21" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I21" s="6">
+      <c r="K21" s="6">
         <v>45964</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="L21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K21" s="4">
+      <c r="M21" s="4">
         <v>45961</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="6">
+      <c r="H22" s="6">
         <v>45961</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="I22" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="5"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K22" s="4">
+      <c r="M22" s="4">
         <v>45961</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="5"/>
+      <c r="C23" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="6">
+      <c r="H23" s="6">
         <v>45961</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="I23" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="5" t="s">
+      <c r="J23" s="5"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K23" s="4">
+      <c r="M23" s="4">
         <v>45962</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="5"/>
+      <c r="C24" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5"/>
+      <c r="G24" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F24" s="6">
+      <c r="H24" s="6">
         <v>45961</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="I24" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H24" s="5"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="5" t="s">
+      <c r="J24" s="5"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K24" s="4">
+      <c r="M24" s="4">
         <v>45961</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5"/>
+      <c r="G25" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="6">
+      <c r="H25" s="6">
         <v>45961</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="I25" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="J25" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="6">
+      <c r="K25" s="6">
         <v>45966</v>
       </c>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="5"/>
+      <c r="C26" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="F26" s="5"/>
+      <c r="G26" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F26" s="6">
+      <c r="H26" s="6">
         <v>45961</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="I26" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="J26" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="6">
         <v>45966</v>
       </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="4"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L26" s="5"/>
+      <c r="M26" s="4"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5"/>
+      <c r="G27" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F27" s="6">
+      <c r="H27" s="6">
         <v>45962</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="I27" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="J27" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I27" s="6">
+      <c r="K27" s="6">
         <v>45964</v>
       </c>
-      <c r="J27" s="5" t="s">
+      <c r="L27" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K27" s="4">
+      <c r="M27" s="4">
         <v>45962</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="5"/>
+      <c r="C28" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="F28" s="5"/>
+      <c r="G28" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F28" s="6">
+      <c r="H28" s="6">
         <v>45962</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="I28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="5" t="s">
+      <c r="J28" s="5"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K28" s="4">
+      <c r="M28" s="4">
         <v>45962</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="5"/>
+      <c r="C29" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="F29" s="5"/>
+      <c r="G29" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="6">
+      <c r="H29" s="6">
         <v>45962</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="I29" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="J29" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I29" s="6">
+      <c r="K29" s="6">
         <v>45962</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="L29" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K29" s="4">
+      <c r="M29" s="4">
         <v>45962</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>29</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="5"/>
+      <c r="C30" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="E30" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="F30" s="5"/>
+      <c r="G30" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F30" s="6">
+      <c r="H30" s="6">
         <v>45962</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="I30" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="J30" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="I30" s="6">
+      <c r="K30" s="6">
         <v>45962</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="L30" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K30" s="4">
+      <c r="M30" s="4">
         <v>45962</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="5"/>
+      <c r="C31" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="F31" s="5"/>
+      <c r="G31" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F31" s="6">
+      <c r="H31" s="6">
         <v>45965</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="I31" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H31" s="5"/>
-      <c r="I31" s="6"/>
       <c r="J31" s="5"/>
-      <c r="K31" s="4"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="4"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>31</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="5"/>
+      <c r="C32" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="F32" s="5"/>
+      <c r="G32" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="F32" s="6">
+      <c r="H32" s="6">
         <v>45965</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="I32" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="H32" s="5"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="4"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J32" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K32" s="6">
+        <v>45967</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" s="4"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="5"/>
+      <c r="C33" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="E33" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="F33" s="5"/>
+      <c r="G33" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F33" s="6">
+      <c r="H33" s="6">
         <v>45965</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="I33" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H33" s="13"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="4"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J33" s="13"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="4"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>33</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="5"/>
+      <c r="C34" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="E34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="5" t="s">
+      <c r="H34" s="6">
+        <v>45966</v>
+      </c>
+      <c r="I34" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="F34" s="6">
-        <v>45966</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K34" s="6"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>34</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="5"/>
+      <c r="C35" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D35" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F35" s="6">
-        <v>45966</v>
-      </c>
+      <c r="F35" s="5"/>
       <c r="G35" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="H35" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="I35" s="6">
+      <c r="H35" s="6">
         <v>45966</v>
       </c>
-      <c r="J35" s="5"/>
-      <c r="K35" s="4"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I35" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="K35" s="6">
+        <v>45966</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="4"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>35</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="5"/>
+      <c r="C36" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F36" s="6">
+      <c r="F36" s="5"/>
+      <c r="G36" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H36" s="6">
         <v>45966</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="H36" s="5"/>
-      <c r="I36" s="6"/>
+      <c r="I36" s="5" t="s">
+        <v>179</v>
+      </c>
       <c r="J36" s="5"/>
-      <c r="K36" s="4"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K36" s="6"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="4"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="E37" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="F37" s="6">
+      <c r="H37" s="6">
         <v>45966</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="I37" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H37" s="5"/>
-      <c r="I37" s="6"/>
       <c r="J37" s="5"/>
-      <c r="K37" s="4"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K37" s="6"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="4"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>37</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="6"/>
+      <c r="B38" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H38" s="6">
+        <v>45967</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="J38" s="5"/>
-      <c r="K38" s="4"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K38" s="6"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="4"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="6"/>
+      <c r="B39" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H39" s="6">
+        <v>45967</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="J39" s="5"/>
-      <c r="K39" s="4"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K39" s="6"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="4"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>39</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="6"/>
+      <c r="B40" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H40" s="6">
+        <v>45967</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="J40" s="5"/>
-      <c r="K40" s="4"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K40" s="6"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="4"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="6"/>
+      <c r="B41" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="6"/>
+      <c r="H41" s="6">
+        <v>45967</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>179</v>
+      </c>
       <c r="J41" s="5"/>
-      <c r="K41" s="4"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K41" s="6"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="4"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>41</v>
       </c>
       <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="6"/>
+      <c r="C42" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="H42" s="6">
+        <v>45959</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="J42" s="5"/>
-      <c r="K42" s="4"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K42" s="6"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="4"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -2881,29 +3142,35 @@
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
-      <c r="F43" s="6"/>
+      <c r="F43" s="5"/>
       <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="5"/>
       <c r="J43" s="5"/>
-      <c r="K43" s="4"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K43" s="6"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="4"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>43</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
+      <c r="D44" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="E44" s="5"/>
-      <c r="F44" s="6"/>
+      <c r="F44" s="5"/>
       <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="5"/>
       <c r="J44" s="5"/>
-      <c r="K44" s="4"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K44" s="6"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="4"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -2911,14 +3178,16 @@
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
-      <c r="F45" s="6"/>
+      <c r="F45" s="5"/>
       <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="5"/>
       <c r="J45" s="5"/>
-      <c r="K45" s="4"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K45" s="6"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="4"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -2926,14 +3195,16 @@
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
-      <c r="F46" s="6"/>
+      <c r="F46" s="5"/>
       <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="5"/>
       <c r="J46" s="5"/>
-      <c r="K46" s="4"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K46" s="6"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="4"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -2941,14 +3212,16 @@
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
-      <c r="F47" s="6"/>
+      <c r="F47" s="5"/>
       <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="5"/>
       <c r="J47" s="5"/>
-      <c r="K47" s="4"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K47" s="6"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="4"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -2956,14 +3229,16 @@
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
-      <c r="F48" s="6"/>
+      <c r="F48" s="5"/>
       <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="5"/>
       <c r="J48" s="5"/>
-      <c r="K48" s="4"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K48" s="6"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="4"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -2971,14 +3246,16 @@
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
-      <c r="F49" s="6"/>
+      <c r="F49" s="5"/>
       <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="5"/>
       <c r="J49" s="5"/>
-      <c r="K49" s="4"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K49" s="6"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="4"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -2986,14 +3263,16 @@
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
-      <c r="F50" s="6"/>
+      <c r="F50" s="5"/>
       <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="5"/>
       <c r="J50" s="5"/>
-      <c r="K50" s="4"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K50" s="6"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="4"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -3001,14 +3280,16 @@
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
-      <c r="F51" s="6"/>
+      <c r="F51" s="5"/>
       <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="5"/>
       <c r="J51" s="5"/>
-      <c r="K51" s="4"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K51" s="6"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="4"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -3016,14 +3297,16 @@
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
-      <c r="F52" s="6"/>
+      <c r="F52" s="5"/>
       <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="5"/>
       <c r="J52" s="5"/>
-      <c r="K52" s="4"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K52" s="6"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="4"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -3031,14 +3314,16 @@
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
-      <c r="F53" s="6"/>
+      <c r="F53" s="5"/>
       <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="5"/>
       <c r="J53" s="5"/>
-      <c r="K53" s="4"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K53" s="6"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="4"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -3046,14 +3331,16 @@
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
-      <c r="F54" s="6"/>
+      <c r="F54" s="5"/>
       <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="5"/>
       <c r="J54" s="5"/>
-      <c r="K54" s="4"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K54" s="6"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="4"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -3061,14 +3348,16 @@
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
-      <c r="F55" s="6"/>
+      <c r="F55" s="5"/>
       <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="5"/>
       <c r="J55" s="5"/>
-      <c r="K55" s="4"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K55" s="6"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="4"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -3076,14 +3365,16 @@
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
-      <c r="F56" s="6"/>
+      <c r="F56" s="5"/>
       <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="5"/>
       <c r="J56" s="5"/>
-      <c r="K56" s="4"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K56" s="6"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="4"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -3091,14 +3382,16 @@
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
-      <c r="F57" s="6"/>
+      <c r="F57" s="5"/>
       <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="5"/>
       <c r="J57" s="5"/>
-      <c r="K57" s="4"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K57" s="6"/>
+      <c r="L57" s="5"/>
+      <c r="M57" s="4"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -3106,14 +3399,16 @@
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
-      <c r="F58" s="6"/>
+      <c r="F58" s="5"/>
       <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="5"/>
       <c r="J58" s="5"/>
-      <c r="K58" s="4"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K58" s="6"/>
+      <c r="L58" s="5"/>
+      <c r="M58" s="4"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -3121,14 +3416,16 @@
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
-      <c r="F59" s="6"/>
+      <c r="F59" s="5"/>
       <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
-      <c r="I59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="5"/>
       <c r="J59" s="5"/>
-      <c r="K59" s="4"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K59" s="6"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="4"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -3136,14 +3433,16 @@
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
-      <c r="F60" s="6"/>
+      <c r="F60" s="5"/>
       <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="5"/>
       <c r="J60" s="5"/>
-      <c r="K60" s="4"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K60" s="6"/>
+      <c r="L60" s="5"/>
+      <c r="M60" s="4"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -3151,14 +3450,16 @@
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
-      <c r="F61" s="6"/>
+      <c r="F61" s="5"/>
       <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="5"/>
       <c r="J61" s="5"/>
-      <c r="K61" s="4"/>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K61" s="6"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="4"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -3166,14 +3467,16 @@
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
-      <c r="F62" s="6"/>
+      <c r="F62" s="5"/>
       <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="5"/>
       <c r="J62" s="5"/>
-      <c r="K62" s="4"/>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K62" s="6"/>
+      <c r="L62" s="5"/>
+      <c r="M62" s="4"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -3181,14 +3484,16 @@
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
-      <c r="F63" s="6"/>
+      <c r="F63" s="5"/>
       <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="5"/>
       <c r="J63" s="5"/>
-      <c r="K63" s="4"/>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K63" s="6"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="4"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -3196,14 +3501,16 @@
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
-      <c r="F64" s="6"/>
+      <c r="F64" s="5"/>
       <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="5"/>
       <c r="J64" s="5"/>
-      <c r="K64" s="4"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K64" s="6"/>
+      <c r="L64" s="5"/>
+      <c r="M64" s="4"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -3211,14 +3518,16 @@
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
-      <c r="F65" s="6"/>
+      <c r="F65" s="5"/>
       <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="5"/>
       <c r="J65" s="5"/>
-      <c r="K65" s="4"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K65" s="6"/>
+      <c r="L65" s="5"/>
+      <c r="M65" s="4"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -3226,14 +3535,16 @@
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
-      <c r="F66" s="6"/>
+      <c r="F66" s="5"/>
       <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="5"/>
       <c r="J66" s="5"/>
-      <c r="K66" s="4"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K66" s="6"/>
+      <c r="L66" s="5"/>
+      <c r="M66" s="4"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -3241,14 +3552,16 @@
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
-      <c r="F67" s="6"/>
+      <c r="F67" s="5"/>
       <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="5"/>
       <c r="J67" s="5"/>
-      <c r="K67" s="4"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K67" s="6"/>
+      <c r="L67" s="5"/>
+      <c r="M67" s="4"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -3256,14 +3569,16 @@
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
-      <c r="F68" s="6"/>
+      <c r="F68" s="5"/>
       <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-      <c r="I68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="5"/>
       <c r="J68" s="5"/>
-      <c r="K68" s="4"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K68" s="6"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="4"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -3271,14 +3586,16 @@
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
-      <c r="F69" s="6"/>
+      <c r="F69" s="5"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="5"/>
       <c r="J69" s="5"/>
-      <c r="K69" s="4"/>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K69" s="6"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="4"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -3286,14 +3603,16 @@
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
-      <c r="F70" s="6"/>
+      <c r="F70" s="5"/>
       <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="5"/>
       <c r="J70" s="5"/>
-      <c r="K70" s="4"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K70" s="6"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="4"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -3301,14 +3620,16 @@
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
-      <c r="F71" s="6"/>
+      <c r="F71" s="5"/>
       <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="5"/>
       <c r="J71" s="5"/>
-      <c r="K71" s="4"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K71" s="6"/>
+      <c r="L71" s="5"/>
+      <c r="M71" s="4"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -3316,14 +3637,16 @@
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
-      <c r="F72" s="6"/>
+      <c r="F72" s="5"/>
       <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="5"/>
       <c r="J72" s="5"/>
-      <c r="K72" s="4"/>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K72" s="6"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="4"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -3331,14 +3654,16 @@
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
-      <c r="F73" s="6"/>
+      <c r="F73" s="5"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
-      <c r="I73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="5"/>
       <c r="J73" s="5"/>
-      <c r="K73" s="4"/>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K73" s="6"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="4"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -3346,14 +3671,16 @@
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
-      <c r="F74" s="6"/>
+      <c r="F74" s="5"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="5"/>
       <c r="J74" s="5"/>
-      <c r="K74" s="4"/>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K74" s="6"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="4"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>74</v>
       </c>
@@ -3361,14 +3688,16 @@
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
-      <c r="F75" s="6"/>
+      <c r="F75" s="5"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-      <c r="I75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="5"/>
       <c r="J75" s="5"/>
-      <c r="K75" s="4"/>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K75" s="6"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="4"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -3376,14 +3705,16 @@
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
-      <c r="F76" s="6"/>
+      <c r="F76" s="5"/>
       <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-      <c r="I76" s="6"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="5"/>
       <c r="J76" s="5"/>
-      <c r="K76" s="4"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K76" s="6"/>
+      <c r="L76" s="5"/>
+      <c r="M76" s="4"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>76</v>
       </c>
@@ -3391,14 +3722,16 @@
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
-      <c r="F77" s="6"/>
+      <c r="F77" s="5"/>
       <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
-      <c r="I77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="5"/>
       <c r="J77" s="5"/>
-      <c r="K77" s="4"/>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K77" s="6"/>
+      <c r="L77" s="5"/>
+      <c r="M77" s="4"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -3406,14 +3739,16 @@
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
-      <c r="F78" s="6"/>
+      <c r="F78" s="5"/>
       <c r="G78" s="5"/>
-      <c r="H78" s="5"/>
-      <c r="I78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="5"/>
       <c r="J78" s="5"/>
-      <c r="K78" s="4"/>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K78" s="6"/>
+      <c r="L78" s="5"/>
+      <c r="M78" s="4"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -3421,14 +3756,16 @@
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
-      <c r="F79" s="6"/>
+      <c r="F79" s="5"/>
       <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
-      <c r="I79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="5"/>
       <c r="J79" s="5"/>
-      <c r="K79" s="4"/>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K79" s="6"/>
+      <c r="L79" s="5"/>
+      <c r="M79" s="4"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -3436,14 +3773,16 @@
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
-      <c r="F80" s="6"/>
+      <c r="F80" s="5"/>
       <c r="G80" s="5"/>
-      <c r="H80" s="5"/>
-      <c r="I80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="5"/>
       <c r="J80" s="5"/>
-      <c r="K80" s="4"/>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K80" s="6"/>
+      <c r="L80" s="5"/>
+      <c r="M80" s="4"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>80</v>
       </c>
@@ -3451,14 +3790,16 @@
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
-      <c r="F81" s="6"/>
+      <c r="F81" s="5"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="5"/>
-      <c r="I81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="5"/>
       <c r="J81" s="5"/>
-      <c r="K81" s="4"/>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K81" s="6"/>
+      <c r="L81" s="5"/>
+      <c r="M81" s="4"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>81</v>
       </c>
@@ -3466,14 +3807,16 @@
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
-      <c r="F82" s="6"/>
+      <c r="F82" s="5"/>
       <c r="G82" s="5"/>
-      <c r="H82" s="5"/>
-      <c r="I82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="5"/>
       <c r="J82" s="5"/>
-      <c r="K82" s="4"/>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K82" s="6"/>
+      <c r="L82" s="5"/>
+      <c r="M82" s="4"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -3481,14 +3824,16 @@
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
-      <c r="F83" s="6"/>
+      <c r="F83" s="5"/>
       <c r="G83" s="5"/>
-      <c r="H83" s="5"/>
-      <c r="I83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="5"/>
       <c r="J83" s="5"/>
-      <c r="K83" s="4"/>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K83" s="6"/>
+      <c r="L83" s="5"/>
+      <c r="M83" s="4"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>83</v>
       </c>
@@ -3496,14 +3841,16 @@
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
-      <c r="F84" s="6"/>
+      <c r="F84" s="5"/>
       <c r="G84" s="5"/>
-      <c r="H84" s="5"/>
-      <c r="I84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="5"/>
       <c r="J84" s="5"/>
-      <c r="K84" s="4"/>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K84" s="6"/>
+      <c r="L84" s="5"/>
+      <c r="M84" s="4"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>84</v>
       </c>
@@ -3511,14 +3858,16 @@
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
-      <c r="F85" s="6"/>
+      <c r="F85" s="5"/>
       <c r="G85" s="5"/>
-      <c r="H85" s="5"/>
-      <c r="I85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="5"/>
       <c r="J85" s="5"/>
-      <c r="K85" s="4"/>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K85" s="6"/>
+      <c r="L85" s="5"/>
+      <c r="M85" s="4"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>85</v>
       </c>
@@ -3526,14 +3875,16 @@
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
-      <c r="F86" s="6"/>
+      <c r="F86" s="5"/>
       <c r="G86" s="5"/>
-      <c r="H86" s="5"/>
-      <c r="I86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="5"/>
       <c r="J86" s="5"/>
-      <c r="K86" s="4"/>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K86" s="6"/>
+      <c r="L86" s="5"/>
+      <c r="M86" s="4"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>86</v>
       </c>
@@ -3541,14 +3892,16 @@
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
-      <c r="F87" s="6"/>
+      <c r="F87" s="5"/>
       <c r="G87" s="5"/>
-      <c r="H87" s="5"/>
-      <c r="I87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="5"/>
       <c r="J87" s="5"/>
-      <c r="K87" s="4"/>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K87" s="6"/>
+      <c r="L87" s="5"/>
+      <c r="M87" s="4"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>87</v>
       </c>
@@ -3556,14 +3909,16 @@
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
-      <c r="F88" s="6"/>
+      <c r="F88" s="5"/>
       <c r="G88" s="5"/>
-      <c r="H88" s="5"/>
-      <c r="I88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="5"/>
       <c r="J88" s="5"/>
-      <c r="K88" s="4"/>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K88" s="6"/>
+      <c r="L88" s="5"/>
+      <c r="M88" s="4"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>88</v>
       </c>
@@ -3571,14 +3926,16 @@
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
-      <c r="F89" s="6"/>
+      <c r="F89" s="5"/>
       <c r="G89" s="5"/>
-      <c r="H89" s="5"/>
-      <c r="I89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="5"/>
       <c r="J89" s="5"/>
-      <c r="K89" s="4"/>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K89" s="6"/>
+      <c r="L89" s="5"/>
+      <c r="M89" s="4"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>89</v>
       </c>
@@ -3586,14 +3943,16 @@
       <c r="C90" s="5"/>
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
-      <c r="F90" s="6"/>
+      <c r="F90" s="5"/>
       <c r="G90" s="5"/>
-      <c r="H90" s="5"/>
-      <c r="I90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="5"/>
       <c r="J90" s="5"/>
-      <c r="K90" s="4"/>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K90" s="6"/>
+      <c r="L90" s="5"/>
+      <c r="M90" s="4"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>90</v>
       </c>
@@ -3601,14 +3960,16 @@
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
-      <c r="F91" s="6"/>
+      <c r="F91" s="5"/>
       <c r="G91" s="5"/>
-      <c r="H91" s="5"/>
-      <c r="I91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="5"/>
       <c r="J91" s="5"/>
-      <c r="K91" s="4"/>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K91" s="6"/>
+      <c r="L91" s="5"/>
+      <c r="M91" s="4"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>91</v>
       </c>
@@ -3616,14 +3977,16 @@
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
-      <c r="F92" s="6"/>
+      <c r="F92" s="5"/>
       <c r="G92" s="5"/>
-      <c r="H92" s="5"/>
-      <c r="I92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="5"/>
       <c r="J92" s="5"/>
-      <c r="K92" s="4"/>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K92" s="6"/>
+      <c r="L92" s="5"/>
+      <c r="M92" s="4"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>92</v>
       </c>
@@ -3631,14 +3994,16 @@
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
-      <c r="F93" s="6"/>
+      <c r="F93" s="5"/>
       <c r="G93" s="5"/>
-      <c r="H93" s="5"/>
-      <c r="I93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="5"/>
       <c r="J93" s="5"/>
-      <c r="K93" s="4"/>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K93" s="6"/>
+      <c r="L93" s="5"/>
+      <c r="M93" s="4"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>93</v>
       </c>
@@ -3646,14 +4011,16 @@
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
-      <c r="F94" s="6"/>
+      <c r="F94" s="5"/>
       <c r="G94" s="5"/>
-      <c r="H94" s="5"/>
-      <c r="I94" s="6"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="5"/>
       <c r="J94" s="5"/>
-      <c r="K94" s="4"/>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K94" s="6"/>
+      <c r="L94" s="5"/>
+      <c r="M94" s="4"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>94</v>
       </c>
@@ -3661,14 +4028,16 @@
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
-      <c r="F95" s="6"/>
+      <c r="F95" s="5"/>
       <c r="G95" s="5"/>
-      <c r="H95" s="5"/>
-      <c r="I95" s="6"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="5"/>
       <c r="J95" s="5"/>
-      <c r="K95" s="4"/>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K95" s="6"/>
+      <c r="L95" s="5"/>
+      <c r="M95" s="4"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <v>95</v>
       </c>
@@ -3676,14 +4045,16 @@
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
-      <c r="F96" s="6"/>
+      <c r="F96" s="5"/>
       <c r="G96" s="5"/>
-      <c r="H96" s="5"/>
-      <c r="I96" s="6"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="5"/>
       <c r="J96" s="5"/>
-      <c r="K96" s="4"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K96" s="6"/>
+      <c r="L96" s="5"/>
+      <c r="M96" s="4"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>96</v>
       </c>
@@ -3691,14 +4062,16 @@
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
-      <c r="F97" s="6"/>
+      <c r="F97" s="5"/>
       <c r="G97" s="5"/>
-      <c r="H97" s="5"/>
-      <c r="I97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="5"/>
       <c r="J97" s="5"/>
-      <c r="K97" s="4"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K97" s="6"/>
+      <c r="L97" s="5"/>
+      <c r="M97" s="4"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>97</v>
       </c>
@@ -3706,14 +4079,16 @@
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
-      <c r="F98" s="6"/>
+      <c r="F98" s="5"/>
       <c r="G98" s="5"/>
-      <c r="H98" s="5"/>
-      <c r="I98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="5"/>
       <c r="J98" s="5"/>
-      <c r="K98" s="4"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K98" s="6"/>
+      <c r="L98" s="5"/>
+      <c r="M98" s="4"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>98</v>
       </c>
@@ -3721,14 +4096,16 @@
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
-      <c r="F99" s="6"/>
+      <c r="F99" s="5"/>
       <c r="G99" s="5"/>
-      <c r="H99" s="5"/>
-      <c r="I99" s="6"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="5"/>
       <c r="J99" s="5"/>
-      <c r="K99" s="4"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K99" s="6"/>
+      <c r="L99" s="5"/>
+      <c r="M99" s="4"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>99</v>
       </c>
@@ -3736,14 +4113,16 @@
       <c r="C100" s="5"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
-      <c r="F100" s="6"/>
+      <c r="F100" s="5"/>
       <c r="G100" s="5"/>
-      <c r="H100" s="5"/>
-      <c r="I100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="5"/>
       <c r="J100" s="5"/>
-      <c r="K100" s="4"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K100" s="6"/>
+      <c r="L100" s="5"/>
+      <c r="M100" s="4"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>100</v>
       </c>
@@ -3751,14 +4130,16 @@
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
-      <c r="F101" s="6"/>
+      <c r="F101" s="5"/>
       <c r="G101" s="5"/>
-      <c r="H101" s="5"/>
-      <c r="I101" s="6"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="5"/>
       <c r="J101" s="5"/>
-      <c r="K101" s="4"/>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K101" s="6"/>
+      <c r="L101" s="5"/>
+      <c r="M101" s="4"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>101</v>
       </c>
@@ -3766,14 +4147,16 @@
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
-      <c r="F102" s="6"/>
+      <c r="F102" s="5"/>
       <c r="G102" s="5"/>
-      <c r="H102" s="5"/>
-      <c r="I102" s="6"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="5"/>
       <c r="J102" s="5"/>
-      <c r="K102" s="4"/>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K102" s="6"/>
+      <c r="L102" s="5"/>
+      <c r="M102" s="4"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>102</v>
       </c>
@@ -3781,14 +4164,16 @@
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
-      <c r="F103" s="6"/>
+      <c r="F103" s="5"/>
       <c r="G103" s="5"/>
-      <c r="H103" s="5"/>
-      <c r="I103" s="6"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="5"/>
       <c r="J103" s="5"/>
-      <c r="K103" s="4"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K103" s="6"/>
+      <c r="L103" s="5"/>
+      <c r="M103" s="4"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>103</v>
       </c>
@@ -3796,21 +4181,24 @@
       <c r="C104" s="5"/>
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
-      <c r="F104" s="6"/>
+      <c r="F104" s="5"/>
       <c r="G104" s="5"/>
-      <c r="H104" s="5"/>
-      <c r="I104" s="6"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="5"/>
       <c r="J104" s="5"/>
-      <c r="K104" s="4"/>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K104" s="6"/>
+      <c r="L104" s="5"/>
+      <c r="M104" s="4"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>104</v>
       </c>
-      <c r="E105"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J106" t="s">
+      <c r="B105" s="5"/>
+      <c r="G105"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L106" t="s">
         <v>44</v>
       </c>
     </row>

--- a/RegistrationsFile.xlsx
+++ b/RegistrationsFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E73B8E-27AE-4074-81A3-43133994E23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9F3B5D-360F-4C62-A776-46177A245C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="541" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="212">
   <si>
     <t>MODEL</t>
   </si>
@@ -598,6 +598,75 @@
   </si>
   <si>
     <t>25BH2180Q</t>
+  </si>
+  <si>
+    <t>RC GIVEN TO MANZOOR PAUL</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSG473446</t>
+  </si>
+  <si>
+    <t>MOHD SHABIR</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSK694682</t>
+  </si>
+  <si>
+    <t>PEER ALTAF AHMAD</t>
+  </si>
+  <si>
+    <t>JK25110771825932</t>
+  </si>
+  <si>
+    <t>JK25110741818372</t>
+  </si>
+  <si>
+    <t>FRONX DELTA+ 6AB AGS</t>
+  </si>
+  <si>
+    <t>ISHFAQ FARASH</t>
+  </si>
+  <si>
+    <t>AFAQ PARRAY</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSK694788</t>
+  </si>
+  <si>
+    <t>IMRAN AHMAD SHEIKH</t>
+  </si>
+  <si>
+    <t>JK25110751843656</t>
+  </si>
+  <si>
+    <t>BLUISH BLACK</t>
+  </si>
+  <si>
+    <t>PEARL ARCTIC WHITE</t>
+  </si>
+  <si>
+    <t>JK01BC5661</t>
+  </si>
+  <si>
+    <t>JK01BC5689</t>
+  </si>
+  <si>
+    <t>JK12D7530</t>
+  </si>
+  <si>
+    <t>JK01BC5609</t>
+  </si>
+  <si>
+    <t>JK04K3123</t>
+  </si>
+  <si>
+    <t>BASHARAT AHMAD WANI</t>
+  </si>
+  <si>
+    <t>MBHHWB13SSDA07910</t>
+  </si>
+  <si>
+    <t>RC GIVEN TO IRFAN</t>
   </si>
 </sst>
 </file>
@@ -1096,7 +1165,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1127,6 +1196,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1175,9 +1247,6 @@
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="15">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1263,6 +1332,9 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1357,14 +1429,14 @@
     <tableColumn id="2" xr3:uid="{6ABB4EDF-0F58-40D7-979C-D37D8D91A6BC}" name="CHASSIS" dataDxfId="10"/>
     <tableColumn id="3" xr3:uid="{285CC4F4-4CD1-4FFC-A101-ED051DA40438}" name="NAME" dataDxfId="9"/>
     <tableColumn id="4" xr3:uid="{28DC8B59-EFA0-4502-86B0-033B0B60D615}" name="MODEL" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{B25F5A6A-3B72-4772-B75C-D86670F35131}" name="Color" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{3D7EC305-A438-47DE-A91A-6CB0CF4B1937}" name="REG NUM" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{9942893D-0703-456F-8072-CD136C7B4052}" name="DATE OF REG" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{3AD2B0D9-D7A5-46E0-B596-F6B7F1CDDEA6}" name="DSE" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{475221AE-3FDC-4CED-B76C-4DA1DD4F8AD9}" name="RC RECEIVED BY" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{F594ED7D-6966-47AC-A5C3-25754B73A3CC}" name="DATE" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{452E3ECD-E927-4EC7-A8A2-4A866233750E}" name="FASTTAG" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{CFEE5573-D700-4B26-B382-BCA8210C54C2}" name="DATED" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{B25F5A6A-3B72-4772-B75C-D86670F35131}" name="Color" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{3D7EC305-A438-47DE-A91A-6CB0CF4B1937}" name="REG NUM" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{9942893D-0703-456F-8072-CD136C7B4052}" name="DATE OF REG" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{3AD2B0D9-D7A5-46E0-B596-F6B7F1CDDEA6}" name="DSE" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{475221AE-3FDC-4CED-B76C-4DA1DD4F8AD9}" name="RC RECEIVED BY" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{F594ED7D-6966-47AC-A5C3-25754B73A3CC}" name="DATE" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{452E3ECD-E927-4EC7-A8A2-4A866233750E}" name="FASTTAG" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{CFEE5573-D700-4B26-B382-BCA8210C54C2}" name="DATED" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1813,29 +1885,31 @@
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
-        <v>47</v>
+        <v>210</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>46</v>
+        <v>209</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="5"/>
+        <v>67</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>203</v>
+      </c>
       <c r="G3" s="5" t="s">
-        <v>45</v>
+        <v>208</v>
       </c>
       <c r="H3" s="6">
-        <v>45934</v>
+        <v>45930</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>49</v>
+        <v>211</v>
       </c>
       <c r="K3" s="6">
-        <v>45962</v>
+        <v>45968</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="4"/>
@@ -1846,29 +1920,29 @@
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="H4" s="6">
-        <v>45937</v>
+        <v>45934</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="K4" s="6">
-        <v>45965</v>
+        <v>45962</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="4"/>
@@ -1879,26 +1953,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H5" s="6">
-        <v>45938</v>
+        <v>45937</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K5" s="6">
         <v>45965</v>
@@ -1912,36 +1986,32 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="H6" s="6">
-        <v>45941</v>
+        <v>45938</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="K6" s="6">
-        <v>45962</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" s="4">
-        <v>45973</v>
-      </c>
+        <v>45965</v>
+      </c>
+      <c r="L6" s="5"/>
+      <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
@@ -1949,31 +2019,35 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="H7" s="6">
         <v>45941</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="6">
+        <v>45962</v>
+      </c>
       <c r="L7" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M7" s="4">
-        <v>45962</v>
+        <v>45973</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -1982,32 +2056,32 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="H8" s="6">
-        <v>45944</v>
+        <v>45941</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="K8" s="6">
-        <v>45966</v>
-      </c>
-      <c r="L8" s="5"/>
-      <c r="M8" s="4"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
@@ -2015,29 +2089,29 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="H9" s="6">
-        <v>45946</v>
+        <v>45944</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="K9" s="6">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="4"/>
@@ -2048,29 +2122,29 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="s">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="H10" s="6">
-        <v>45948</v>
+        <v>45946</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="K10" s="6">
-        <v>45966</v>
+        <v>45964</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="4"/>
@@ -2081,27 +2155,29 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="H11" s="6">
-        <v>45953</v>
-      </c>
-      <c r="I11" s="5"/>
+        <v>45948</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="J11" s="5" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="K11" s="6">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="4"/>
@@ -2112,29 +2188,27 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="H12" s="6">
         <v>45953</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="K12" s="6">
-        <v>45965</v>
+        <v>45964</v>
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="4"/>
@@ -2145,29 +2219,29 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="H13" s="6">
         <v>45953</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K13" s="6">
-        <v>45966</v>
+        <v>45965</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="4"/>
@@ -2178,26 +2252,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H14" s="6">
-        <v>45954</v>
+        <v>45953</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>127</v>
+        <v>14</v>
       </c>
       <c r="K14" s="6">
         <v>45966</v>
@@ -2211,26 +2285,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="H15" s="6">
         <v>45954</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="K15" s="6">
         <v>45966</v>
@@ -2244,29 +2318,29 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="H16" s="6">
-        <v>45958</v>
+        <v>45954</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="K16" s="6">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="4"/>
@@ -2277,36 +2351,32 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="H17" s="6">
-        <v>45959</v>
+        <v>45958</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="K17" s="6">
-        <v>45962</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M17" s="4">
-        <v>45959</v>
-      </c>
+        <v>45965</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17" s="4"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
@@ -2314,35 +2384,35 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="H18" s="6">
-        <v>45960</v>
+        <v>45959</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="K18" s="6">
-        <v>45961</v>
+        <v>45962</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M18" s="4">
-        <v>45960</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -2351,36 +2421,30 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5" t="s">
-        <v>73</v>
+        <v>186</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="5"/>
+      <c r="F19" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="G19" s="5" t="s">
-        <v>72</v>
+        <v>188</v>
       </c>
       <c r="H19" s="6">
-        <v>45960</v>
+        <v>45959</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="K19" s="6">
-        <v>45964</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M19" s="4">
-        <v>45960</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="J19" s="5"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="4"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
@@ -2388,32 +2452,36 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="H20" s="6">
         <v>45960</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K20" s="6">
-        <v>45965</v>
-      </c>
-      <c r="L20" s="5"/>
-      <c r="M20" s="4"/>
+        <v>45961</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" s="4">
+        <v>45960</v>
+      </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
@@ -2421,26 +2489,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="H21" s="6">
-        <v>45961</v>
+        <v>45960</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K21" s="6">
         <v>45964</v>
@@ -2449,7 +2517,7 @@
         <v>23</v>
       </c>
       <c r="M21" s="4">
-        <v>45961</v>
+        <v>45960</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -2458,32 +2526,32 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="H22" s="6">
-        <v>45961</v>
+        <v>45960</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="5"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M22" s="4">
-        <v>45961</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" s="6">
+        <v>45965</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" s="4"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
@@ -2491,31 +2559,35 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="H23" s="6">
         <v>45961</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="5"/>
-      <c r="K23" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="K23" s="6">
+        <v>45964</v>
+      </c>
       <c r="L23" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M23" s="4">
-        <v>45962</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -2524,23 +2596,23 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="H24" s="6">
         <v>45961</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="6"/>
@@ -2557,17 +2629,17 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="H25" s="6">
         <v>45961</v>
@@ -2575,14 +2647,14 @@
       <c r="I25" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" s="6">
-        <v>45966</v>
-      </c>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
@@ -2590,32 +2662,32 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
-        <v>144</v>
+        <v>68</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>146</v>
+        <v>67</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5" t="s">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="H26" s="6">
         <v>45961</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K26" s="6">
-        <v>45966</v>
-      </c>
-      <c r="L26" s="5"/>
-      <c r="M26" s="4"/>
+        <v>70</v>
+      </c>
+      <c r="J26" s="5"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="4">
+        <v>45961</v>
+      </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
@@ -2623,36 +2695,32 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H27" s="6">
-        <v>45962</v>
+        <v>45961</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="K27" s="6">
-        <v>45964</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M27" s="4">
-        <v>45962</v>
-      </c>
+        <v>45966</v>
+      </c>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
@@ -2660,32 +2728,32 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5" t="s">
-        <v>41</v>
+        <v>144</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>42</v>
+        <v>145</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5" t="s">
-        <v>62</v>
+        <v>147</v>
       </c>
       <c r="H28" s="6">
-        <v>45962</v>
+        <v>45961</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J28" s="5"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M28" s="4">
-        <v>45962</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" s="6">
+        <v>45966</v>
+      </c>
+      <c r="L28" s="5"/>
+      <c r="M28" s="4"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
@@ -2693,29 +2761,29 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="H29" s="6">
         <v>45962</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="K29" s="6">
-        <v>45962</v>
+        <v>45964</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>23</v>
@@ -2730,17 +2798,17 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="H30" s="6">
         <v>45962</v>
@@ -2748,12 +2816,8 @@
       <c r="I30" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J30" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K30" s="6">
-        <v>45962</v>
-      </c>
+      <c r="J30" s="5"/>
+      <c r="K30" s="6"/>
       <c r="L30" s="5" t="s">
         <v>23</v>
       </c>
@@ -2767,28 +2831,36 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="H31" s="6">
-        <v>45965</v>
+        <v>45962</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J31" s="5"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="6">
+        <v>45962</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
@@ -2796,32 +2868,36 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="H32" s="6">
-        <v>45965</v>
+        <v>45962</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>162</v>
+        <v>43</v>
       </c>
       <c r="K32" s="6">
-        <v>45967</v>
-      </c>
-      <c r="L32" s="5"/>
-      <c r="M32" s="4"/>
+        <v>45962</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
@@ -2829,17 +2905,17 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H33" s="6">
         <v>45965</v>
@@ -2858,25 +2934,32 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="H34" s="6">
-        <v>45966</v>
+        <v>45965</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="K34" s="6"/>
+        <v>107</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="K34" s="6">
+        <v>45967</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="4"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
@@ -2884,30 +2967,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="H35" s="6">
-        <v>45966</v>
+        <v>45965</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="K35" s="6">
-        <v>45966</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="J35" s="5"/>
+      <c r="K35" s="6"/>
       <c r="L35" s="5"/>
       <c r="M35" s="4"/>
     </row>
@@ -2917,59 +2996,56 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="H36" s="6">
         <v>45966</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="J36" s="5"/>
+        <v>139</v>
+      </c>
       <c r="K36" s="6"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="4"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>36</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>180</v>
-      </c>
+      <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>177</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="F37" s="5"/>
       <c r="G37" s="5" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="H37" s="6">
         <v>45966</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J37" s="5"/>
-      <c r="K37" s="6"/>
+        <v>142</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="K37" s="6">
+        <v>45966</v>
+      </c>
       <c r="L37" s="5"/>
       <c r="M37" s="4"/>
     </row>
@@ -2977,29 +3053,25 @@
       <c r="A38" s="5">
         <v>37</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>169</v>
-      </c>
+      <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>178</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="F38" s="5"/>
       <c r="G38" s="5" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="H38" s="6">
-        <v>45967</v>
+        <v>45966</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="6"/>
@@ -3011,28 +3083,28 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="H39" s="6">
-        <v>45967</v>
+        <v>45966</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="6"/>
@@ -3044,28 +3116,28 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="H40" s="6">
         <v>45967</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="6"/>
@@ -3077,26 +3149,28 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G41" s="5"/>
+        <v>178</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>172</v>
+      </c>
       <c r="H41" s="6">
         <v>45967</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="6"/>
@@ -3107,30 +3181,36 @@
       <c r="A42" s="5">
         <v>41</v>
       </c>
-      <c r="B42" s="5"/>
+      <c r="B42" s="5" t="s">
+        <v>173</v>
+      </c>
       <c r="C42" s="5" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="H42" s="6">
-        <v>45959</v>
+        <v>45967</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="J42" s="5"/>
-      <c r="K42" s="6"/>
+        <v>75</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="K42" s="6">
+        <v>45968</v>
+      </c>
       <c r="L42" s="5"/>
       <c r="M42" s="4"/>
     </row>
@@ -3138,14 +3218,30 @@
       <c r="A43" s="5">
         <v>42</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="5"/>
+      <c r="B43" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H43" s="6">
+        <v>45967</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>179</v>
+      </c>
       <c r="J43" s="5"/>
       <c r="K43" s="6"/>
       <c r="L43" s="5"/>
@@ -3155,16 +3251,30 @@
       <c r="A44" s="5">
         <v>43</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
+      <c r="B44" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="D44" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="5"/>
+        <v>191</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="H44" s="6">
+        <v>45968</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>198</v>
+      </c>
       <c r="J44" s="5"/>
       <c r="K44" s="6"/>
       <c r="L44" s="5"/>
@@ -3174,14 +3284,30 @@
       <c r="A45" s="5">
         <v>44</v>
       </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="5"/>
+      <c r="B45" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H45" s="6">
+        <v>45968</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>197</v>
+      </c>
       <c r="J45" s="5"/>
       <c r="K45" s="6"/>
       <c r="L45" s="5"/>
@@ -3191,14 +3317,30 @@
       <c r="A46" s="5">
         <v>45</v>
       </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="5"/>
+      <c r="B46" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="H46" s="6">
+        <v>45968</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="J46" s="5"/>
       <c r="K46" s="6"/>
       <c r="L46" s="5"/>

--- a/RegistrationsFile.xlsx
+++ b/RegistrationsFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9F3B5D-360F-4C62-A776-46177A245C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E625FC1E-028D-4703-BFB1-522A899B0114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="541" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="226">
   <si>
     <t>MODEL</t>
   </si>
@@ -667,6 +667,48 @@
   </si>
   <si>
     <t>RC GIVEN TO IRFAN</t>
+  </si>
+  <si>
+    <t>JK25110721979186</t>
+  </si>
+  <si>
+    <t>MBHKWD43SSJ655894</t>
+  </si>
+  <si>
+    <t>MALIHA JAVAID</t>
+  </si>
+  <si>
+    <t>FRONX TURBO S. HYBRID ALPHA</t>
+  </si>
+  <si>
+    <t>JK25110842033445</t>
+  </si>
+  <si>
+    <t>JK25110822035459</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSK479203</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSJ476736</t>
+  </si>
+  <si>
+    <t>NUSRAT JABEEN</t>
+  </si>
+  <si>
+    <t>GHULAM QUDIR MIR</t>
+  </si>
+  <si>
+    <t>RIYAZ WANI / SHAFI</t>
+  </si>
+  <si>
+    <t>MUDASIR WANI / HILAL PADDAR</t>
+  </si>
+  <si>
+    <t>SILKY SILVER</t>
+  </si>
+  <si>
+    <t>RTO</t>
   </si>
 </sst>
 </file>
@@ -1165,7 +1207,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1198,9 +1240,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1246,7 +1292,26 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="16">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1335,21 +1400,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <strike val="0"/>
@@ -1418,25 +1468,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97E63F84-BDFB-4C38-B1FD-28318E0D1D3F}" name="Table13" displayName="Table13" ref="A1:M105" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
-  <autoFilter ref="A1:M105" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M105">
-    <sortCondition ref="H1:H105"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97E63F84-BDFB-4C38-B1FD-28318E0D1D3F}" name="Table13" displayName="Table13" ref="A1:N105" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:N105" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N105">
+    <sortCondition ref="I1:I105"/>
   </sortState>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{DEBB3640-E433-4779-93BC-95B8FB492623}" name="S.NO" dataDxfId="12"/>
-    <tableColumn id="13" xr3:uid="{86C56767-9BFE-4154-9FC1-CEA7C183815E}" name="Application No." dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{6ABB4EDF-0F58-40D7-979C-D37D8D91A6BC}" name="CHASSIS" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{285CC4F4-4CD1-4FFC-A101-ED051DA40438}" name="NAME" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{28DC8B59-EFA0-4502-86B0-033B0B60D615}" name="MODEL" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{B25F5A6A-3B72-4772-B75C-D86670F35131}" name="Color" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{3D7EC305-A438-47DE-A91A-6CB0CF4B1937}" name="REG NUM" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{9942893D-0703-456F-8072-CD136C7B4052}" name="DATE OF REG" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{3AD2B0D9-D7A5-46E0-B596-F6B7F1CDDEA6}" name="DSE" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{475221AE-3FDC-4CED-B76C-4DA1DD4F8AD9}" name="RC RECEIVED BY" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{F594ED7D-6966-47AC-A5C3-25754B73A3CC}" name="DATE" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{452E3ECD-E927-4EC7-A8A2-4A866233750E}" name="FASTTAG" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{CFEE5573-D700-4B26-B382-BCA8210C54C2}" name="DATED" dataDxfId="0"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{DEBB3640-E433-4779-93BC-95B8FB492623}" name="S.NO" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{86C56767-9BFE-4154-9FC1-CEA7C183815E}" name="Application No." dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{6ABB4EDF-0F58-40D7-979C-D37D8D91A6BC}" name="CHASSIS" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{285CC4F4-4CD1-4FFC-A101-ED051DA40438}" name="NAME" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{28DC8B59-EFA0-4502-86B0-033B0B60D615}" name="MODEL" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{B25F5A6A-3B72-4772-B75C-D86670F35131}" name="Color" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{22F5E9AE-FC4E-4EBD-ADBF-5C93F85B331F}" name="RTO" dataDxfId="0">
+      <calculatedColumnFormula>IF(LEFT(H2,4)="JK13","PULWAMA",IF(LEFT(H2,4)="JK01","SRINAGAR",IF(LEFT(H2,4)="JK04","BUDGAM",IF(LEFT(H2,4)="JK03","ANANTNAG",IF(LEFT(H2,4)="JK05","BARAMULLA",IF(LEFT(H2,4)="25BH","BHARAT",IF(LEFT(H2,4)="JK12","POONCH",IF(LEFT(H2,4)="JK18","KULGAM",IF(LEFT(H2,4)="JK22","SHOPIAN",IF(LEFT(H2,4)="T102","TEMP",IF(LEFT(H2,4)="","NEW","NA")))))))))))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{3D7EC305-A438-47DE-A91A-6CB0CF4B1937}" name="REG NUM" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{9942893D-0703-456F-8072-CD136C7B4052}" name="DATE OF REG" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{3AD2B0D9-D7A5-46E0-B596-F6B7F1CDDEA6}" name="DSE" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{475221AE-3FDC-4CED-B76C-4DA1DD4F8AD9}" name="RC RECEIVED BY" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{F594ED7D-6966-47AC-A5C3-25754B73A3CC}" name="DATE" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{452E3ECD-E927-4EC7-A8A2-4A866233750E}" name="FASTTAG" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{CFEE5573-D700-4B26-B382-BCA8210C54C2}" name="DATED" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1789,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE94C64E-9B39-47CE-ACCD-DD5031A70035}">
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:N106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
@@ -1798,16 +1851,17 @@
     <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32.85546875" customWidth="1"/>
     <col min="6" max="6" width="30.140625" customWidth="1"/>
-    <col min="7" max="7" width="19" style="12" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="22.28515625" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="30.140625" style="16" customWidth="1"/>
+    <col min="8" max="8" width="19" style="12" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="30" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="22.28515625" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>9</v>
       </c>
@@ -1826,29 +1880,32 @@
       <c r="F1" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="H1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="N1" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1863,23 +1920,27 @@
         <v>101</v>
       </c>
       <c r="F2" s="5"/>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="15" t="str">
+        <f>IF(LEFT(H2,4)="JK13","PULWAMA",IF(LEFT(H2,4)="JK01","SRINAGAR",IF(LEFT(H2,4)="JK04","BUDGAM",IF(LEFT(H2,4)="JK03","ANANTNAG",IF(LEFT(H2,4)="JK05","BARAMULLA",IF(LEFT(H2,4)="25BH","BHARAT",IF(LEFT(H2,4)="JK12","POONCH",IF(LEFT(H2,4)="JK18","KULGAM",IF(LEFT(H2,4)="JK22","SHOPIAN",IF(LEFT(H2,4)="T102","TEMP",IF(LEFT(H2,4)="","NEW","NA")))))))))))</f>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="6">
+      <c r="I2" s="6">
         <v>45927</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="K2" s="6">
+      <c r="L2" s="6">
         <v>45965</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="4"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M2" s="5"/>
+      <c r="N2" s="4"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1896,25 +1957,29 @@
       <c r="F3" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="15" t="str">
+        <f t="shared" ref="G3:G49" si="0">IF(LEFT(H3,4)="JK13","PULWAMA",IF(LEFT(H3,4)="JK01","SRINAGAR",IF(LEFT(H3,4)="JK04","BUDGAM",IF(LEFT(H3,4)="JK03","ANANTNAG",IF(LEFT(H3,4)="JK05","BARAMULLA",IF(LEFT(H3,4)="25BH","BHARAT",IF(LEFT(H3,4)="JK12","POONCH",IF(LEFT(H3,4)="JK18","KULGAM",IF(LEFT(H3,4)="JK22","SHOPIAN",IF(LEFT(H3,4)="T102","TEMP",IF(LEFT(H3,4)="","NEW","NA")))))))))))</f>
+        <v>BUDGAM</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="H3" s="6">
+      <c r="I3" s="6">
         <v>45930</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="K3" s="6">
+      <c r="L3" s="6">
         <v>45968</v>
       </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M3" s="5"/>
+      <c r="N3" s="4"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1929,25 +1994,29 @@
         <v>12</v>
       </c>
       <c r="F4" s="5"/>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>BUDGAM</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="6">
+      <c r="I4" s="6">
         <v>45934</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="6">
+      <c r="L4" s="6">
         <v>45962</v>
       </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M4" s="5"/>
+      <c r="N4" s="4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1962,25 +2031,29 @@
         <v>31</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>BUDGAM</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H5" s="6">
+      <c r="I5" s="6">
         <v>45937</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="K5" s="6">
+      <c r="L5" s="6">
         <v>45965</v>
       </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M5" s="5"/>
+      <c r="N5" s="4"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1995,25 +2068,29 @@
         <v>31</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="6">
+      <c r="I6" s="6">
         <v>45938</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="K6" s="6">
+      <c r="L6" s="6">
         <v>45965</v>
       </c>
-      <c r="L6" s="5"/>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M6" s="5"/>
+      <c r="N6" s="4"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -2028,29 +2105,33 @@
         <v>5</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="6">
+      <c r="I7" s="6">
         <v>45941</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="6">
         <v>45962</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="M7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M7" s="4">
+      <c r="N7" s="4">
         <v>45973</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -2065,25 +2146,29 @@
         <v>31</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="6">
+      <c r="I8" s="6">
         <v>45941</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="5" t="s">
+      <c r="K8" s="5"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="4">
+      <c r="N8" s="4">
         <v>45962</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -2098,25 +2183,29 @@
         <v>126</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="H9" s="6">
+      <c r="I9" s="6">
         <v>45944</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="J9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="K9" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="K9" s="6">
+      <c r="L9" s="6">
         <v>45966</v>
       </c>
-      <c r="L9" s="5"/>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M9" s="5"/>
+      <c r="N9" s="4"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -2131,25 +2220,29 @@
         <v>5</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H10" s="6">
+      <c r="I10" s="6">
         <v>45946</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="J10" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="K10" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="K10" s="6">
+      <c r="L10" s="6">
         <v>45964</v>
       </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="4"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M10" s="5"/>
+      <c r="N10" s="4"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -2164,25 +2257,29 @@
         <v>150</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SHOPIAN</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="H11" s="6">
+      <c r="I11" s="6">
         <v>45948</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>14</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="6">
         <v>45966</v>
       </c>
-      <c r="L11" s="5"/>
-      <c r="M11" s="4"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M11" s="5"/>
+      <c r="N11" s="4"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -2197,23 +2294,27 @@
         <v>12</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H12" s="6">
+      <c r="I12" s="6">
         <v>45953</v>
       </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="5"/>
+      <c r="K12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K12" s="6">
+      <c r="L12" s="6">
         <v>45964</v>
       </c>
-      <c r="L12" s="5"/>
-      <c r="M12" s="4"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M12" s="5"/>
+      <c r="N12" s="4"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -2228,25 +2329,29 @@
         <v>12</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="H13" s="6">
+      <c r="I13" s="6">
         <v>45953</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="6">
         <v>45965</v>
       </c>
-      <c r="L13" s="5"/>
-      <c r="M13" s="4"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M13" s="5"/>
+      <c r="N13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -2261,25 +2366,29 @@
         <v>5</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>ANANTNAG</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="H14" s="6">
+      <c r="I14" s="6">
         <v>45953</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>14</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L14" s="6">
         <v>45966</v>
       </c>
-      <c r="L14" s="5"/>
-      <c r="M14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M14" s="5"/>
+      <c r="N14" s="4"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -2294,25 +2403,29 @@
         <v>5</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H15" s="6">
+      <c r="I15" s="6">
         <v>45954</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="J15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="K15" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="K15" s="6">
+      <c r="L15" s="6">
         <v>45966</v>
       </c>
-      <c r="L15" s="5"/>
-      <c r="M15" s="4"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M15" s="5"/>
+      <c r="N15" s="4"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -2327,25 +2440,29 @@
         <v>31</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="H16" s="6">
+      <c r="I16" s="6">
         <v>45954</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="J16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="K16" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="K16" s="6">
+      <c r="L16" s="6">
         <v>45966</v>
       </c>
-      <c r="L16" s="5"/>
-      <c r="M16" s="4"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M16" s="5"/>
+      <c r="N16" s="4"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -2360,25 +2477,29 @@
         <v>5</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H17" s="6">
+      <c r="I17" s="6">
         <v>45958</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="J17" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="K17" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="K17" s="6">
+      <c r="L17" s="6">
         <v>45965</v>
       </c>
-      <c r="L17" s="5"/>
-      <c r="M17" s="4"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M17" s="5"/>
+      <c r="N17" s="4"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -2393,29 +2514,33 @@
         <v>12</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H18" s="6">
+      <c r="I18" s="6">
         <v>45959</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L18" s="6">
         <v>45962</v>
       </c>
-      <c r="L18" s="5" t="s">
+      <c r="M18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M18" s="4">
+      <c r="N18" s="4">
         <v>45959</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -2432,21 +2557,25 @@
       <c r="F19" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>BHARAT</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="H19" s="6">
+      <c r="I19" s="6">
         <v>45959</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="J19" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="J19" s="5"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="4"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K19" s="5"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="4"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -2461,29 +2590,33 @@
         <v>5</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H20" s="6">
+      <c r="I20" s="6">
         <v>45960</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" s="6">
         <v>45961</v>
       </c>
-      <c r="L20" s="5" t="s">
+      <c r="M20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M20" s="4">
+      <c r="N20" s="4">
         <v>45960</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -2498,29 +2631,33 @@
         <v>12</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>BUDGAM</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H21" s="6">
+      <c r="I21" s="6">
         <v>45960</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="J21" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="K21" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="K21" s="6">
+      <c r="L21" s="6">
         <v>45964</v>
       </c>
-      <c r="L21" s="5" t="s">
+      <c r="M21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M21" s="4">
+      <c r="N21" s="4">
         <v>45960</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -2535,25 +2672,29 @@
         <v>120</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="H22" s="6">
+      <c r="I22" s="6">
         <v>45960</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" s="6">
         <v>45965</v>
       </c>
-      <c r="L22" s="5"/>
-      <c r="M22" s="4"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M22" s="5"/>
+      <c r="N22" s="4"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -2568,29 +2709,33 @@
         <v>5</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>ANANTNAG</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H23" s="6">
+      <c r="I23" s="6">
         <v>45961</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="J23" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="K23" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="K23" s="6">
+      <c r="L23" s="6">
         <v>45964</v>
       </c>
-      <c r="L23" s="5" t="s">
+      <c r="M23" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M23" s="4">
+      <c r="N23" s="4">
         <v>45961</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -2605,25 +2750,29 @@
         <v>12</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>ANANTNAG</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H24" s="6">
+      <c r="I24" s="6">
         <v>45961</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="J24" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J24" s="5"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="5" t="s">
+      <c r="K24" s="5"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M24" s="4">
+      <c r="N24" s="4">
         <v>45961</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -2638,25 +2787,29 @@
         <v>31</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>KULGAM</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="H25" s="6">
+      <c r="I25" s="6">
         <v>45961</v>
       </c>
-      <c r="I25" s="5" t="s">
+      <c r="J25" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J25" s="5"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="5" t="s">
+      <c r="K25" s="5"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M25" s="4">
+      <c r="N25" s="4">
         <v>45962</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -2671,25 +2824,29 @@
         <v>67</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="H26" s="6">
+      <c r="I26" s="6">
         <v>45961</v>
       </c>
-      <c r="I26" s="5" t="s">
+      <c r="J26" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="5" t="s">
+      <c r="K26" s="5"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M26" s="4">
+      <c r="N26" s="4">
         <v>45961</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -2704,25 +2861,29 @@
         <v>37</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>ANANTNAG</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H27" s="6">
+      <c r="I27" s="6">
         <v>45961</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>14</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L27" s="6">
         <v>45966</v>
       </c>
-      <c r="L27" s="6"/>
       <c r="M27" s="6"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -2737,25 +2898,29 @@
         <v>146</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>BHARAT</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="H28" s="6">
+      <c r="I28" s="6">
         <v>45961</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" s="6">
         <v>45966</v>
       </c>
-      <c r="L28" s="5"/>
-      <c r="M28" s="4"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M28" s="5"/>
+      <c r="N28" s="4"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -2770,29 +2935,33 @@
         <v>31</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H29" s="6">
+      <c r="I29" s="6">
         <v>45962</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L29" s="6">
         <v>45964</v>
       </c>
-      <c r="L29" s="5" t="s">
+      <c r="M29" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M29" s="4">
+      <c r="N29" s="4">
         <v>45962</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -2807,25 +2976,29 @@
         <v>31</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H30" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H30" s="6">
+      <c r="I30" s="6">
         <v>45962</v>
       </c>
-      <c r="I30" s="5" t="s">
+      <c r="J30" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J30" s="5"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="5" t="s">
+      <c r="K30" s="5"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M30" s="4">
+      <c r="N30" s="4">
         <v>45962</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -2840,29 +3013,33 @@
         <v>51</v>
       </c>
       <c r="F31" s="5"/>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>TEMP</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H31" s="6">
+      <c r="I31" s="6">
         <v>45962</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="6">
         <v>45962</v>
       </c>
-      <c r="L31" s="5" t="s">
+      <c r="M31" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M31" s="4">
+      <c r="N31" s="4">
         <v>45962</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -2877,29 +3054,33 @@
         <v>57</v>
       </c>
       <c r="F32" s="5"/>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>BARAMULLA</v>
+      </c>
+      <c r="H32" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H32" s="6">
+      <c r="I32" s="6">
         <v>45962</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>43</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L32" s="6">
         <v>45962</v>
       </c>
-      <c r="L32" s="5" t="s">
+      <c r="M32" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M32" s="4">
+      <c r="N32" s="4">
         <v>45962</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -2914,21 +3095,25 @@
         <v>101</v>
       </c>
       <c r="F33" s="5"/>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H33" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="H33" s="6">
+      <c r="I33" s="6">
         <v>45965</v>
       </c>
-      <c r="I33" s="5" t="s">
+      <c r="J33" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J33" s="13"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="4"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K33" s="13"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="4"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -2943,25 +3128,29 @@
         <v>102</v>
       </c>
       <c r="F34" s="5"/>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H34" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="H34" s="6">
+      <c r="I34" s="6">
         <v>45965</v>
       </c>
-      <c r="I34" s="5" t="s">
+      <c r="J34" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="J34" s="14" t="s">
+      <c r="K34" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="K34" s="6">
+      <c r="L34" s="6">
         <v>45967</v>
       </c>
-      <c r="L34" s="5"/>
-      <c r="M34" s="4"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M34" s="5"/>
+      <c r="N34" s="4"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -2976,21 +3165,25 @@
         <v>103</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="G35" s="5" t="s">
+      <c r="G35" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="H35" s="6">
+      <c r="I35" s="6">
         <v>45965</v>
       </c>
-      <c r="I35" s="5" t="s">
+      <c r="J35" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J35" s="5"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="4"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K35" s="5"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="4"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -3005,18 +3198,22 @@
         <v>12</v>
       </c>
       <c r="F36" s="5"/>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>KULGAM</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="H36" s="6">
+      <c r="I36" s="6">
         <v>45966</v>
       </c>
-      <c r="I36" s="5" t="s">
+      <c r="J36" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="K36" s="6"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L36" s="6"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -3031,25 +3228,29 @@
         <v>31</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>BUDGAM</v>
+      </c>
+      <c r="H37" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="H37" s="6">
+      <c r="I37" s="6">
         <v>45966</v>
       </c>
-      <c r="I37" s="5" t="s">
+      <c r="J37" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="K37" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="K37" s="6">
+      <c r="L37" s="6">
         <v>45966</v>
       </c>
-      <c r="L37" s="5"/>
-      <c r="M37" s="4"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M37" s="5"/>
+      <c r="N37" s="4"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -3064,21 +3265,25 @@
         <v>101</v>
       </c>
       <c r="F38" s="5"/>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>BUDGAM</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="H38" s="6">
+      <c r="I38" s="6">
         <v>45966</v>
       </c>
-      <c r="I38" s="5" t="s">
+      <c r="J38" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="J38" s="5"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="4"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K38" s="5"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="4"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -3097,21 +3302,25 @@
       <c r="F39" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H39" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="H39" s="6">
+      <c r="I39" s="6">
         <v>45966</v>
       </c>
-      <c r="I39" s="5" t="s">
+      <c r="J39" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="5"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="4"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K39" s="5"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="4"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -3130,21 +3339,25 @@
       <c r="F40" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H40" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H40" s="6">
+      <c r="I40" s="6">
         <v>45967</v>
       </c>
-      <c r="I40" s="5" t="s">
+      <c r="J40" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="J40" s="5"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="4"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K40" s="5"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="4"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -3163,21 +3376,25 @@
       <c r="F41" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G41" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H41" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="H41" s="6">
+      <c r="I41" s="6">
         <v>45967</v>
       </c>
-      <c r="I41" s="5" t="s">
+      <c r="J41" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="J41" s="5"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="4"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K41" s="5"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="4"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -3196,25 +3413,29 @@
       <c r="F42" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H42" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="H42" s="6">
+      <c r="I42" s="6">
         <v>45967</v>
       </c>
-      <c r="I42" s="5" t="s">
+      <c r="J42" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="J42" s="5" t="s">
+      <c r="K42" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="K42" s="6">
+      <c r="L42" s="6">
         <v>45968</v>
       </c>
-      <c r="L42" s="5"/>
-      <c r="M42" s="4"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M42" s="5"/>
+      <c r="N42" s="4"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -3233,21 +3454,25 @@
       <c r="F43" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="G43" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H43" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="H43" s="6">
+      <c r="I43" s="6">
         <v>45967</v>
       </c>
-      <c r="I43" s="5" t="s">
+      <c r="J43" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="J43" s="5"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="4"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K43" s="5"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="4"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -3266,21 +3491,25 @@
       <c r="F44" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>POONCH</v>
+      </c>
+      <c r="H44" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="H44" s="6">
+      <c r="I44" s="6">
         <v>45968</v>
       </c>
-      <c r="I44" s="5" t="s">
+      <c r="J44" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="J44" s="5"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="4"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K44" s="5"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="4"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -3299,21 +3528,25 @@
       <c r="F45" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="G45" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H45" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="H45" s="6">
+      <c r="I45" s="6">
         <v>45968</v>
       </c>
-      <c r="I45" s="5" t="s">
+      <c r="J45" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="J45" s="5"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="5"/>
-      <c r="M45" s="4"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K45" s="5"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="4"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -3332,89 +3565,144 @@
       <c r="F46" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H46" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="H46" s="6">
+      <c r="I46" s="6">
         <v>45968</v>
       </c>
-      <c r="I46" s="5" t="s">
+      <c r="J46" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="J46" s="5"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="4"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K46" s="5"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="4"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>46</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="5"/>
+      <c r="B47" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G47" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>NEW</v>
+      </c>
+      <c r="H47" s="5"/>
+      <c r="I47" s="6">
+        <v>45968</v>
+      </c>
       <c r="J47" s="5"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="4"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K47" s="5"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="4"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>47</v>
       </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="5"/>
-      <c r="M48" s="4"/>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B48" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="G48" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>NEW</v>
+      </c>
+      <c r="H48" s="5"/>
+      <c r="I48" s="6">
+        <v>45969</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="K48" s="5"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="4"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>48</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="5"/>
-      <c r="M49" s="4"/>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B49" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G49" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>NEW</v>
+      </c>
+      <c r="H49" s="5"/>
+      <c r="I49" s="6">
+        <v>45969</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="K49" s="5"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="4"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>49</v>
       </c>
       <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
       <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
       <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="5"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="6"/>
       <c r="J50" s="5"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="4"/>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K50" s="5"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="4"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -3423,15 +3711,16 @@
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="5"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="6"/>
       <c r="J51" s="5"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="4"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K51" s="5"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="4"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -3440,15 +3729,16 @@
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="5"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="6"/>
       <c r="J52" s="5"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="4"/>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K52" s="5"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="4"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -3457,15 +3747,16 @@
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="5"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="6"/>
       <c r="J53" s="5"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="5"/>
-      <c r="M53" s="4"/>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K53" s="5"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="4"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -3474,15 +3765,16 @@
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="5"/>
+      <c r="G54" s="15"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="6"/>
       <c r="J54" s="5"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="4"/>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K54" s="5"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="4"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -3491,15 +3783,16 @@
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="5"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="6"/>
       <c r="J55" s="5"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="5"/>
-      <c r="M55" s="4"/>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K55" s="5"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="4"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -3508,15 +3801,16 @@
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="5"/>
+      <c r="G56" s="15"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="6"/>
       <c r="J56" s="5"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="5"/>
-      <c r="M56" s="4"/>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K56" s="5"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="4"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -3525,15 +3819,16 @@
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="5"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="6"/>
       <c r="J57" s="5"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="5"/>
-      <c r="M57" s="4"/>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K57" s="5"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="4"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -3542,15 +3837,16 @@
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="5"/>
+      <c r="G58" s="15"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="6"/>
       <c r="J58" s="5"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="5"/>
-      <c r="M58" s="4"/>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K58" s="5"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="4"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -3559,15 +3855,16 @@
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="5"/>
+      <c r="G59" s="15"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="6"/>
       <c r="J59" s="5"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="5"/>
-      <c r="M59" s="4"/>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K59" s="5"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="4"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -3576,15 +3873,16 @@
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="5"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="6"/>
       <c r="J60" s="5"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="5"/>
-      <c r="M60" s="4"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K60" s="5"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="4"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -3593,15 +3891,16 @@
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="5"/>
+      <c r="G61" s="15"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="6"/>
       <c r="J61" s="5"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="5"/>
-      <c r="M61" s="4"/>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K61" s="5"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="4"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -3610,15 +3909,16 @@
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="5"/>
+      <c r="G62" s="15"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="6"/>
       <c r="J62" s="5"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="5"/>
-      <c r="M62" s="4"/>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K62" s="5"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="4"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -3627,15 +3927,16 @@
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="5"/>
+      <c r="G63" s="15"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="6"/>
       <c r="J63" s="5"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="5"/>
-      <c r="M63" s="4"/>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K63" s="5"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="4"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -3644,15 +3945,16 @@
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="5"/>
+      <c r="G64" s="15"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="6"/>
       <c r="J64" s="5"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="5"/>
-      <c r="M64" s="4"/>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K64" s="5"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="4"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -3661,15 +3963,16 @@
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="5"/>
+      <c r="G65" s="15"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="6"/>
       <c r="J65" s="5"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="5"/>
-      <c r="M65" s="4"/>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K65" s="5"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="4"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -3678,15 +3981,16 @@
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="5"/>
+      <c r="G66" s="15"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="6"/>
       <c r="J66" s="5"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="5"/>
-      <c r="M66" s="4"/>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K66" s="5"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="4"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -3695,15 +3999,16 @@
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="5"/>
+      <c r="G67" s="15"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="6"/>
       <c r="J67" s="5"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="5"/>
-      <c r="M67" s="4"/>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K67" s="5"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="4"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -3712,15 +4017,16 @@
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="5"/>
+      <c r="G68" s="15"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="6"/>
       <c r="J68" s="5"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="5"/>
-      <c r="M68" s="4"/>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K68" s="5"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="4"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -3729,15 +4035,16 @@
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="5"/>
+      <c r="G69" s="15"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="6"/>
       <c r="J69" s="5"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="5"/>
-      <c r="M69" s="4"/>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K69" s="5"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="4"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -3746,15 +4053,16 @@
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="5"/>
+      <c r="G70" s="15"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="6"/>
       <c r="J70" s="5"/>
-      <c r="K70" s="6"/>
-      <c r="L70" s="5"/>
-      <c r="M70" s="4"/>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K70" s="5"/>
+      <c r="L70" s="6"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="4"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -3763,15 +4071,16 @@
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="5"/>
+      <c r="G71" s="15"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="6"/>
       <c r="J71" s="5"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="5"/>
-      <c r="M71" s="4"/>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K71" s="5"/>
+      <c r="L71" s="6"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="4"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -3780,15 +4089,16 @@
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="5"/>
+      <c r="G72" s="15"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="6"/>
       <c r="J72" s="5"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="5"/>
-      <c r="M72" s="4"/>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K72" s="5"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="4"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -3797,15 +4107,16 @@
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="5"/>
+      <c r="G73" s="15"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="6"/>
       <c r="J73" s="5"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="5"/>
-      <c r="M73" s="4"/>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K73" s="5"/>
+      <c r="L73" s="6"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="4"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -3814,15 +4125,16 @@
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="5"/>
+      <c r="G74" s="15"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="6"/>
       <c r="J74" s="5"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="4"/>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K74" s="5"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="4"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>74</v>
       </c>
@@ -3831,15 +4143,16 @@
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="5"/>
+      <c r="G75" s="15"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="6"/>
       <c r="J75" s="5"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="5"/>
-      <c r="M75" s="4"/>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K75" s="5"/>
+      <c r="L75" s="6"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="4"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -3848,15 +4161,16 @@
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="5"/>
+      <c r="G76" s="15"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="6"/>
       <c r="J76" s="5"/>
-      <c r="K76" s="6"/>
-      <c r="L76" s="5"/>
-      <c r="M76" s="4"/>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K76" s="5"/>
+      <c r="L76" s="6"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="4"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>76</v>
       </c>
@@ -3865,15 +4179,16 @@
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="5"/>
+      <c r="G77" s="15"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="6"/>
       <c r="J77" s="5"/>
-      <c r="K77" s="6"/>
-      <c r="L77" s="5"/>
-      <c r="M77" s="4"/>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K77" s="5"/>
+      <c r="L77" s="6"/>
+      <c r="M77" s="5"/>
+      <c r="N77" s="4"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -3882,15 +4197,16 @@
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="5"/>
+      <c r="G78" s="15"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="6"/>
       <c r="J78" s="5"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="5"/>
-      <c r="M78" s="4"/>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K78" s="5"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="4"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -3899,15 +4215,16 @@
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="5"/>
+      <c r="G79" s="15"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="6"/>
       <c r="J79" s="5"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="5"/>
-      <c r="M79" s="4"/>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K79" s="5"/>
+      <c r="L79" s="6"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="4"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -3916,15 +4233,16 @@
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
-      <c r="G80" s="5"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="5"/>
+      <c r="G80" s="15"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="6"/>
       <c r="J80" s="5"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="5"/>
-      <c r="M80" s="4"/>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K80" s="5"/>
+      <c r="L80" s="6"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="4"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>80</v>
       </c>
@@ -3933,15 +4251,16 @@
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
       <c r="F81" s="5"/>
-      <c r="G81" s="5"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="5"/>
+      <c r="G81" s="15"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="6"/>
       <c r="J81" s="5"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="5"/>
-      <c r="M81" s="4"/>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K81" s="5"/>
+      <c r="L81" s="6"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="4"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>81</v>
       </c>
@@ -3950,15 +4269,16 @@
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
-      <c r="G82" s="5"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="5"/>
+      <c r="G82" s="15"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="6"/>
       <c r="J82" s="5"/>
-      <c r="K82" s="6"/>
-      <c r="L82" s="5"/>
-      <c r="M82" s="4"/>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K82" s="5"/>
+      <c r="L82" s="6"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="4"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -3967,15 +4287,16 @@
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
-      <c r="G83" s="5"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="5"/>
+      <c r="G83" s="15"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="6"/>
       <c r="J83" s="5"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="5"/>
-      <c r="M83" s="4"/>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K83" s="5"/>
+      <c r="L83" s="6"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="4"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>83</v>
       </c>
@@ -3984,15 +4305,16 @@
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
-      <c r="G84" s="5"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="5"/>
+      <c r="G84" s="15"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="6"/>
       <c r="J84" s="5"/>
-      <c r="K84" s="6"/>
-      <c r="L84" s="5"/>
-      <c r="M84" s="4"/>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K84" s="5"/>
+      <c r="L84" s="6"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="4"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>84</v>
       </c>
@@ -4001,15 +4323,16 @@
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
-      <c r="G85" s="5"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="5"/>
+      <c r="G85" s="15"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="6"/>
       <c r="J85" s="5"/>
-      <c r="K85" s="6"/>
-      <c r="L85" s="5"/>
-      <c r="M85" s="4"/>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K85" s="5"/>
+      <c r="L85" s="6"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="4"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>85</v>
       </c>
@@ -4018,15 +4341,16 @@
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
-      <c r="G86" s="5"/>
-      <c r="H86" s="6"/>
-      <c r="I86" s="5"/>
+      <c r="G86" s="15"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="6"/>
       <c r="J86" s="5"/>
-      <c r="K86" s="6"/>
-      <c r="L86" s="5"/>
-      <c r="M86" s="4"/>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K86" s="5"/>
+      <c r="L86" s="6"/>
+      <c r="M86" s="5"/>
+      <c r="N86" s="4"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>86</v>
       </c>
@@ -4035,15 +4359,16 @@
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
-      <c r="G87" s="5"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="5"/>
+      <c r="G87" s="15"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="6"/>
       <c r="J87" s="5"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="5"/>
-      <c r="M87" s="4"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K87" s="5"/>
+      <c r="L87" s="6"/>
+      <c r="M87" s="5"/>
+      <c r="N87" s="4"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>87</v>
       </c>
@@ -4052,15 +4377,16 @@
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
-      <c r="G88" s="5"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="5"/>
+      <c r="G88" s="15"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="6"/>
       <c r="J88" s="5"/>
-      <c r="K88" s="6"/>
-      <c r="L88" s="5"/>
-      <c r="M88" s="4"/>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K88" s="5"/>
+      <c r="L88" s="6"/>
+      <c r="M88" s="5"/>
+      <c r="N88" s="4"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>88</v>
       </c>
@@ -4069,15 +4395,16 @@
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
-      <c r="G89" s="5"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="5"/>
+      <c r="G89" s="15"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="6"/>
       <c r="J89" s="5"/>
-      <c r="K89" s="6"/>
-      <c r="L89" s="5"/>
-      <c r="M89" s="4"/>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K89" s="5"/>
+      <c r="L89" s="6"/>
+      <c r="M89" s="5"/>
+      <c r="N89" s="4"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>89</v>
       </c>
@@ -4086,15 +4413,16 @@
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="5"/>
+      <c r="G90" s="15"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="6"/>
       <c r="J90" s="5"/>
-      <c r="K90" s="6"/>
-      <c r="L90" s="5"/>
-      <c r="M90" s="4"/>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K90" s="5"/>
+      <c r="L90" s="6"/>
+      <c r="M90" s="5"/>
+      <c r="N90" s="4"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>90</v>
       </c>
@@ -4103,15 +4431,16 @@
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="5"/>
+      <c r="G91" s="15"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="6"/>
       <c r="J91" s="5"/>
-      <c r="K91" s="6"/>
-      <c r="L91" s="5"/>
-      <c r="M91" s="4"/>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K91" s="5"/>
+      <c r="L91" s="6"/>
+      <c r="M91" s="5"/>
+      <c r="N91" s="4"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>91</v>
       </c>
@@ -4120,15 +4449,16 @@
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
-      <c r="G92" s="5"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="5"/>
+      <c r="G92" s="15"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="6"/>
       <c r="J92" s="5"/>
-      <c r="K92" s="6"/>
-      <c r="L92" s="5"/>
-      <c r="M92" s="4"/>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K92" s="5"/>
+      <c r="L92" s="6"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="4"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>92</v>
       </c>
@@ -4137,15 +4467,16 @@
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="5"/>
+      <c r="G93" s="15"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="6"/>
       <c r="J93" s="5"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="5"/>
-      <c r="M93" s="4"/>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K93" s="5"/>
+      <c r="L93" s="6"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="4"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>93</v>
       </c>
@@ -4154,15 +4485,16 @@
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
-      <c r="G94" s="5"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="5"/>
+      <c r="G94" s="15"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="6"/>
       <c r="J94" s="5"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="5"/>
-      <c r="M94" s="4"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K94" s="5"/>
+      <c r="L94" s="6"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="4"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>94</v>
       </c>
@@ -4171,15 +4503,16 @@
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="5"/>
+      <c r="G95" s="15"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="6"/>
       <c r="J95" s="5"/>
-      <c r="K95" s="6"/>
-      <c r="L95" s="5"/>
-      <c r="M95" s="4"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K95" s="5"/>
+      <c r="L95" s="6"/>
+      <c r="M95" s="5"/>
+      <c r="N95" s="4"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <v>95</v>
       </c>
@@ -4188,15 +4521,16 @@
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="5"/>
+      <c r="G96" s="15"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="6"/>
       <c r="J96" s="5"/>
-      <c r="K96" s="6"/>
-      <c r="L96" s="5"/>
-      <c r="M96" s="4"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K96" s="5"/>
+      <c r="L96" s="6"/>
+      <c r="M96" s="5"/>
+      <c r="N96" s="4"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>96</v>
       </c>
@@ -4205,15 +4539,16 @@
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="5"/>
+      <c r="G97" s="15"/>
+      <c r="H97" s="5"/>
+      <c r="I97" s="6"/>
       <c r="J97" s="5"/>
-      <c r="K97" s="6"/>
-      <c r="L97" s="5"/>
-      <c r="M97" s="4"/>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K97" s="5"/>
+      <c r="L97" s="6"/>
+      <c r="M97" s="5"/>
+      <c r="N97" s="4"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>97</v>
       </c>
@@ -4222,15 +4557,16 @@
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="5"/>
+      <c r="G98" s="15"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="6"/>
       <c r="J98" s="5"/>
-      <c r="K98" s="6"/>
-      <c r="L98" s="5"/>
-      <c r="M98" s="4"/>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K98" s="5"/>
+      <c r="L98" s="6"/>
+      <c r="M98" s="5"/>
+      <c r="N98" s="4"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>98</v>
       </c>
@@ -4239,15 +4575,16 @@
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="5"/>
+      <c r="G99" s="15"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="6"/>
       <c r="J99" s="5"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="5"/>
-      <c r="M99" s="4"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K99" s="5"/>
+      <c r="L99" s="6"/>
+      <c r="M99" s="5"/>
+      <c r="N99" s="4"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>99</v>
       </c>
@@ -4256,15 +4593,16 @@
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
       <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="5"/>
+      <c r="G100" s="15"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="6"/>
       <c r="J100" s="5"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="5"/>
-      <c r="M100" s="4"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K100" s="5"/>
+      <c r="L100" s="6"/>
+      <c r="M100" s="5"/>
+      <c r="N100" s="4"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>100</v>
       </c>
@@ -4273,15 +4611,16 @@
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="5"/>
+      <c r="G101" s="15"/>
+      <c r="H101" s="5"/>
+      <c r="I101" s="6"/>
       <c r="J101" s="5"/>
-      <c r="K101" s="6"/>
-      <c r="L101" s="5"/>
-      <c r="M101" s="4"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K101" s="5"/>
+      <c r="L101" s="6"/>
+      <c r="M101" s="5"/>
+      <c r="N101" s="4"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>101</v>
       </c>
@@ -4290,15 +4629,16 @@
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
-      <c r="G102" s="5"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="5"/>
+      <c r="G102" s="15"/>
+      <c r="H102" s="5"/>
+      <c r="I102" s="6"/>
       <c r="J102" s="5"/>
-      <c r="K102" s="6"/>
-      <c r="L102" s="5"/>
-      <c r="M102" s="4"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K102" s="5"/>
+      <c r="L102" s="6"/>
+      <c r="M102" s="5"/>
+      <c r="N102" s="4"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>102</v>
       </c>
@@ -4307,15 +4647,16 @@
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
-      <c r="G103" s="5"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="5"/>
+      <c r="G103" s="15"/>
+      <c r="H103" s="5"/>
+      <c r="I103" s="6"/>
       <c r="J103" s="5"/>
-      <c r="K103" s="6"/>
-      <c r="L103" s="5"/>
-      <c r="M103" s="4"/>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K103" s="5"/>
+      <c r="L103" s="6"/>
+      <c r="M103" s="5"/>
+      <c r="N103" s="4"/>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>103</v>
       </c>
@@ -4324,23 +4665,25 @@
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
-      <c r="G104" s="5"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="5"/>
+      <c r="G104" s="15"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="6"/>
       <c r="J104" s="5"/>
-      <c r="K104" s="6"/>
-      <c r="L104" s="5"/>
-      <c r="M104" s="4"/>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K104" s="5"/>
+      <c r="L104" s="6"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="4"/>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>104</v>
       </c>
       <c r="B105" s="5"/>
-      <c r="G105"/>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L106" t="s">
+      <c r="G105" s="15"/>
+      <c r="H105"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M106" t="s">
         <v>44</v>
       </c>
     </row>

--- a/RegistrationsFile.xlsx
+++ b/RegistrationsFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E625FC1E-028D-4703-BFB1-522A899B0114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63AF9978-3782-4297-A546-49CFAD0AF01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="541" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="231">
   <si>
     <t>MODEL</t>
   </si>
@@ -709,6 +709,21 @@
   </si>
   <si>
     <t>RTO</t>
+  </si>
+  <si>
+    <t>JK13K1708</t>
+  </si>
+  <si>
+    <t>MBHKWD43SSH641288</t>
+  </si>
+  <si>
+    <t>SAJAD AHMAD MIR</t>
+  </si>
+  <si>
+    <t>PRME SPLENDID SILVER</t>
+  </si>
+  <si>
+    <t>JK25101566763596</t>
   </si>
 </sst>
 </file>
@@ -1207,7 +1222,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1240,13 +1255,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1293,25 +1304,6 @@
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="16">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1385,6 +1377,25 @@
         <sz val="11"/>
       </font>
       <numFmt numFmtId="165" formatCode="[$-409]dd/mmm/yy;@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1479,17 +1490,17 @@
     <tableColumn id="2" xr3:uid="{6ABB4EDF-0F58-40D7-979C-D37D8D91A6BC}" name="CHASSIS" dataDxfId="11"/>
     <tableColumn id="3" xr3:uid="{285CC4F4-4CD1-4FFC-A101-ED051DA40438}" name="NAME" dataDxfId="10"/>
     <tableColumn id="4" xr3:uid="{28DC8B59-EFA0-4502-86B0-033B0B60D615}" name="MODEL" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{B25F5A6A-3B72-4772-B75C-D86670F35131}" name="Color" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{22F5E9AE-FC4E-4EBD-ADBF-5C93F85B331F}" name="RTO" dataDxfId="0">
+    <tableColumn id="14" xr3:uid="{B25F5A6A-3B72-4772-B75C-D86670F35131}" name="Color" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{22F5E9AE-FC4E-4EBD-ADBF-5C93F85B331F}" name="RTO" dataDxfId="7">
       <calculatedColumnFormula>IF(LEFT(H2,4)="JK13","PULWAMA",IF(LEFT(H2,4)="JK01","SRINAGAR",IF(LEFT(H2,4)="JK04","BUDGAM",IF(LEFT(H2,4)="JK03","ANANTNAG",IF(LEFT(H2,4)="JK05","BARAMULLA",IF(LEFT(H2,4)="25BH","BHARAT",IF(LEFT(H2,4)="JK12","POONCH",IF(LEFT(H2,4)="JK18","KULGAM",IF(LEFT(H2,4)="JK22","SHOPIAN",IF(LEFT(H2,4)="T102","TEMP",IF(LEFT(H2,4)="","NEW","NA")))))))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3D7EC305-A438-47DE-A91A-6CB0CF4B1937}" name="REG NUM" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{9942893D-0703-456F-8072-CD136C7B4052}" name="DATE OF REG" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{3AD2B0D9-D7A5-46E0-B596-F6B7F1CDDEA6}" name="DSE" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{475221AE-3FDC-4CED-B76C-4DA1DD4F8AD9}" name="RC RECEIVED BY" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{F594ED7D-6966-47AC-A5C3-25754B73A3CC}" name="DATE" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{452E3ECD-E927-4EC7-A8A2-4A866233750E}" name="FASTTAG" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{CFEE5573-D700-4B26-B382-BCA8210C54C2}" name="DATED" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{3D7EC305-A438-47DE-A91A-6CB0CF4B1937}" name="REG NUM" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{9942893D-0703-456F-8072-CD136C7B4052}" name="DATE OF REG" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{3AD2B0D9-D7A5-46E0-B596-F6B7F1CDDEA6}" name="DSE" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{475221AE-3FDC-4CED-B76C-4DA1DD4F8AD9}" name="RC RECEIVED BY" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{F594ED7D-6966-47AC-A5C3-25754B73A3CC}" name="DATE" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{452E3ECD-E927-4EC7-A8A2-4A866233750E}" name="FASTTAG" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{CFEE5573-D700-4B26-B382-BCA8210C54C2}" name="DATED" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1850,8 +1861,7 @@
     <col min="3" max="3" width="31.5703125" customWidth="1"/>
     <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32.85546875" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" customWidth="1"/>
-    <col min="7" max="7" width="30.140625" style="16" customWidth="1"/>
+    <col min="6" max="7" width="30.140625" customWidth="1"/>
     <col min="8" max="8" width="19" style="12" customWidth="1"/>
     <col min="9" max="9" width="17.28515625" style="3" customWidth="1"/>
     <col min="10" max="10" width="30" bestFit="1" customWidth="1"/>
@@ -1880,7 +1890,7 @@
       <c r="F1" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="8" t="s">
         <v>225</v>
       </c>
       <c r="H1" s="11" t="s">
@@ -1920,7 +1930,7 @@
         <v>101</v>
       </c>
       <c r="F2" s="5"/>
-      <c r="G2" s="15" t="str">
+      <c r="G2" s="5" t="str">
         <f>IF(LEFT(H2,4)="JK13","PULWAMA",IF(LEFT(H2,4)="JK01","SRINAGAR",IF(LEFT(H2,4)="JK04","BUDGAM",IF(LEFT(H2,4)="JK03","ANANTNAG",IF(LEFT(H2,4)="JK05","BARAMULLA",IF(LEFT(H2,4)="25BH","BHARAT",IF(LEFT(H2,4)="JK12","POONCH",IF(LEFT(H2,4)="JK18","KULGAM",IF(LEFT(H2,4)="JK22","SHOPIAN",IF(LEFT(H2,4)="T102","TEMP",IF(LEFT(H2,4)="","NEW","NA")))))))))))</f>
         <v>SRINAGAR</v>
       </c>
@@ -1957,8 +1967,8 @@
       <c r="F3" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="G3" s="15" t="str">
-        <f t="shared" ref="G3:G49" si="0">IF(LEFT(H3,4)="JK13","PULWAMA",IF(LEFT(H3,4)="JK01","SRINAGAR",IF(LEFT(H3,4)="JK04","BUDGAM",IF(LEFT(H3,4)="JK03","ANANTNAG",IF(LEFT(H3,4)="JK05","BARAMULLA",IF(LEFT(H3,4)="25BH","BHARAT",IF(LEFT(H3,4)="JK12","POONCH",IF(LEFT(H3,4)="JK18","KULGAM",IF(LEFT(H3,4)="JK22","SHOPIAN",IF(LEFT(H3,4)="T102","TEMP",IF(LEFT(H3,4)="","NEW","NA")))))))))))</f>
+      <c r="G3" s="5" t="str">
+        <f>IF(LEFT(H3,4)="JK13","PULWAMA",IF(LEFT(H3,4)="JK01","SRINAGAR",IF(LEFT(H3,4)="JK04","BUDGAM",IF(LEFT(H3,4)="JK03","ANANTNAG",IF(LEFT(H3,4)="JK05","BARAMULLA",IF(LEFT(H3,4)="25BH","BHARAT",IF(LEFT(H3,4)="JK12","POONCH",IF(LEFT(H3,4)="JK18","KULGAM",IF(LEFT(H3,4)="JK22","SHOPIAN",IF(LEFT(H3,4)="T102","TEMP",IF(LEFT(H3,4)="","NEW","NA")))))))))))</f>
         <v>BUDGAM</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -1994,8 +2004,8 @@
         <v>12</v>
       </c>
       <c r="F4" s="5"/>
-      <c r="G4" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G4" s="5" t="str">
+        <f>IF(LEFT(H4,4)="JK13","PULWAMA",IF(LEFT(H4,4)="JK01","SRINAGAR",IF(LEFT(H4,4)="JK04","BUDGAM",IF(LEFT(H4,4)="JK03","ANANTNAG",IF(LEFT(H4,4)="JK05","BARAMULLA",IF(LEFT(H4,4)="25BH","BHARAT",IF(LEFT(H4,4)="JK12","POONCH",IF(LEFT(H4,4)="JK18","KULGAM",IF(LEFT(H4,4)="JK22","SHOPIAN",IF(LEFT(H4,4)="T102","TEMP",IF(LEFT(H4,4)="","NEW","NA")))))))))))</f>
         <v>BUDGAM</v>
       </c>
       <c r="H4" s="5" t="s">
@@ -2031,8 +2041,8 @@
         <v>31</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="G5" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G5" s="5" t="str">
+        <f>IF(LEFT(H5,4)="JK13","PULWAMA",IF(LEFT(H5,4)="JK01","SRINAGAR",IF(LEFT(H5,4)="JK04","BUDGAM",IF(LEFT(H5,4)="JK03","ANANTNAG",IF(LEFT(H5,4)="JK05","BARAMULLA",IF(LEFT(H5,4)="25BH","BHARAT",IF(LEFT(H5,4)="JK12","POONCH",IF(LEFT(H5,4)="JK18","KULGAM",IF(LEFT(H5,4)="JK22","SHOPIAN",IF(LEFT(H5,4)="T102","TEMP",IF(LEFT(H5,4)="","NEW","NA")))))))))))</f>
         <v>BUDGAM</v>
       </c>
       <c r="H5" s="5" t="s">
@@ -2068,8 +2078,8 @@
         <v>31</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G6" s="5" t="str">
+        <f>IF(LEFT(H6,4)="JK13","PULWAMA",IF(LEFT(H6,4)="JK01","SRINAGAR",IF(LEFT(H6,4)="JK04","BUDGAM",IF(LEFT(H6,4)="JK03","ANANTNAG",IF(LEFT(H6,4)="JK05","BARAMULLA",IF(LEFT(H6,4)="25BH","BHARAT",IF(LEFT(H6,4)="JK12","POONCH",IF(LEFT(H6,4)="JK18","KULGAM",IF(LEFT(H6,4)="JK22","SHOPIAN",IF(LEFT(H6,4)="T102","TEMP",IF(LEFT(H6,4)="","NEW","NA")))))))))))</f>
         <v>SRINAGAR</v>
       </c>
       <c r="H6" s="5" t="s">
@@ -2105,8 +2115,8 @@
         <v>5</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G7" s="5" t="str">
+        <f>IF(LEFT(H7,4)="JK13","PULWAMA",IF(LEFT(H7,4)="JK01","SRINAGAR",IF(LEFT(H7,4)="JK04","BUDGAM",IF(LEFT(H7,4)="JK03","ANANTNAG",IF(LEFT(H7,4)="JK05","BARAMULLA",IF(LEFT(H7,4)="25BH","BHARAT",IF(LEFT(H7,4)="JK12","POONCH",IF(LEFT(H7,4)="JK18","KULGAM",IF(LEFT(H7,4)="JK22","SHOPIAN",IF(LEFT(H7,4)="T102","TEMP",IF(LEFT(H7,4)="","NEW","NA")))))))))))</f>
         <v>SRINAGAR</v>
       </c>
       <c r="H7" s="5" t="s">
@@ -2146,8 +2156,8 @@
         <v>31</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G8" s="5" t="str">
+        <f>IF(LEFT(H8,4)="JK13","PULWAMA",IF(LEFT(H8,4)="JK01","SRINAGAR",IF(LEFT(H8,4)="JK04","BUDGAM",IF(LEFT(H8,4)="JK03","ANANTNAG",IF(LEFT(H8,4)="JK05","BARAMULLA",IF(LEFT(H8,4)="25BH","BHARAT",IF(LEFT(H8,4)="JK12","POONCH",IF(LEFT(H8,4)="JK18","KULGAM",IF(LEFT(H8,4)="JK22","SHOPIAN",IF(LEFT(H8,4)="T102","TEMP",IF(LEFT(H8,4)="","NEW","NA")))))))))))</f>
         <v>PULWAMA</v>
       </c>
       <c r="H8" s="5" t="s">
@@ -2183,8 +2193,8 @@
         <v>126</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G9" s="5" t="str">
+        <f>IF(LEFT(H9,4)="JK13","PULWAMA",IF(LEFT(H9,4)="JK01","SRINAGAR",IF(LEFT(H9,4)="JK04","BUDGAM",IF(LEFT(H9,4)="JK03","ANANTNAG",IF(LEFT(H9,4)="JK05","BARAMULLA",IF(LEFT(H9,4)="25BH","BHARAT",IF(LEFT(H9,4)="JK12","POONCH",IF(LEFT(H9,4)="JK18","KULGAM",IF(LEFT(H9,4)="JK22","SHOPIAN",IF(LEFT(H9,4)="T102","TEMP",IF(LEFT(H9,4)="","NEW","NA")))))))))))</f>
         <v>PULWAMA</v>
       </c>
       <c r="H9" s="5" t="s">
@@ -2220,8 +2230,8 @@
         <v>5</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G10" s="5" t="str">
+        <f>IF(LEFT(H10,4)="JK13","PULWAMA",IF(LEFT(H10,4)="JK01","SRINAGAR",IF(LEFT(H10,4)="JK04","BUDGAM",IF(LEFT(H10,4)="JK03","ANANTNAG",IF(LEFT(H10,4)="JK05","BARAMULLA",IF(LEFT(H10,4)="25BH","BHARAT",IF(LEFT(H10,4)="JK12","POONCH",IF(LEFT(H10,4)="JK18","KULGAM",IF(LEFT(H10,4)="JK22","SHOPIAN",IF(LEFT(H10,4)="T102","TEMP",IF(LEFT(H10,4)="","NEW","NA")))))))))))</f>
         <v>PULWAMA</v>
       </c>
       <c r="H10" s="5" t="s">
@@ -2246,35 +2256,39 @@
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>230</v>
+      </c>
       <c r="C11" s="5" t="s">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>149</v>
+        <v>228</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>SHOPIAN</v>
+        <v>215</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="G11" s="5" t="str">
+        <f>IF(LEFT(H11,4)="JK13","PULWAMA",IF(LEFT(H11,4)="JK01","SRINAGAR",IF(LEFT(H11,4)="JK04","BUDGAM",IF(LEFT(H11,4)="JK03","ANANTNAG",IF(LEFT(H11,4)="JK05","BARAMULLA",IF(LEFT(H11,4)="25BH","BHARAT",IF(LEFT(H11,4)="JK12","POONCH",IF(LEFT(H11,4)="JK18","KULGAM",IF(LEFT(H11,4)="JK22","SHOPIAN",IF(LEFT(H11,4)="T102","TEMP",IF(LEFT(H11,4)="","NEW","NA")))))))))))</f>
+        <v>PULWAMA</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="I11" s="6">
-        <v>45948</v>
+        <v>45946</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="L11" s="6">
-        <v>45966</v>
+        <v>45971</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="4"/>
@@ -2285,31 +2299,33 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+      <c r="G12" s="5" t="str">
+        <f>IF(LEFT(H12,4)="JK13","PULWAMA",IF(LEFT(H12,4)="JK01","SRINAGAR",IF(LEFT(H12,4)="JK04","BUDGAM",IF(LEFT(H12,4)="JK03","ANANTNAG",IF(LEFT(H12,4)="JK05","BARAMULLA",IF(LEFT(H12,4)="25BH","BHARAT",IF(LEFT(H12,4)="JK12","POONCH",IF(LEFT(H12,4)="JK18","KULGAM",IF(LEFT(H12,4)="JK22","SHOPIAN",IF(LEFT(H12,4)="T102","TEMP",IF(LEFT(H12,4)="","NEW","NA")))))))))))</f>
+        <v>SHOPIAN</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="I12" s="6">
-        <v>45953</v>
-      </c>
-      <c r="J12" s="5"/>
+        <v>45948</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="K12" s="5" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="L12" s="6">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="M12" s="5"/>
       <c r="N12" s="4"/>
@@ -2320,33 +2336,31 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G13" s="5" t="str">
+        <f>IF(LEFT(H13,4)="JK13","PULWAMA",IF(LEFT(H13,4)="JK01","SRINAGAR",IF(LEFT(H13,4)="JK04","BUDGAM",IF(LEFT(H13,4)="JK03","ANANTNAG",IF(LEFT(H13,4)="JK05","BARAMULLA",IF(LEFT(H13,4)="25BH","BHARAT",IF(LEFT(H13,4)="JK12","POONCH",IF(LEFT(H13,4)="JK18","KULGAM",IF(LEFT(H13,4)="JK22","SHOPIAN",IF(LEFT(H13,4)="T102","TEMP",IF(LEFT(H13,4)="","NEW","NA")))))))))))</f>
         <v>SRINAGAR</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="I13" s="6">
         <v>45953</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="J13" s="5"/>
       <c r="K13" s="5" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="L13" s="6">
-        <v>45965</v>
+        <v>45964</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" s="4"/>
@@ -2357,33 +2371,33 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>ANANTNAG</v>
+      <c r="G14" s="5" t="str">
+        <f>IF(LEFT(H14,4)="JK13","PULWAMA",IF(LEFT(H14,4)="JK01","SRINAGAR",IF(LEFT(H14,4)="JK04","BUDGAM",IF(LEFT(H14,4)="JK03","ANANTNAG",IF(LEFT(H14,4)="JK05","BARAMULLA",IF(LEFT(H14,4)="25BH","BHARAT",IF(LEFT(H14,4)="JK12","POONCH",IF(LEFT(H14,4)="JK18","KULGAM",IF(LEFT(H14,4)="JK22","SHOPIAN",IF(LEFT(H14,4)="T102","TEMP",IF(LEFT(H14,4)="","NEW","NA")))))))))))</f>
+        <v>SRINAGAR</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="I14" s="6">
         <v>45953</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="L14" s="6">
-        <v>45966</v>
+        <v>45965</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" s="4"/>
@@ -2394,30 +2408,30 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>PULWAMA</v>
+      <c r="G15" s="5" t="str">
+        <f>IF(LEFT(H15,4)="JK13","PULWAMA",IF(LEFT(H15,4)="JK01","SRINAGAR",IF(LEFT(H15,4)="JK04","BUDGAM",IF(LEFT(H15,4)="JK03","ANANTNAG",IF(LEFT(H15,4)="JK05","BARAMULLA",IF(LEFT(H15,4)="25BH","BHARAT",IF(LEFT(H15,4)="JK12","POONCH",IF(LEFT(H15,4)="JK18","KULGAM",IF(LEFT(H15,4)="JK22","SHOPIAN",IF(LEFT(H15,4)="T102","TEMP",IF(LEFT(H15,4)="","NEW","NA")))))))))))</f>
+        <v>ANANTNAG</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I15" s="6">
-        <v>45954</v>
+        <v>45953</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>127</v>
+        <v>14</v>
       </c>
       <c r="L15" s="6">
         <v>45966</v>
@@ -2431,30 +2445,30 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G16" s="5" t="str">
+        <f>IF(LEFT(H16,4)="JK13","PULWAMA",IF(LEFT(H16,4)="JK01","SRINAGAR",IF(LEFT(H16,4)="JK04","BUDGAM",IF(LEFT(H16,4)="JK03","ANANTNAG",IF(LEFT(H16,4)="JK05","BARAMULLA",IF(LEFT(H16,4)="25BH","BHARAT",IF(LEFT(H16,4)="JK12","POONCH",IF(LEFT(H16,4)="JK18","KULGAM",IF(LEFT(H16,4)="JK22","SHOPIAN",IF(LEFT(H16,4)="T102","TEMP",IF(LEFT(H16,4)="","NEW","NA")))))))))))</f>
         <v>PULWAMA</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="I16" s="6">
         <v>45954</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="L16" s="6">
         <v>45966</v>
@@ -2468,33 +2482,33 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+      <c r="G17" s="5" t="str">
+        <f>IF(LEFT(H17,4)="JK13","PULWAMA",IF(LEFT(H17,4)="JK01","SRINAGAR",IF(LEFT(H17,4)="JK04","BUDGAM",IF(LEFT(H17,4)="JK03","ANANTNAG",IF(LEFT(H17,4)="JK05","BARAMULLA",IF(LEFT(H17,4)="25BH","BHARAT",IF(LEFT(H17,4)="JK12","POONCH",IF(LEFT(H17,4)="JK18","KULGAM",IF(LEFT(H17,4)="JK22","SHOPIAN",IF(LEFT(H17,4)="T102","TEMP",IF(LEFT(H17,4)="","NEW","NA")))))))))))</f>
+        <v>PULWAMA</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="I17" s="6">
-        <v>45958</v>
+        <v>45954</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="L17" s="6">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="M17" s="5"/>
       <c r="N17" s="4"/>
@@ -2505,40 +2519,36 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G18" s="5" t="str">
+        <f>IF(LEFT(H18,4)="JK13","PULWAMA",IF(LEFT(H18,4)="JK01","SRINAGAR",IF(LEFT(H18,4)="JK04","BUDGAM",IF(LEFT(H18,4)="JK03","ANANTNAG",IF(LEFT(H18,4)="JK05","BARAMULLA",IF(LEFT(H18,4)="25BH","BHARAT",IF(LEFT(H18,4)="JK12","POONCH",IF(LEFT(H18,4)="JK18","KULGAM",IF(LEFT(H18,4)="JK22","SHOPIAN",IF(LEFT(H18,4)="T102","TEMP",IF(LEFT(H18,4)="","NEW","NA")))))))))))</f>
         <v>SRINAGAR</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="I18" s="6">
-        <v>45959</v>
+        <v>45958</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="L18" s="6">
-        <v>45962</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N18" s="4">
-        <v>45959</v>
-      </c>
+        <v>45965</v>
+      </c>
+      <c r="M18" s="5"/>
+      <c r="N18" s="4"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
@@ -2546,34 +2556,40 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5" t="s">
-        <v>186</v>
+        <v>60</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>187</v>
+        <v>59</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G19" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>BHARAT</v>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5" t="str">
+        <f>IF(LEFT(H19,4)="JK13","PULWAMA",IF(LEFT(H19,4)="JK01","SRINAGAR",IF(LEFT(H19,4)="JK04","BUDGAM",IF(LEFT(H19,4)="JK03","ANANTNAG",IF(LEFT(H19,4)="JK05","BARAMULLA",IF(LEFT(H19,4)="25BH","BHARAT",IF(LEFT(H19,4)="JK12","POONCH",IF(LEFT(H19,4)="JK18","KULGAM",IF(LEFT(H19,4)="JK22","SHOPIAN",IF(LEFT(H19,4)="T102","TEMP",IF(LEFT(H19,4)="","NEW","NA")))))))))))</f>
+        <v>SRINAGAR</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>188</v>
+        <v>58</v>
       </c>
       <c r="I19" s="6">
         <v>45959</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="K19" s="5"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L19" s="6">
+        <v>45962</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" s="4">
+        <v>45959</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
@@ -2581,40 +2597,34 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>22</v>
+        <v>187</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+        <v>12</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="G20" s="5" t="str">
+        <f>IF(LEFT(H20,4)="JK13","PULWAMA",IF(LEFT(H20,4)="JK01","SRINAGAR",IF(LEFT(H20,4)="JK04","BUDGAM",IF(LEFT(H20,4)="JK03","ANANTNAG",IF(LEFT(H20,4)="JK05","BARAMULLA",IF(LEFT(H20,4)="25BH","BHARAT",IF(LEFT(H20,4)="JK12","POONCH",IF(LEFT(H20,4)="JK18","KULGAM",IF(LEFT(H20,4)="JK22","SHOPIAN",IF(LEFT(H20,4)="T102","TEMP",IF(LEFT(H20,4)="","NEW","NA")))))))))))</f>
+        <v>BHARAT</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="I20" s="6">
-        <v>45960</v>
+        <v>45959</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L20" s="6">
-        <v>45961</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N20" s="4">
-        <v>45960</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="K20" s="5"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="4"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
@@ -2622,33 +2632,33 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="G21" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>BUDGAM</v>
+      <c r="G21" s="5" t="str">
+        <f>IF(LEFT(H21,4)="JK13","PULWAMA",IF(LEFT(H21,4)="JK01","SRINAGAR",IF(LEFT(H21,4)="JK04","BUDGAM",IF(LEFT(H21,4)="JK03","ANANTNAG",IF(LEFT(H21,4)="JK05","BARAMULLA",IF(LEFT(H21,4)="25BH","BHARAT",IF(LEFT(H21,4)="JK12","POONCH",IF(LEFT(H21,4)="JK18","KULGAM",IF(LEFT(H21,4)="JK22","SHOPIAN",IF(LEFT(H21,4)="T102","TEMP",IF(LEFT(H21,4)="","NEW","NA")))))))))))</f>
+        <v>SRINAGAR</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="I21" s="6">
         <v>45960</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="L21" s="6">
-        <v>45964</v>
+        <v>45961</v>
       </c>
       <c r="M21" s="5" t="s">
         <v>23</v>
@@ -2663,36 +2673,40 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="G22" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+      <c r="G22" s="5" t="str">
+        <f>IF(LEFT(H22,4)="JK13","PULWAMA",IF(LEFT(H22,4)="JK01","SRINAGAR",IF(LEFT(H22,4)="JK04","BUDGAM",IF(LEFT(H22,4)="JK03","ANANTNAG",IF(LEFT(H22,4)="JK05","BARAMULLA",IF(LEFT(H22,4)="25BH","BHARAT",IF(LEFT(H22,4)="JK12","POONCH",IF(LEFT(H22,4)="JK18","KULGAM",IF(LEFT(H22,4)="JK22","SHOPIAN",IF(LEFT(H22,4)="T102","TEMP",IF(LEFT(H22,4)="","NEW","NA")))))))))))</f>
+        <v>BUDGAM</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="I22" s="6">
         <v>45960</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="L22" s="6">
-        <v>45965</v>
-      </c>
-      <c r="M22" s="5"/>
-      <c r="N22" s="4"/>
+        <v>45964</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N22" s="4">
+        <v>45960</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
@@ -2700,40 +2714,36 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>2</v>
+        <v>118</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>ANANTNAG</v>
+      <c r="G23" s="5" t="str">
+        <f>IF(LEFT(H23,4)="JK13","PULWAMA",IF(LEFT(H23,4)="JK01","SRINAGAR",IF(LEFT(H23,4)="JK04","BUDGAM",IF(LEFT(H23,4)="JK03","ANANTNAG",IF(LEFT(H23,4)="JK05","BARAMULLA",IF(LEFT(H23,4)="25BH","BHARAT",IF(LEFT(H23,4)="JK12","POONCH",IF(LEFT(H23,4)="JK18","KULGAM",IF(LEFT(H23,4)="JK22","SHOPIAN",IF(LEFT(H23,4)="T102","TEMP",IF(LEFT(H23,4)="","NEW","NA")))))))))))</f>
+        <v>SRINAGAR</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="I23" s="6">
-        <v>45961</v>
+        <v>45960</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="L23" s="6">
-        <v>45964</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N23" s="4">
-        <v>45961</v>
-      </c>
+        <v>45965</v>
+      </c>
+      <c r="M23" s="5"/>
+      <c r="N23" s="4"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
@@ -2741,30 +2751,34 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="G24" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G24" s="5" t="str">
+        <f>IF(LEFT(H24,4)="JK13","PULWAMA",IF(LEFT(H24,4)="JK01","SRINAGAR",IF(LEFT(H24,4)="JK04","BUDGAM",IF(LEFT(H24,4)="JK03","ANANTNAG",IF(LEFT(H24,4)="JK05","BARAMULLA",IF(LEFT(H24,4)="25BH","BHARAT",IF(LEFT(H24,4)="JK12","POONCH",IF(LEFT(H24,4)="JK18","KULGAM",IF(LEFT(H24,4)="JK22","SHOPIAN",IF(LEFT(H24,4)="T102","TEMP",IF(LEFT(H24,4)="","NEW","NA")))))))))))</f>
         <v>ANANTNAG</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I24" s="6">
         <v>45961</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K24" s="5"/>
-      <c r="L24" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L24" s="6">
+        <v>45964</v>
+      </c>
       <c r="M24" s="5" t="s">
         <v>23</v>
       </c>
@@ -2778,21 +2792,21 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="G25" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>KULGAM</v>
+      <c r="G25" s="5" t="str">
+        <f>IF(LEFT(H25,4)="JK13","PULWAMA",IF(LEFT(H25,4)="JK01","SRINAGAR",IF(LEFT(H25,4)="JK04","BUDGAM",IF(LEFT(H25,4)="JK03","ANANTNAG",IF(LEFT(H25,4)="JK05","BARAMULLA",IF(LEFT(H25,4)="25BH","BHARAT",IF(LEFT(H25,4)="JK12","POONCH",IF(LEFT(H25,4)="JK18","KULGAM",IF(LEFT(H25,4)="JK22","SHOPIAN",IF(LEFT(H25,4)="T102","TEMP",IF(LEFT(H25,4)="","NEW","NA")))))))))))</f>
+        <v>ANANTNAG</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="I25" s="6">
         <v>45961</v>
@@ -2806,7 +2820,7 @@
         <v>23</v>
       </c>
       <c r="N25" s="4">
-        <v>45962</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2815,27 +2829,27 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>PULWAMA</v>
+      <c r="G26" s="5" t="str">
+        <f>IF(LEFT(H26,4)="JK13","PULWAMA",IF(LEFT(H26,4)="JK01","SRINAGAR",IF(LEFT(H26,4)="JK04","BUDGAM",IF(LEFT(H26,4)="JK03","ANANTNAG",IF(LEFT(H26,4)="JK05","BARAMULLA",IF(LEFT(H26,4)="25BH","BHARAT",IF(LEFT(H26,4)="JK12","POONCH",IF(LEFT(H26,4)="JK18","KULGAM",IF(LEFT(H26,4)="JK22","SHOPIAN",IF(LEFT(H26,4)="T102","TEMP",IF(LEFT(H26,4)="","NEW","NA")))))))))))</f>
+        <v>KULGAM</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I26" s="6">
         <v>45961</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="6"/>
@@ -2843,7 +2857,7 @@
         <v>23</v>
       </c>
       <c r="N26" s="4">
-        <v>45961</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2852,36 +2866,36 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="G27" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>ANANTNAG</v>
+      <c r="G27" s="5" t="str">
+        <f>IF(LEFT(H27,4)="JK13","PULWAMA",IF(LEFT(H27,4)="JK01","SRINAGAR",IF(LEFT(H27,4)="JK04","BUDGAM",IF(LEFT(H27,4)="JK03","ANANTNAG",IF(LEFT(H27,4)="JK05","BARAMULLA",IF(LEFT(H27,4)="25BH","BHARAT",IF(LEFT(H27,4)="JK12","POONCH",IF(LEFT(H27,4)="JK18","KULGAM",IF(LEFT(H27,4)="JK22","SHOPIAN",IF(LEFT(H27,4)="T102","TEMP",IF(LEFT(H27,4)="","NEW","NA")))))))))))</f>
+        <v>PULWAMA</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="I27" s="6">
         <v>45961</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L27" s="6">
-        <v>45966</v>
-      </c>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="K27" s="5"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N27" s="4">
+        <v>45961</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
@@ -2889,36 +2903,36 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5" t="s">
-        <v>144</v>
+        <v>35</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="G28" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>BHARAT</v>
+      <c r="G28" s="5" t="str">
+        <f>IF(LEFT(H28,4)="JK13","PULWAMA",IF(LEFT(H28,4)="JK01","SRINAGAR",IF(LEFT(H28,4)="JK04","BUDGAM",IF(LEFT(H28,4)="JK03","ANANTNAG",IF(LEFT(H28,4)="JK05","BARAMULLA",IF(LEFT(H28,4)="25BH","BHARAT",IF(LEFT(H28,4)="JK12","POONCH",IF(LEFT(H28,4)="JK18","KULGAM",IF(LEFT(H28,4)="JK22","SHOPIAN",IF(LEFT(H28,4)="T102","TEMP",IF(LEFT(H28,4)="","NEW","NA")))))))))))</f>
+        <v>ANANTNAG</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="I28" s="6">
         <v>45961</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="L28" s="6">
         <v>45966</v>
       </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="4"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
@@ -2926,40 +2940,36 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="G29" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+      <c r="G29" s="5" t="str">
+        <f>IF(LEFT(H29,4)="JK13","PULWAMA",IF(LEFT(H29,4)="JK01","SRINAGAR",IF(LEFT(H29,4)="JK04","BUDGAM",IF(LEFT(H29,4)="JK03","ANANTNAG",IF(LEFT(H29,4)="JK05","BARAMULLA",IF(LEFT(H29,4)="25BH","BHARAT",IF(LEFT(H29,4)="JK12","POONCH",IF(LEFT(H29,4)="JK18","KULGAM",IF(LEFT(H29,4)="JK22","SHOPIAN",IF(LEFT(H29,4)="T102","TEMP",IF(LEFT(H29,4)="","NEW","NA")))))))))))</f>
+        <v>BHARAT</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>63</v>
+        <v>147</v>
       </c>
       <c r="I29" s="6">
-        <v>45962</v>
+        <v>45961</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="L29" s="6">
-        <v>45964</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N29" s="4">
-        <v>45962</v>
-      </c>
+        <v>45966</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="4"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
@@ -2967,30 +2977,34 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="G30" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G30" s="5" t="str">
+        <f>IF(LEFT(H30,4)="JK13","PULWAMA",IF(LEFT(H30,4)="JK01","SRINAGAR",IF(LEFT(H30,4)="JK04","BUDGAM",IF(LEFT(H30,4)="JK03","ANANTNAG",IF(LEFT(H30,4)="JK05","BARAMULLA",IF(LEFT(H30,4)="25BH","BHARAT",IF(LEFT(H30,4)="JK12","POONCH",IF(LEFT(H30,4)="JK18","KULGAM",IF(LEFT(H30,4)="JK22","SHOPIAN",IF(LEFT(H30,4)="T102","TEMP",IF(LEFT(H30,4)="","NEW","NA")))))))))))</f>
         <v>SRINAGAR</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I30" s="6">
         <v>45962</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K30" s="5"/>
-      <c r="L30" s="6"/>
+        <v>75</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L30" s="6">
+        <v>45964</v>
+      </c>
       <c r="M30" s="5" t="s">
         <v>23</v>
       </c>
@@ -3004,34 +3018,30 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F31" s="5"/>
-      <c r="G31" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>TEMP</v>
+      <c r="G31" s="5" t="str">
+        <f>IF(LEFT(H31,4)="JK13","PULWAMA",IF(LEFT(H31,4)="JK01","SRINAGAR",IF(LEFT(H31,4)="JK04","BUDGAM",IF(LEFT(H31,4)="JK03","ANANTNAG",IF(LEFT(H31,4)="JK05","BARAMULLA",IF(LEFT(H31,4)="25BH","BHARAT",IF(LEFT(H31,4)="JK12","POONCH",IF(LEFT(H31,4)="JK18","KULGAM",IF(LEFT(H31,4)="JK22","SHOPIAN",IF(LEFT(H31,4)="T102","TEMP",IF(LEFT(H31,4)="","NEW","NA")))))))))))</f>
+        <v>SRINAGAR</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="I31" s="6">
         <v>45962</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="6">
-        <v>45962</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="K31" s="5"/>
+      <c r="L31" s="6"/>
       <c r="M31" s="5" t="s">
         <v>23</v>
       </c>
@@ -3045,30 +3055,30 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F32" s="5"/>
-      <c r="G32" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>BARAMULLA</v>
+      <c r="G32" s="5" t="str">
+        <f>IF(LEFT(H32,4)="JK13","PULWAMA",IF(LEFT(H32,4)="JK01","SRINAGAR",IF(LEFT(H32,4)="JK04","BUDGAM",IF(LEFT(H32,4)="JK03","ANANTNAG",IF(LEFT(H32,4)="JK05","BARAMULLA",IF(LEFT(H32,4)="25BH","BHARAT",IF(LEFT(H32,4)="JK12","POONCH",IF(LEFT(H32,4)="JK18","KULGAM",IF(LEFT(H32,4)="JK22","SHOPIAN",IF(LEFT(H32,4)="T102","TEMP",IF(LEFT(H32,4)="","NEW","NA")))))))))))</f>
+        <v>TEMP</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I32" s="6">
         <v>45962</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="L32" s="6">
         <v>45962</v>
@@ -3086,32 +3096,40 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="F33" s="5"/>
-      <c r="G33" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>PULWAMA</v>
+      <c r="G33" s="5" t="str">
+        <f>IF(LEFT(H33,4)="JK13","PULWAMA",IF(LEFT(H33,4)="JK01","SRINAGAR",IF(LEFT(H33,4)="JK04","BUDGAM",IF(LEFT(H33,4)="JK03","ANANTNAG",IF(LEFT(H33,4)="JK05","BARAMULLA",IF(LEFT(H33,4)="25BH","BHARAT",IF(LEFT(H33,4)="JK12","POONCH",IF(LEFT(H33,4)="JK18","KULGAM",IF(LEFT(H33,4)="JK22","SHOPIAN",IF(LEFT(H33,4)="T102","TEMP",IF(LEFT(H33,4)="","NEW","NA")))))))))))</f>
+        <v>BARAMULLA</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="I33" s="6">
-        <v>45965</v>
+        <v>45962</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K33" s="13"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="K33" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="L33" s="6">
+        <v>45962</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N33" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
@@ -3119,34 +3137,30 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F34" s="5"/>
-      <c r="G34" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+      <c r="G34" s="5" t="str">
+        <f>IF(LEFT(H34,4)="JK13","PULWAMA",IF(LEFT(H34,4)="JK01","SRINAGAR",IF(LEFT(H34,4)="JK04","BUDGAM",IF(LEFT(H34,4)="JK03","ANANTNAG",IF(LEFT(H34,4)="JK05","BARAMULLA",IF(LEFT(H34,4)="25BH","BHARAT",IF(LEFT(H34,4)="JK12","POONCH",IF(LEFT(H34,4)="JK18","KULGAM",IF(LEFT(H34,4)="JK22","SHOPIAN",IF(LEFT(H34,4)="T102","TEMP",IF(LEFT(H34,4)="","NEW","NA")))))))))))</f>
+        <v>PULWAMA</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I34" s="6">
         <v>45965</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L34" s="6">
-        <v>45967</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="K34" s="14"/>
+      <c r="L34" s="6"/>
       <c r="M34" s="5"/>
       <c r="N34" s="4"/>
     </row>
@@ -3156,30 +3170,34 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="G35" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G35" s="5" t="str">
+        <f>IF(LEFT(H35,4)="JK13","PULWAMA",IF(LEFT(H35,4)="JK01","SRINAGAR",IF(LEFT(H35,4)="JK04","BUDGAM",IF(LEFT(H35,4)="JK03","ANANTNAG",IF(LEFT(H35,4)="JK05","BARAMULLA",IF(LEFT(H35,4)="25BH","BHARAT",IF(LEFT(H35,4)="JK12","POONCH",IF(LEFT(H35,4)="JK18","KULGAM",IF(LEFT(H35,4)="JK22","SHOPIAN",IF(LEFT(H35,4)="T102","TEMP",IF(LEFT(H35,4)="","NEW","NA")))))))))))</f>
         <v>SRINAGAR</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I35" s="6">
         <v>45965</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K35" s="5"/>
-      <c r="L35" s="6"/>
+        <v>107</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="L35" s="6">
+        <v>45967</v>
+      </c>
       <c r="M35" s="5"/>
       <c r="N35" s="4"/>
     </row>
@@ -3189,29 +3207,32 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="F36" s="5"/>
-      <c r="G36" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>KULGAM</v>
+      <c r="G36" s="5" t="str">
+        <f>IF(LEFT(H36,4)="JK13","PULWAMA",IF(LEFT(H36,4)="JK01","SRINAGAR",IF(LEFT(H36,4)="JK04","BUDGAM",IF(LEFT(H36,4)="JK03","ANANTNAG",IF(LEFT(H36,4)="JK05","BARAMULLA",IF(LEFT(H36,4)="25BH","BHARAT",IF(LEFT(H36,4)="JK12","POONCH",IF(LEFT(H36,4)="JK18","KULGAM",IF(LEFT(H36,4)="JK22","SHOPIAN",IF(LEFT(H36,4)="T102","TEMP",IF(LEFT(H36,4)="","NEW","NA")))))))))))</f>
+        <v>SRINAGAR</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="I36" s="6">
-        <v>45966</v>
+        <v>45965</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>139</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="K36" s="5"/>
       <c r="L36" s="6"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="4"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
@@ -3219,36 +3240,29 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="G37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>BUDGAM</v>
+      <c r="G37" s="5" t="str">
+        <f>IF(LEFT(H37,4)="JK13","PULWAMA",IF(LEFT(H37,4)="JK01","SRINAGAR",IF(LEFT(H37,4)="JK04","BUDGAM",IF(LEFT(H37,4)="JK03","ANANTNAG",IF(LEFT(H37,4)="JK05","BARAMULLA",IF(LEFT(H37,4)="25BH","BHARAT",IF(LEFT(H37,4)="JK12","POONCH",IF(LEFT(H37,4)="JK18","KULGAM",IF(LEFT(H37,4)="JK22","SHOPIAN",IF(LEFT(H37,4)="T102","TEMP",IF(LEFT(H37,4)="","NEW","NA")))))))))))</f>
+        <v>KULGAM</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I37" s="6">
         <v>45966</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="L37" s="6">
-        <v>45966</v>
-      </c>
-      <c r="M37" s="5"/>
-      <c r="N37" s="4"/>
+        <v>139</v>
+      </c>
+      <c r="L37" s="6"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
@@ -3256,30 +3270,34 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="F38" s="5"/>
-      <c r="G38" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G38" s="5" t="str">
+        <f>IF(LEFT(H38,4)="JK13","PULWAMA",IF(LEFT(H38,4)="JK01","SRINAGAR",IF(LEFT(H38,4)="JK04","BUDGAM",IF(LEFT(H38,4)="JK03","ANANTNAG",IF(LEFT(H38,4)="JK05","BARAMULLA",IF(LEFT(H38,4)="25BH","BHARAT",IF(LEFT(H38,4)="JK12","POONCH",IF(LEFT(H38,4)="JK18","KULGAM",IF(LEFT(H38,4)="JK22","SHOPIAN",IF(LEFT(H38,4)="T102","TEMP",IF(LEFT(H38,4)="","NEW","NA")))))))))))</f>
         <v>BUDGAM</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I38" s="6">
         <v>45966</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="K38" s="5"/>
-      <c r="L38" s="6"/>
+        <v>142</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="L38" s="6">
+        <v>45966</v>
+      </c>
       <c r="M38" s="5"/>
       <c r="N38" s="4"/>
     </row>
@@ -3287,33 +3305,29 @@
       <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>180</v>
-      </c>
+      <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="G39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>PULWAMA</v>
+        <v>101</v>
+      </c>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5" t="str">
+        <f>IF(LEFT(H39,4)="JK13","PULWAMA",IF(LEFT(H39,4)="JK01","SRINAGAR",IF(LEFT(H39,4)="JK04","BUDGAM",IF(LEFT(H39,4)="JK03","ANANTNAG",IF(LEFT(H39,4)="JK05","BARAMULLA",IF(LEFT(H39,4)="25BH","BHARAT",IF(LEFT(H39,4)="JK12","POONCH",IF(LEFT(H39,4)="JK18","KULGAM",IF(LEFT(H39,4)="JK22","SHOPIAN",IF(LEFT(H39,4)="T102","TEMP",IF(LEFT(H39,4)="","NEW","NA")))))))))))</f>
+        <v>BUDGAM</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I39" s="6">
         <v>45966</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>32</v>
+        <v>179</v>
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="6"/>
@@ -3325,32 +3339,32 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="G40" s="15" t="str">
-        <f t="shared" si="0"/>
+        <v>177</v>
+      </c>
+      <c r="G40" s="5" t="str">
+        <f>IF(LEFT(H40,4)="JK13","PULWAMA",IF(LEFT(H40,4)="JK01","SRINAGAR",IF(LEFT(H40,4)="JK04","BUDGAM",IF(LEFT(H40,4)="JK03","ANANTNAG",IF(LEFT(H40,4)="JK05","BARAMULLA",IF(LEFT(H40,4)="25BH","BHARAT",IF(LEFT(H40,4)="JK12","POONCH",IF(LEFT(H40,4)="JK18","KULGAM",IF(LEFT(H40,4)="JK22","SHOPIAN",IF(LEFT(H40,4)="T102","TEMP",IF(LEFT(H40,4)="","NEW","NA")))))))))))</f>
         <v>PULWAMA</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="I40" s="6">
-        <v>45967</v>
+        <v>45966</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
       <c r="K40" s="5"/>
       <c r="L40" s="6"/>
@@ -3362,13 +3376,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>31</v>
@@ -3376,12 +3390,12 @@
       <c r="F41" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="G41" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="G41" s="5" t="str">
+        <f>IF(LEFT(H41,4)="JK13","PULWAMA",IF(LEFT(H41,4)="JK01","SRINAGAR",IF(LEFT(H41,4)="JK04","BUDGAM",IF(LEFT(H41,4)="JK03","ANANTNAG",IF(LEFT(H41,4)="JK05","BARAMULLA",IF(LEFT(H41,4)="25BH","BHARAT",IF(LEFT(H41,4)="JK12","POONCH",IF(LEFT(H41,4)="JK18","KULGAM",IF(LEFT(H41,4)="JK22","SHOPIAN",IF(LEFT(H41,4)="T102","TEMP",IF(LEFT(H41,4)="","NEW","NA")))))))))))</f>
         <v>PULWAMA</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I41" s="6">
         <v>45967</v>
@@ -3399,39 +3413,35 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="G42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+        <v>178</v>
+      </c>
+      <c r="G42" s="5" t="str">
+        <f>IF(LEFT(H42,4)="JK13","PULWAMA",IF(LEFT(H42,4)="JK01","SRINAGAR",IF(LEFT(H42,4)="JK04","BUDGAM",IF(LEFT(H42,4)="JK03","ANANTNAG",IF(LEFT(H42,4)="JK05","BARAMULLA",IF(LEFT(H42,4)="25BH","BHARAT",IF(LEFT(H42,4)="JK12","POONCH",IF(LEFT(H42,4)="JK18","KULGAM",IF(LEFT(H42,4)="JK22","SHOPIAN",IF(LEFT(H42,4)="T102","TEMP",IF(LEFT(H42,4)="","NEW","NA")))))))))))</f>
+        <v>PULWAMA</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="I42" s="6">
         <v>45967</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="L42" s="6">
-        <v>45968</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="K42" s="5"/>
+      <c r="L42" s="6"/>
       <c r="M42" s="5"/>
       <c r="N42" s="4"/>
     </row>
@@ -3440,35 +3450,39 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G43" s="15" t="str">
-        <f t="shared" si="0"/>
+        <v>177</v>
+      </c>
+      <c r="G43" s="5" t="str">
+        <f>IF(LEFT(H43,4)="JK13","PULWAMA",IF(LEFT(H43,4)="JK01","SRINAGAR",IF(LEFT(H43,4)="JK04","BUDGAM",IF(LEFT(H43,4)="JK03","ANANTNAG",IF(LEFT(H43,4)="JK05","BARAMULLA",IF(LEFT(H43,4)="25BH","BHARAT",IF(LEFT(H43,4)="JK12","POONCH",IF(LEFT(H43,4)="JK18","KULGAM",IF(LEFT(H43,4)="JK22","SHOPIAN",IF(LEFT(H43,4)="T102","TEMP",IF(LEFT(H43,4)="","NEW","NA")))))))))))</f>
         <v>SRINAGAR</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="I43" s="6">
         <v>45967</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="6"/>
+        <v>75</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="L43" s="6">
+        <v>45968</v>
+      </c>
       <c r="M43" s="5"/>
       <c r="N43" s="4"/>
     </row>
@@ -3477,32 +3491,32 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="G44" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>POONCH</v>
+        <v>184</v>
+      </c>
+      <c r="G44" s="5" t="str">
+        <f>IF(LEFT(H44,4)="JK13","PULWAMA",IF(LEFT(H44,4)="JK01","SRINAGAR",IF(LEFT(H44,4)="JK04","BUDGAM",IF(LEFT(H44,4)="JK03","ANANTNAG",IF(LEFT(H44,4)="JK05","BARAMULLA",IF(LEFT(H44,4)="25BH","BHARAT",IF(LEFT(H44,4)="JK12","POONCH",IF(LEFT(H44,4)="JK18","KULGAM",IF(LEFT(H44,4)="JK22","SHOPIAN",IF(LEFT(H44,4)="T102","TEMP",IF(LEFT(H44,4)="","NEW","NA")))))))))))</f>
+        <v>SRINAGAR</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I44" s="6">
-        <v>45968</v>
+        <v>45967</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="6"/>
@@ -3514,32 +3528,32 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>196</v>
+        <v>31</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G45" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+        <v>203</v>
+      </c>
+      <c r="G45" s="5" t="str">
+        <f>IF(LEFT(H45,4)="JK13","PULWAMA",IF(LEFT(H45,4)="JK01","SRINAGAR",IF(LEFT(H45,4)="JK04","BUDGAM",IF(LEFT(H45,4)="JK03","ANANTNAG",IF(LEFT(H45,4)="JK05","BARAMULLA",IF(LEFT(H45,4)="25BH","BHARAT",IF(LEFT(H45,4)="JK12","POONCH",IF(LEFT(H45,4)="JK18","KULGAM",IF(LEFT(H45,4)="JK22","SHOPIAN",IF(LEFT(H45,4)="T102","TEMP",IF(LEFT(H45,4)="","NEW","NA")))))))))))</f>
+        <v>POONCH</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I45" s="6">
         <v>45968</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K45" s="5"/>
       <c r="L45" s="6"/>
@@ -3551,32 +3565,32 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>12</v>
+        <v>196</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G46" s="15" t="str">
-        <f t="shared" si="0"/>
+        <v>202</v>
+      </c>
+      <c r="G46" s="5" t="str">
+        <f>IF(LEFT(H46,4)="JK13","PULWAMA",IF(LEFT(H46,4)="JK01","SRINAGAR",IF(LEFT(H46,4)="JK04","BUDGAM",IF(LEFT(H46,4)="JK03","ANANTNAG",IF(LEFT(H46,4)="JK05","BARAMULLA",IF(LEFT(H46,4)="25BH","BHARAT",IF(LEFT(H46,4)="JK12","POONCH",IF(LEFT(H46,4)="JK18","KULGAM",IF(LEFT(H46,4)="JK22","SHOPIAN",IF(LEFT(H46,4)="T102","TEMP",IF(LEFT(H46,4)="","NEW","NA")))))))))))</f>
         <v>SRINAGAR</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I46" s="6">
         <v>45968</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>107</v>
+        <v>197</v>
       </c>
       <c r="K46" s="5"/>
       <c r="L46" s="6"/>
@@ -3588,29 +3602,33 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="G47" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>NEW</v>
-      </c>
-      <c r="H47" s="5"/>
+        <v>184</v>
+      </c>
+      <c r="G47" s="5" t="str">
+        <f>IF(LEFT(H47,4)="JK13","PULWAMA",IF(LEFT(H47,4)="JK01","SRINAGAR",IF(LEFT(H47,4)="JK04","BUDGAM",IF(LEFT(H47,4)="JK03","ANANTNAG",IF(LEFT(H47,4)="JK05","BARAMULLA",IF(LEFT(H47,4)="25BH","BHARAT",IF(LEFT(H47,4)="JK12","POONCH",IF(LEFT(H47,4)="JK18","KULGAM",IF(LEFT(H47,4)="JK22","SHOPIAN",IF(LEFT(H47,4)="T102","TEMP",IF(LEFT(H47,4)="","NEW","NA")))))))))))</f>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>205</v>
+      </c>
       <c r="I47" s="6">
         <v>45968</v>
       </c>
-      <c r="J47" s="5"/>
+      <c r="J47" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="K47" s="5"/>
       <c r="L47" s="6"/>
       <c r="M47" s="5"/>
@@ -3621,31 +3639,29 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>31</v>
+        <v>215</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="G48" s="15" t="str">
-        <f t="shared" si="0"/>
+        <v>177</v>
+      </c>
+      <c r="G48" s="5" t="str">
+        <f>IF(LEFT(H48,4)="JK13","PULWAMA",IF(LEFT(H48,4)="JK01","SRINAGAR",IF(LEFT(H48,4)="JK04","BUDGAM",IF(LEFT(H48,4)="JK03","ANANTNAG",IF(LEFT(H48,4)="JK05","BARAMULLA",IF(LEFT(H48,4)="25BH","BHARAT",IF(LEFT(H48,4)="JK12","POONCH",IF(LEFT(H48,4)="JK18","KULGAM",IF(LEFT(H48,4)="JK22","SHOPIAN",IF(LEFT(H48,4)="T102","TEMP",IF(LEFT(H48,4)="","NEW","NA")))))))))))</f>
         <v>NEW</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="6">
-        <v>45969</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>222</v>
-      </c>
+        <v>45968</v>
+      </c>
+      <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="6"/>
       <c r="M48" s="5"/>
@@ -3656,22 +3672,22 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G49" s="15" t="str">
-        <f t="shared" si="0"/>
+        <v>224</v>
+      </c>
+      <c r="G49" s="5" t="str">
+        <f>IF(LEFT(H49,4)="JK13","PULWAMA",IF(LEFT(H49,4)="JK01","SRINAGAR",IF(LEFT(H49,4)="JK04","BUDGAM",IF(LEFT(H49,4)="JK03","ANANTNAG",IF(LEFT(H49,4)="JK05","BARAMULLA",IF(LEFT(H49,4)="25BH","BHARAT",IF(LEFT(H49,4)="JK12","POONCH",IF(LEFT(H49,4)="JK18","KULGAM",IF(LEFT(H49,4)="JK22","SHOPIAN",IF(LEFT(H49,4)="T102","TEMP",IF(LEFT(H49,4)="","NEW","NA")))))))))))</f>
         <v>NEW</v>
       </c>
       <c r="H49" s="5"/>
@@ -3679,7 +3695,7 @@
         <v>45969</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K49" s="5"/>
       <c r="L49" s="6"/>
@@ -3690,13 +3706,32 @@
       <c r="A50" s="5">
         <v>49</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="15"/>
+      <c r="B50" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G50" s="5" t="str">
+        <f>IF(LEFT(H50,4)="JK13","PULWAMA",IF(LEFT(H50,4)="JK01","SRINAGAR",IF(LEFT(H50,4)="JK04","BUDGAM",IF(LEFT(H50,4)="JK03","ANANTNAG",IF(LEFT(H50,4)="JK05","BARAMULLA",IF(LEFT(H50,4)="25BH","BHARAT",IF(LEFT(H50,4)="JK12","POONCH",IF(LEFT(H50,4)="JK18","KULGAM",IF(LEFT(H50,4)="JK22","SHOPIAN",IF(LEFT(H50,4)="T102","TEMP",IF(LEFT(H50,4)="","NEW","NA")))))))))))</f>
+        <v>NEW</v>
+      </c>
       <c r="H50" s="5"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="5"/>
+      <c r="I50" s="6">
+        <v>45969</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>223</v>
+      </c>
       <c r="K50" s="5"/>
       <c r="L50" s="6"/>
       <c r="M50" s="5"/>
@@ -3711,7 +3746,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
-      <c r="G51" s="15"/>
+      <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="6"/>
       <c r="J51" s="5"/>
@@ -3729,7 +3764,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
-      <c r="G52" s="15"/>
+      <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="6"/>
       <c r="J52" s="5"/>
@@ -3747,7 +3782,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
-      <c r="G53" s="15"/>
+      <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="6"/>
       <c r="J53" s="5"/>
@@ -3765,7 +3800,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
-      <c r="G54" s="15"/>
+      <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="6"/>
       <c r="J54" s="5"/>
@@ -3783,7 +3818,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
-      <c r="G55" s="15"/>
+      <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="6"/>
       <c r="J55" s="5"/>
@@ -3801,7 +3836,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
-      <c r="G56" s="15"/>
+      <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="6"/>
       <c r="J56" s="5"/>
@@ -3819,7 +3854,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
-      <c r="G57" s="15"/>
+      <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="6"/>
       <c r="J57" s="5"/>
@@ -3837,7 +3872,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
-      <c r="G58" s="15"/>
+      <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="6"/>
       <c r="J58" s="5"/>
@@ -3855,7 +3890,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
-      <c r="G59" s="15"/>
+      <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="6"/>
       <c r="J59" s="5"/>
@@ -3873,7 +3908,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
-      <c r="G60" s="15"/>
+      <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="6"/>
       <c r="J60" s="5"/>
@@ -3891,7 +3926,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
-      <c r="G61" s="15"/>
+      <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="6"/>
       <c r="J61" s="5"/>
@@ -3909,7 +3944,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
-      <c r="G62" s="15"/>
+      <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="6"/>
       <c r="J62" s="5"/>
@@ -3927,7 +3962,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
-      <c r="G63" s="15"/>
+      <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="6"/>
       <c r="J63" s="5"/>
@@ -3945,7 +3980,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
-      <c r="G64" s="15"/>
+      <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="6"/>
       <c r="J64" s="5"/>
@@ -3963,7 +3998,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
-      <c r="G65" s="15"/>
+      <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="6"/>
       <c r="J65" s="5"/>
@@ -3981,7 +4016,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
-      <c r="G66" s="15"/>
+      <c r="G66" s="5"/>
       <c r="H66" s="5"/>
       <c r="I66" s="6"/>
       <c r="J66" s="5"/>
@@ -3999,7 +4034,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
-      <c r="G67" s="15"/>
+      <c r="G67" s="5"/>
       <c r="H67" s="5"/>
       <c r="I67" s="6"/>
       <c r="J67" s="5"/>
@@ -4017,7 +4052,7 @@
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
-      <c r="G68" s="15"/>
+      <c r="G68" s="5"/>
       <c r="H68" s="5"/>
       <c r="I68" s="6"/>
       <c r="J68" s="5"/>
@@ -4035,7 +4070,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
-      <c r="G69" s="15"/>
+      <c r="G69" s="5"/>
       <c r="H69" s="5"/>
       <c r="I69" s="6"/>
       <c r="J69" s="5"/>
@@ -4053,7 +4088,7 @@
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
-      <c r="G70" s="15"/>
+      <c r="G70" s="5"/>
       <c r="H70" s="5"/>
       <c r="I70" s="6"/>
       <c r="J70" s="5"/>
@@ -4071,7 +4106,7 @@
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
-      <c r="G71" s="15"/>
+      <c r="G71" s="5"/>
       <c r="H71" s="5"/>
       <c r="I71" s="6"/>
       <c r="J71" s="5"/>
@@ -4089,7 +4124,7 @@
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
-      <c r="G72" s="15"/>
+      <c r="G72" s="5"/>
       <c r="H72" s="5"/>
       <c r="I72" s="6"/>
       <c r="J72" s="5"/>
@@ -4107,7 +4142,7 @@
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
-      <c r="G73" s="15"/>
+      <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="6"/>
       <c r="J73" s="5"/>
@@ -4125,7 +4160,7 @@
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
-      <c r="G74" s="15"/>
+      <c r="G74" s="5"/>
       <c r="H74" s="5"/>
       <c r="I74" s="6"/>
       <c r="J74" s="5"/>
@@ -4143,7 +4178,7 @@
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
-      <c r="G75" s="15"/>
+      <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="6"/>
       <c r="J75" s="5"/>
@@ -4161,7 +4196,7 @@
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
-      <c r="G76" s="15"/>
+      <c r="G76" s="5"/>
       <c r="H76" s="5"/>
       <c r="I76" s="6"/>
       <c r="J76" s="5"/>
@@ -4179,7 +4214,7 @@
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
-      <c r="G77" s="15"/>
+      <c r="G77" s="5"/>
       <c r="H77" s="5"/>
       <c r="I77" s="6"/>
       <c r="J77" s="5"/>
@@ -4197,7 +4232,7 @@
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
-      <c r="G78" s="15"/>
+      <c r="G78" s="5"/>
       <c r="H78" s="5"/>
       <c r="I78" s="6"/>
       <c r="J78" s="5"/>
@@ -4215,7 +4250,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
-      <c r="G79" s="15"/>
+      <c r="G79" s="5"/>
       <c r="H79" s="5"/>
       <c r="I79" s="6"/>
       <c r="J79" s="5"/>
@@ -4233,7 +4268,7 @@
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
-      <c r="G80" s="15"/>
+      <c r="G80" s="5"/>
       <c r="H80" s="5"/>
       <c r="I80" s="6"/>
       <c r="J80" s="5"/>
@@ -4251,7 +4286,7 @@
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
       <c r="F81" s="5"/>
-      <c r="G81" s="15"/>
+      <c r="G81" s="5"/>
       <c r="H81" s="5"/>
       <c r="I81" s="6"/>
       <c r="J81" s="5"/>
@@ -4269,7 +4304,7 @@
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
-      <c r="G82" s="15"/>
+      <c r="G82" s="5"/>
       <c r="H82" s="5"/>
       <c r="I82" s="6"/>
       <c r="J82" s="5"/>
@@ -4287,7 +4322,7 @@
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
-      <c r="G83" s="15"/>
+      <c r="G83" s="5"/>
       <c r="H83" s="5"/>
       <c r="I83" s="6"/>
       <c r="J83" s="5"/>
@@ -4305,7 +4340,7 @@
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
-      <c r="G84" s="15"/>
+      <c r="G84" s="5"/>
       <c r="H84" s="5"/>
       <c r="I84" s="6"/>
       <c r="J84" s="5"/>
@@ -4323,7 +4358,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
-      <c r="G85" s="15"/>
+      <c r="G85" s="5"/>
       <c r="H85" s="5"/>
       <c r="I85" s="6"/>
       <c r="J85" s="5"/>
@@ -4341,7 +4376,7 @@
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
-      <c r="G86" s="15"/>
+      <c r="G86" s="5"/>
       <c r="H86" s="5"/>
       <c r="I86" s="6"/>
       <c r="J86" s="5"/>
@@ -4359,7 +4394,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
-      <c r="G87" s="15"/>
+      <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="6"/>
       <c r="J87" s="5"/>
@@ -4377,7 +4412,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
-      <c r="G88" s="15"/>
+      <c r="G88" s="5"/>
       <c r="H88" s="5"/>
       <c r="I88" s="6"/>
       <c r="J88" s="5"/>
@@ -4395,7 +4430,7 @@
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
-      <c r="G89" s="15"/>
+      <c r="G89" s="5"/>
       <c r="H89" s="5"/>
       <c r="I89" s="6"/>
       <c r="J89" s="5"/>
@@ -4413,7 +4448,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
-      <c r="G90" s="15"/>
+      <c r="G90" s="5"/>
       <c r="H90" s="5"/>
       <c r="I90" s="6"/>
       <c r="J90" s="5"/>
@@ -4431,7 +4466,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
-      <c r="G91" s="15"/>
+      <c r="G91" s="5"/>
       <c r="H91" s="5"/>
       <c r="I91" s="6"/>
       <c r="J91" s="5"/>
@@ -4449,7 +4484,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
-      <c r="G92" s="15"/>
+      <c r="G92" s="5"/>
       <c r="H92" s="5"/>
       <c r="I92" s="6"/>
       <c r="J92" s="5"/>
@@ -4467,7 +4502,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
-      <c r="G93" s="15"/>
+      <c r="G93" s="5"/>
       <c r="H93" s="5"/>
       <c r="I93" s="6"/>
       <c r="J93" s="5"/>
@@ -4485,7 +4520,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
-      <c r="G94" s="15"/>
+      <c r="G94" s="5"/>
       <c r="H94" s="5"/>
       <c r="I94" s="6"/>
       <c r="J94" s="5"/>
@@ -4503,7 +4538,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
-      <c r="G95" s="15"/>
+      <c r="G95" s="5"/>
       <c r="H95" s="5"/>
       <c r="I95" s="6"/>
       <c r="J95" s="5"/>
@@ -4521,7 +4556,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
-      <c r="G96" s="15"/>
+      <c r="G96" s="5"/>
       <c r="H96" s="5"/>
       <c r="I96" s="6"/>
       <c r="J96" s="5"/>
@@ -4539,7 +4574,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
-      <c r="G97" s="15"/>
+      <c r="G97" s="5"/>
       <c r="H97" s="5"/>
       <c r="I97" s="6"/>
       <c r="J97" s="5"/>
@@ -4557,7 +4592,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
-      <c r="G98" s="15"/>
+      <c r="G98" s="5"/>
       <c r="H98" s="5"/>
       <c r="I98" s="6"/>
       <c r="J98" s="5"/>
@@ -4575,7 +4610,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
-      <c r="G99" s="15"/>
+      <c r="G99" s="5"/>
       <c r="H99" s="5"/>
       <c r="I99" s="6"/>
       <c r="J99" s="5"/>
@@ -4593,7 +4628,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
       <c r="F100" s="5"/>
-      <c r="G100" s="15"/>
+      <c r="G100" s="5"/>
       <c r="H100" s="5"/>
       <c r="I100" s="6"/>
       <c r="J100" s="5"/>
@@ -4611,7 +4646,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5"/>
-      <c r="G101" s="15"/>
+      <c r="G101" s="5"/>
       <c r="H101" s="5"/>
       <c r="I101" s="6"/>
       <c r="J101" s="5"/>
@@ -4629,7 +4664,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
-      <c r="G102" s="15"/>
+      <c r="G102" s="5"/>
       <c r="H102" s="5"/>
       <c r="I102" s="6"/>
       <c r="J102" s="5"/>
@@ -4647,7 +4682,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
-      <c r="G103" s="15"/>
+      <c r="G103" s="5"/>
       <c r="H103" s="5"/>
       <c r="I103" s="6"/>
       <c r="J103" s="5"/>
@@ -4665,7 +4700,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
-      <c r="G104" s="15"/>
+      <c r="G104" s="5"/>
       <c r="H104" s="5"/>
       <c r="I104" s="6"/>
       <c r="J104" s="5"/>
@@ -4679,7 +4714,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="5"/>
-      <c r="G105" s="15"/>
+      <c r="G105" s="5"/>
       <c r="H105"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">

--- a/RegistrationsFile.xlsx
+++ b/RegistrationsFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63AF9978-3782-4297-A546-49CFAD0AF01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30B5D9A-B785-4371-8C92-33CCD4CAF739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="541" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="277">
   <si>
     <t>MODEL</t>
   </si>
@@ -724,6 +724,144 @@
   </si>
   <si>
     <t>JK25101566763596</t>
+  </si>
+  <si>
+    <t>JK25111052264658</t>
+  </si>
+  <si>
+    <t>MBHHWB13SSKB37812</t>
+  </si>
+  <si>
+    <t>FAYAZ AHMAD NAIK</t>
+  </si>
+  <si>
+    <t>MUZAFFAR PAALA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC GIVEN TO AAFAQ </t>
+  </si>
+  <si>
+    <t>JK01BC9898</t>
+  </si>
+  <si>
+    <t>JK22D2964</t>
+  </si>
+  <si>
+    <t>JK13K2103</t>
+  </si>
+  <si>
+    <t>JK13K2166</t>
+  </si>
+  <si>
+    <t>MBJTYKL1SSH335304</t>
+  </si>
+  <si>
+    <t>G VITARA SMTHYBRID DELTA</t>
+  </si>
+  <si>
+    <t>RAFIQ AHMAD MENGNOO</t>
+  </si>
+  <si>
+    <t>JK01BC3889</t>
+  </si>
+  <si>
+    <t>JK25101356269872</t>
+  </si>
+  <si>
+    <t>RC GIVEN TO CUSTOMER / ISHFAQ</t>
+  </si>
+  <si>
+    <t>SEERAT UL REHMAN</t>
+  </si>
+  <si>
+    <t>MBHHWB13SSKB38264</t>
+  </si>
+  <si>
+    <t>JK04K4119</t>
+  </si>
+  <si>
+    <t>RC GIVEN TO ISHFAQ FARASH</t>
+  </si>
+  <si>
+    <t>JK25110842109754</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSD468549</t>
+  </si>
+  <si>
+    <t>ZAHID AHMAD KANA</t>
+  </si>
+  <si>
+    <t>IGNIS ZETA AGS</t>
+  </si>
+  <si>
+    <t>JK01BC5755</t>
+  </si>
+  <si>
+    <t>JK25110832113304</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSC465330</t>
+  </si>
+  <si>
+    <t>GOWHAR AHMAD BHAT</t>
+  </si>
+  <si>
+    <t>JK13K2300</t>
+  </si>
+  <si>
+    <t>jk25110761965660</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSC466596</t>
+  </si>
+  <si>
+    <t>SANA ULLAH</t>
+  </si>
+  <si>
+    <t>JK12D7557</t>
+  </si>
+  <si>
+    <t>JK25110842087671</t>
+  </si>
+  <si>
+    <t>JK25111052346311</t>
+  </si>
+  <si>
+    <t>JK25111042344790</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSJ672358</t>
+  </si>
+  <si>
+    <t>MUDASIR AHMAD BHAT</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSK694930</t>
+  </si>
+  <si>
+    <t>WAJAHAT YOUNIS</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSK697949</t>
+  </si>
+  <si>
+    <t>DANISH MAJEED GANIE</t>
+  </si>
+  <si>
+    <t>JK25111062382368</t>
+  </si>
+  <si>
+    <t>JK18E1564</t>
+  </si>
+  <si>
+    <t>JK22D9903</t>
+  </si>
+  <si>
+    <t>JK18E1532</t>
+  </si>
+  <si>
+    <t>RC GIVEN TO IQBAL HABIB</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1393,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1931,7 +2069,7 @@
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="str">
-        <f>IF(LEFT(H2,4)="JK13","PULWAMA",IF(LEFT(H2,4)="JK01","SRINAGAR",IF(LEFT(H2,4)="JK04","BUDGAM",IF(LEFT(H2,4)="JK03","ANANTNAG",IF(LEFT(H2,4)="JK05","BARAMULLA",IF(LEFT(H2,4)="25BH","BHARAT",IF(LEFT(H2,4)="JK12","POONCH",IF(LEFT(H2,4)="JK18","KULGAM",IF(LEFT(H2,4)="JK22","SHOPIAN",IF(LEFT(H2,4)="T102","TEMP",IF(LEFT(H2,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" ref="G2:G33" si="0">IF(LEFT(H2,4)="JK13","PULWAMA",IF(LEFT(H2,4)="JK01","SRINAGAR",IF(LEFT(H2,4)="JK04","BUDGAM",IF(LEFT(H2,4)="JK03","ANANTNAG",IF(LEFT(H2,4)="JK05","BARAMULLA",IF(LEFT(H2,4)="25BH","BHARAT",IF(LEFT(H2,4)="JK12","POONCH",IF(LEFT(H2,4)="JK18","KULGAM",IF(LEFT(H2,4)="JK22","SHOPIAN",IF(LEFT(H2,4)="T102","TEMP",IF(LEFT(H2,4)="","NEW","NA")))))))))))</f>
         <v>SRINAGAR</v>
       </c>
       <c r="H2" s="5" t="s">
@@ -1968,7 +2106,7 @@
         <v>203</v>
       </c>
       <c r="G3" s="5" t="str">
-        <f>IF(LEFT(H3,4)="JK13","PULWAMA",IF(LEFT(H3,4)="JK01","SRINAGAR",IF(LEFT(H3,4)="JK04","BUDGAM",IF(LEFT(H3,4)="JK03","ANANTNAG",IF(LEFT(H3,4)="JK05","BARAMULLA",IF(LEFT(H3,4)="25BH","BHARAT",IF(LEFT(H3,4)="JK12","POONCH",IF(LEFT(H3,4)="JK18","KULGAM",IF(LEFT(H3,4)="JK22","SHOPIAN",IF(LEFT(H3,4)="T102","TEMP",IF(LEFT(H3,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="0"/>
         <v>BUDGAM</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -2005,7 +2143,7 @@
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="str">
-        <f>IF(LEFT(H4,4)="JK13","PULWAMA",IF(LEFT(H4,4)="JK01","SRINAGAR",IF(LEFT(H4,4)="JK04","BUDGAM",IF(LEFT(H4,4)="JK03","ANANTNAG",IF(LEFT(H4,4)="JK05","BARAMULLA",IF(LEFT(H4,4)="25BH","BHARAT",IF(LEFT(H4,4)="JK12","POONCH",IF(LEFT(H4,4)="JK18","KULGAM",IF(LEFT(H4,4)="JK22","SHOPIAN",IF(LEFT(H4,4)="T102","TEMP",IF(LEFT(H4,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="0"/>
         <v>BUDGAM</v>
       </c>
       <c r="H4" s="5" t="s">
@@ -2042,7 +2180,7 @@
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="str">
-        <f>IF(LEFT(H5,4)="JK13","PULWAMA",IF(LEFT(H5,4)="JK01","SRINAGAR",IF(LEFT(H5,4)="JK04","BUDGAM",IF(LEFT(H5,4)="JK03","ANANTNAG",IF(LEFT(H5,4)="JK05","BARAMULLA",IF(LEFT(H5,4)="25BH","BHARAT",IF(LEFT(H5,4)="JK12","POONCH",IF(LEFT(H5,4)="JK18","KULGAM",IF(LEFT(H5,4)="JK22","SHOPIAN",IF(LEFT(H5,4)="T102","TEMP",IF(LEFT(H5,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="0"/>
         <v>BUDGAM</v>
       </c>
       <c r="H5" s="5" t="s">
@@ -2079,7 +2217,7 @@
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="str">
-        <f>IF(LEFT(H6,4)="JK13","PULWAMA",IF(LEFT(H6,4)="JK01","SRINAGAR",IF(LEFT(H6,4)="JK04","BUDGAM",IF(LEFT(H6,4)="JK03","ANANTNAG",IF(LEFT(H6,4)="JK05","BARAMULLA",IF(LEFT(H6,4)="25BH","BHARAT",IF(LEFT(H6,4)="JK12","POONCH",IF(LEFT(H6,4)="JK18","KULGAM",IF(LEFT(H6,4)="JK22","SHOPIAN",IF(LEFT(H6,4)="T102","TEMP",IF(LEFT(H6,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="0"/>
         <v>SRINAGAR</v>
       </c>
       <c r="H6" s="5" t="s">
@@ -2116,7 +2254,7 @@
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="str">
-        <f>IF(LEFT(H7,4)="JK13","PULWAMA",IF(LEFT(H7,4)="JK01","SRINAGAR",IF(LEFT(H7,4)="JK04","BUDGAM",IF(LEFT(H7,4)="JK03","ANANTNAG",IF(LEFT(H7,4)="JK05","BARAMULLA",IF(LEFT(H7,4)="25BH","BHARAT",IF(LEFT(H7,4)="JK12","POONCH",IF(LEFT(H7,4)="JK18","KULGAM",IF(LEFT(H7,4)="JK22","SHOPIAN",IF(LEFT(H7,4)="T102","TEMP",IF(LEFT(H7,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="0"/>
         <v>SRINAGAR</v>
       </c>
       <c r="H7" s="5" t="s">
@@ -2157,7 +2295,7 @@
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="str">
-        <f>IF(LEFT(H8,4)="JK13","PULWAMA",IF(LEFT(H8,4)="JK01","SRINAGAR",IF(LEFT(H8,4)="JK04","BUDGAM",IF(LEFT(H8,4)="JK03","ANANTNAG",IF(LEFT(H8,4)="JK05","BARAMULLA",IF(LEFT(H8,4)="25BH","BHARAT",IF(LEFT(H8,4)="JK12","POONCH",IF(LEFT(H8,4)="JK18","KULGAM",IF(LEFT(H8,4)="JK22","SHOPIAN",IF(LEFT(H8,4)="T102","TEMP",IF(LEFT(H8,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="0"/>
         <v>PULWAMA</v>
       </c>
       <c r="H8" s="5" t="s">
@@ -2180,295 +2318,299 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5"/>
+        <v>51</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>244</v>
+      </c>
       <c r="C9" s="5" t="s">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>43</v>
+        <v>242</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F9" s="5"/>
+        <v>241</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>203</v>
+      </c>
       <c r="G9" s="5" t="str">
-        <f>IF(LEFT(H9,4)="JK13","PULWAMA",IF(LEFT(H9,4)="JK01","SRINAGAR",IF(LEFT(H9,4)="JK04","BUDGAM",IF(LEFT(H9,4)="JK03","ANANTNAG",IF(LEFT(H9,4)="JK05","BARAMULLA",IF(LEFT(H9,4)="25BH","BHARAT",IF(LEFT(H9,4)="JK12","POONCH",IF(LEFT(H9,4)="JK18","KULGAM",IF(LEFT(H9,4)="JK22","SHOPIAN",IF(LEFT(H9,4)="T102","TEMP",IF(LEFT(H9,4)="","NEW","NA")))))))))))</f>
-        <v>PULWAMA</v>
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>124</v>
+        <v>243</v>
       </c>
       <c r="I9" s="6">
-        <v>45944</v>
+        <v>45943</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>32</v>
+        <v>197</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>127</v>
+        <v>245</v>
       </c>
       <c r="L9" s="6">
-        <v>45966</v>
+        <v>45971</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="4"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="str">
-        <f>IF(LEFT(H10,4)="JK13","PULWAMA",IF(LEFT(H10,4)="JK01","SRINAGAR",IF(LEFT(H10,4)="JK04","BUDGAM",IF(LEFT(H10,4)="JK03","ANANTNAG",IF(LEFT(H10,4)="JK05","BARAMULLA",IF(LEFT(H10,4)="25BH","BHARAT",IF(LEFT(H10,4)="JK12","POONCH",IF(LEFT(H10,4)="JK18","KULGAM",IF(LEFT(H10,4)="JK22","SHOPIAN",IF(LEFT(H10,4)="T102","TEMP",IF(LEFT(H10,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="0"/>
         <v>PULWAMA</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="I10" s="6">
-        <v>45946</v>
+        <v>45944</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="L10" s="6">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="M10" s="5"/>
       <c r="N10" s="4"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>230</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
-        <v>227</v>
+        <v>84</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>228</v>
+        <v>83</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>229</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F11" s="5"/>
       <c r="G11" s="5" t="str">
-        <f>IF(LEFT(H11,4)="JK13","PULWAMA",IF(LEFT(H11,4)="JK01","SRINAGAR",IF(LEFT(H11,4)="JK04","BUDGAM",IF(LEFT(H11,4)="JK03","ANANTNAG",IF(LEFT(H11,4)="JK05","BARAMULLA",IF(LEFT(H11,4)="25BH","BHARAT",IF(LEFT(H11,4)="JK12","POONCH",IF(LEFT(H11,4)="JK18","KULGAM",IF(LEFT(H11,4)="JK22","SHOPIAN",IF(LEFT(H11,4)="T102","TEMP",IF(LEFT(H11,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="0"/>
         <v>PULWAMA</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="I11" s="6">
         <v>45946</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="L11" s="6">
-        <v>45971</v>
+        <v>45964</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="4"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>230</v>
+      </c>
       <c r="C12" s="5" t="s">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>149</v>
+        <v>228</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F12" s="5"/>
+        <v>215</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>229</v>
+      </c>
       <c r="G12" s="5" t="str">
-        <f>IF(LEFT(H12,4)="JK13","PULWAMA",IF(LEFT(H12,4)="JK01","SRINAGAR",IF(LEFT(H12,4)="JK04","BUDGAM",IF(LEFT(H12,4)="JK03","ANANTNAG",IF(LEFT(H12,4)="JK05","BARAMULLA",IF(LEFT(H12,4)="25BH","BHARAT",IF(LEFT(H12,4)="JK12","POONCH",IF(LEFT(H12,4)="JK18","KULGAM",IF(LEFT(H12,4)="JK22","SHOPIAN",IF(LEFT(H12,4)="T102","TEMP",IF(LEFT(H12,4)="","NEW","NA")))))))))))</f>
-        <v>SHOPIAN</v>
+        <f t="shared" si="0"/>
+        <v>PULWAMA</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="I12" s="6">
-        <v>45948</v>
+        <v>45946</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="L12" s="6">
-        <v>45966</v>
+        <v>45971</v>
       </c>
       <c r="M12" s="5"/>
       <c r="N12" s="4"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="str">
-        <f>IF(LEFT(H13,4)="JK13","PULWAMA",IF(LEFT(H13,4)="JK01","SRINAGAR",IF(LEFT(H13,4)="JK04","BUDGAM",IF(LEFT(H13,4)="JK03","ANANTNAG",IF(LEFT(H13,4)="JK05","BARAMULLA",IF(LEFT(H13,4)="25BH","BHARAT",IF(LEFT(H13,4)="JK12","POONCH",IF(LEFT(H13,4)="JK18","KULGAM",IF(LEFT(H13,4)="JK22","SHOPIAN",IF(LEFT(H13,4)="T102","TEMP",IF(LEFT(H13,4)="","NEW","NA")))))))))))</f>
-        <v>SRINAGAR</v>
+        <f t="shared" si="0"/>
+        <v>SHOPIAN</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="I13" s="6">
-        <v>45953</v>
-      </c>
-      <c r="J13" s="5"/>
+        <v>45948</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="K13" s="5" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="L13" s="6">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" s="4"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="str">
-        <f>IF(LEFT(H14,4)="JK13","PULWAMA",IF(LEFT(H14,4)="JK01","SRINAGAR",IF(LEFT(H14,4)="JK04","BUDGAM",IF(LEFT(H14,4)="JK03","ANANTNAG",IF(LEFT(H14,4)="JK05","BARAMULLA",IF(LEFT(H14,4)="25BH","BHARAT",IF(LEFT(H14,4)="JK12","POONCH",IF(LEFT(H14,4)="JK18","KULGAM",IF(LEFT(H14,4)="JK22","SHOPIAN",IF(LEFT(H14,4)="T102","TEMP",IF(LEFT(H14,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="0"/>
         <v>SRINAGAR</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="I14" s="6">
         <v>45953</v>
       </c>
-      <c r="J14" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="J14" s="5"/>
       <c r="K14" s="5" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="L14" s="6">
-        <v>45965</v>
+        <v>45964</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" s="4"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="str">
-        <f>IF(LEFT(H15,4)="JK13","PULWAMA",IF(LEFT(H15,4)="JK01","SRINAGAR",IF(LEFT(H15,4)="JK04","BUDGAM",IF(LEFT(H15,4)="JK03","ANANTNAG",IF(LEFT(H15,4)="JK05","BARAMULLA",IF(LEFT(H15,4)="25BH","BHARAT",IF(LEFT(H15,4)="JK12","POONCH",IF(LEFT(H15,4)="JK18","KULGAM",IF(LEFT(H15,4)="JK22","SHOPIAN",IF(LEFT(H15,4)="T102","TEMP",IF(LEFT(H15,4)="","NEW","NA")))))))))))</f>
-        <v>ANANTNAG</v>
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="I15" s="6">
         <v>45953</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="L15" s="6">
-        <v>45966</v>
+        <v>45965</v>
       </c>
       <c r="M15" s="5"/>
       <c r="N15" s="4"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="str">
-        <f>IF(LEFT(H16,4)="JK13","PULWAMA",IF(LEFT(H16,4)="JK01","SRINAGAR",IF(LEFT(H16,4)="JK04","BUDGAM",IF(LEFT(H16,4)="JK03","ANANTNAG",IF(LEFT(H16,4)="JK05","BARAMULLA",IF(LEFT(H16,4)="25BH","BHARAT",IF(LEFT(H16,4)="JK12","POONCH",IF(LEFT(H16,4)="JK18","KULGAM",IF(LEFT(H16,4)="JK22","SHOPIAN",IF(LEFT(H16,4)="T102","TEMP",IF(LEFT(H16,4)="","NEW","NA")))))))))))</f>
-        <v>PULWAMA</v>
+        <f t="shared" si="0"/>
+        <v>ANANTNAG</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I16" s="6">
-        <v>45954</v>
+        <v>45953</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>127</v>
+        <v>14</v>
       </c>
       <c r="L16" s="6">
         <v>45966</v>
@@ -2478,34 +2620,34 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="str">
-        <f>IF(LEFT(H17,4)="JK13","PULWAMA",IF(LEFT(H17,4)="JK01","SRINAGAR",IF(LEFT(H17,4)="JK04","BUDGAM",IF(LEFT(H17,4)="JK03","ANANTNAG",IF(LEFT(H17,4)="JK05","BARAMULLA",IF(LEFT(H17,4)="25BH","BHARAT",IF(LEFT(H17,4)="JK12","POONCH",IF(LEFT(H17,4)="JK18","KULGAM",IF(LEFT(H17,4)="JK22","SHOPIAN",IF(LEFT(H17,4)="T102","TEMP",IF(LEFT(H17,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="0"/>
         <v>PULWAMA</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="I17" s="6">
         <v>45954</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="L17" s="6">
         <v>45966</v>
@@ -2515,191 +2657,187 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="str">
-        <f>IF(LEFT(H18,4)="JK13","PULWAMA",IF(LEFT(H18,4)="JK01","SRINAGAR",IF(LEFT(H18,4)="JK04","BUDGAM",IF(LEFT(H18,4)="JK03","ANANTNAG",IF(LEFT(H18,4)="JK05","BARAMULLA",IF(LEFT(H18,4)="25BH","BHARAT",IF(LEFT(H18,4)="JK12","POONCH",IF(LEFT(H18,4)="JK18","KULGAM",IF(LEFT(H18,4)="JK22","SHOPIAN",IF(LEFT(H18,4)="T102","TEMP",IF(LEFT(H18,4)="","NEW","NA")))))))))))</f>
-        <v>SRINAGAR</v>
+        <f t="shared" si="0"/>
+        <v>PULWAMA</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="I18" s="6">
-        <v>45958</v>
+        <v>45954</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="L18" s="6">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="M18" s="5"/>
       <c r="N18" s="4"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="str">
-        <f>IF(LEFT(H19,4)="JK13","PULWAMA",IF(LEFT(H19,4)="JK01","SRINAGAR",IF(LEFT(H19,4)="JK04","BUDGAM",IF(LEFT(H19,4)="JK03","ANANTNAG",IF(LEFT(H19,4)="JK05","BARAMULLA",IF(LEFT(H19,4)="25BH","BHARAT",IF(LEFT(H19,4)="JK12","POONCH",IF(LEFT(H19,4)="JK18","KULGAM",IF(LEFT(H19,4)="JK22","SHOPIAN",IF(LEFT(H19,4)="T102","TEMP",IF(LEFT(H19,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="0"/>
         <v>SRINAGAR</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="I19" s="6">
-        <v>45959</v>
+        <v>45958</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="L19" s="6">
-        <v>45962</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N19" s="4">
-        <v>45959</v>
-      </c>
+        <v>45965</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="4"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
-        <v>186</v>
+        <v>60</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>187</v>
+        <v>59</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>184</v>
-      </c>
+      <c r="F20" s="5"/>
       <c r="G20" s="5" t="str">
-        <f>IF(LEFT(H20,4)="JK13","PULWAMA",IF(LEFT(H20,4)="JK01","SRINAGAR",IF(LEFT(H20,4)="JK04","BUDGAM",IF(LEFT(H20,4)="JK03","ANANTNAG",IF(LEFT(H20,4)="JK05","BARAMULLA",IF(LEFT(H20,4)="25BH","BHARAT",IF(LEFT(H20,4)="JK12","POONCH",IF(LEFT(H20,4)="JK18","KULGAM",IF(LEFT(H20,4)="JK22","SHOPIAN",IF(LEFT(H20,4)="T102","TEMP",IF(LEFT(H20,4)="","NEW","NA")))))))))))</f>
-        <v>BHARAT</v>
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>188</v>
+        <v>58</v>
       </c>
       <c r="I20" s="6">
         <v>45959</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="K20" s="5"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="6">
+        <v>45962</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N20" s="4">
+        <v>45959</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>22</v>
+        <v>187</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="G21" s="5" t="str">
-        <f>IF(LEFT(H21,4)="JK13","PULWAMA",IF(LEFT(H21,4)="JK01","SRINAGAR",IF(LEFT(H21,4)="JK04","BUDGAM",IF(LEFT(H21,4)="JK03","ANANTNAG",IF(LEFT(H21,4)="JK05","BARAMULLA",IF(LEFT(H21,4)="25BH","BHARAT",IF(LEFT(H21,4)="JK12","POONCH",IF(LEFT(H21,4)="JK18","KULGAM",IF(LEFT(H21,4)="JK22","SHOPIAN",IF(LEFT(H21,4)="T102","TEMP",IF(LEFT(H21,4)="","NEW","NA")))))))))))</f>
-        <v>SRINAGAR</v>
+        <f t="shared" si="0"/>
+        <v>BHARAT</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="I21" s="6">
-        <v>45960</v>
+        <v>45959</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L21" s="6">
-        <v>45961</v>
-      </c>
-      <c r="M21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N21" s="4">
-        <v>45960</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="K21" s="5"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="4"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="str">
-        <f>IF(LEFT(H22,4)="JK13","PULWAMA",IF(LEFT(H22,4)="JK01","SRINAGAR",IF(LEFT(H22,4)="JK04","BUDGAM",IF(LEFT(H22,4)="JK03","ANANTNAG",IF(LEFT(H22,4)="JK05","BARAMULLA",IF(LEFT(H22,4)="25BH","BHARAT",IF(LEFT(H22,4)="JK12","POONCH",IF(LEFT(H22,4)="JK18","KULGAM",IF(LEFT(H22,4)="JK22","SHOPIAN",IF(LEFT(H22,4)="T102","TEMP",IF(LEFT(H22,4)="","NEW","NA")))))))))))</f>
-        <v>BUDGAM</v>
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="I22" s="6">
         <v>45960</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="L22" s="6">
-        <v>45964</v>
+        <v>45961</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>23</v>
@@ -2710,112 +2848,116 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="str">
-        <f>IF(LEFT(H23,4)="JK13","PULWAMA",IF(LEFT(H23,4)="JK01","SRINAGAR",IF(LEFT(H23,4)="JK04","BUDGAM",IF(LEFT(H23,4)="JK03","ANANTNAG",IF(LEFT(H23,4)="JK05","BARAMULLA",IF(LEFT(H23,4)="25BH","BHARAT",IF(LEFT(H23,4)="JK12","POONCH",IF(LEFT(H23,4)="JK18","KULGAM",IF(LEFT(H23,4)="JK22","SHOPIAN",IF(LEFT(H23,4)="T102","TEMP",IF(LEFT(H23,4)="","NEW","NA")))))))))))</f>
-        <v>SRINAGAR</v>
+        <f t="shared" si="0"/>
+        <v>BUDGAM</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="I23" s="6">
         <v>45960</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="L23" s="6">
-        <v>45965</v>
-      </c>
-      <c r="M23" s="5"/>
-      <c r="N23" s="4"/>
+        <v>45964</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N23" s="4">
+        <v>45960</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
-        <v>2</v>
+        <v>118</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="str">
-        <f>IF(LEFT(H24,4)="JK13","PULWAMA",IF(LEFT(H24,4)="JK01","SRINAGAR",IF(LEFT(H24,4)="JK04","BUDGAM",IF(LEFT(H24,4)="JK03","ANANTNAG",IF(LEFT(H24,4)="JK05","BARAMULLA",IF(LEFT(H24,4)="25BH","BHARAT",IF(LEFT(H24,4)="JK12","POONCH",IF(LEFT(H24,4)="JK18","KULGAM",IF(LEFT(H24,4)="JK22","SHOPIAN",IF(LEFT(H24,4)="T102","TEMP",IF(LEFT(H24,4)="","NEW","NA")))))))))))</f>
-        <v>ANANTNAG</v>
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="I24" s="6">
-        <v>45961</v>
+        <v>45960</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="L24" s="6">
-        <v>45964</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N24" s="4">
-        <v>45961</v>
-      </c>
+        <v>45965</v>
+      </c>
+      <c r="M24" s="5"/>
+      <c r="N24" s="4"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="str">
-        <f>IF(LEFT(H25,4)="JK13","PULWAMA",IF(LEFT(H25,4)="JK01","SRINAGAR",IF(LEFT(H25,4)="JK04","BUDGAM",IF(LEFT(H25,4)="JK03","ANANTNAG",IF(LEFT(H25,4)="JK05","BARAMULLA",IF(LEFT(H25,4)="25BH","BHARAT",IF(LEFT(H25,4)="JK12","POONCH",IF(LEFT(H25,4)="JK18","KULGAM",IF(LEFT(H25,4)="JK22","SHOPIAN",IF(LEFT(H25,4)="T102","TEMP",IF(LEFT(H25,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="0"/>
         <v>ANANTNAG</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I25" s="6">
         <v>45961</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" s="5"/>
-      <c r="L25" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L25" s="6">
+        <v>45964</v>
+      </c>
       <c r="M25" s="5" t="s">
         <v>23</v>
       </c>
@@ -2825,25 +2967,25 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5" t="str">
-        <f>IF(LEFT(H26,4)="JK13","PULWAMA",IF(LEFT(H26,4)="JK01","SRINAGAR",IF(LEFT(H26,4)="JK04","BUDGAM",IF(LEFT(H26,4)="JK03","ANANTNAG",IF(LEFT(H26,4)="JK05","BARAMULLA",IF(LEFT(H26,4)="25BH","BHARAT",IF(LEFT(H26,4)="JK12","POONCH",IF(LEFT(H26,4)="JK18","KULGAM",IF(LEFT(H26,4)="JK22","SHOPIAN",IF(LEFT(H26,4)="T102","TEMP",IF(LEFT(H26,4)="","NEW","NA")))))))))))</f>
-        <v>KULGAM</v>
+        <f t="shared" si="0"/>
+        <v>ANANTNAG</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="I26" s="6">
         <v>45961</v>
@@ -2857,36 +2999,36 @@
         <v>23</v>
       </c>
       <c r="N26" s="4">
-        <v>45962</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="str">
-        <f>IF(LEFT(H27,4)="JK13","PULWAMA",IF(LEFT(H27,4)="JK01","SRINAGAR",IF(LEFT(H27,4)="JK04","BUDGAM",IF(LEFT(H27,4)="JK03","ANANTNAG",IF(LEFT(H27,4)="JK05","BARAMULLA",IF(LEFT(H27,4)="25BH","BHARAT",IF(LEFT(H27,4)="JK12","POONCH",IF(LEFT(H27,4)="JK18","KULGAM",IF(LEFT(H27,4)="JK22","SHOPIAN",IF(LEFT(H27,4)="T102","TEMP",IF(LEFT(H27,4)="","NEW","NA")))))))))))</f>
-        <v>PULWAMA</v>
+        <f t="shared" si="0"/>
+        <v>KULGAM</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I27" s="6">
         <v>45961</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="6"/>
@@ -2894,154 +3036,154 @@
         <v>23</v>
       </c>
       <c r="N27" s="4">
-        <v>45961</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5" t="str">
-        <f>IF(LEFT(H28,4)="JK13","PULWAMA",IF(LEFT(H28,4)="JK01","SRINAGAR",IF(LEFT(H28,4)="JK04","BUDGAM",IF(LEFT(H28,4)="JK03","ANANTNAG",IF(LEFT(H28,4)="JK05","BARAMULLA",IF(LEFT(H28,4)="25BH","BHARAT",IF(LEFT(H28,4)="JK12","POONCH",IF(LEFT(H28,4)="JK18","KULGAM",IF(LEFT(H28,4)="JK22","SHOPIAN",IF(LEFT(H28,4)="T102","TEMP",IF(LEFT(H28,4)="","NEW","NA")))))))))))</f>
-        <v>ANANTNAG</v>
+        <f t="shared" si="0"/>
+        <v>PULWAMA</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="I28" s="6">
         <v>45961</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L28" s="6">
-        <v>45966</v>
-      </c>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="K28" s="5"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N28" s="4">
+        <v>45961</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>144</v>
+        <v>35</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5" t="str">
-        <f>IF(LEFT(H29,4)="JK13","PULWAMA",IF(LEFT(H29,4)="JK01","SRINAGAR",IF(LEFT(H29,4)="JK04","BUDGAM",IF(LEFT(H29,4)="JK03","ANANTNAG",IF(LEFT(H29,4)="JK05","BARAMULLA",IF(LEFT(H29,4)="25BH","BHARAT",IF(LEFT(H29,4)="JK12","POONCH",IF(LEFT(H29,4)="JK18","KULGAM",IF(LEFT(H29,4)="JK22","SHOPIAN",IF(LEFT(H29,4)="T102","TEMP",IF(LEFT(H29,4)="","NEW","NA")))))))))))</f>
-        <v>BHARAT</v>
+        <f t="shared" si="0"/>
+        <v>ANANTNAG</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="I29" s="6">
         <v>45961</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="L29" s="6">
         <v>45966</v>
       </c>
-      <c r="M29" s="5"/>
-      <c r="N29" s="4"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5" t="str">
-        <f>IF(LEFT(H30,4)="JK13","PULWAMA",IF(LEFT(H30,4)="JK01","SRINAGAR",IF(LEFT(H30,4)="JK04","BUDGAM",IF(LEFT(H30,4)="JK03","ANANTNAG",IF(LEFT(H30,4)="JK05","BARAMULLA",IF(LEFT(H30,4)="25BH","BHARAT",IF(LEFT(H30,4)="JK12","POONCH",IF(LEFT(H30,4)="JK18","KULGAM",IF(LEFT(H30,4)="JK22","SHOPIAN",IF(LEFT(H30,4)="T102","TEMP",IF(LEFT(H30,4)="","NEW","NA")))))))))))</f>
-        <v>SRINAGAR</v>
+        <f t="shared" si="0"/>
+        <v>BHARAT</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>63</v>
+        <v>147</v>
       </c>
       <c r="I30" s="6">
-        <v>45962</v>
+        <v>45961</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="L30" s="6">
-        <v>45964</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N30" s="4">
-        <v>45962</v>
-      </c>
+        <v>45966</v>
+      </c>
+      <c r="M30" s="5"/>
+      <c r="N30" s="4"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="str">
-        <f>IF(LEFT(H31,4)="JK13","PULWAMA",IF(LEFT(H31,4)="JK01","SRINAGAR",IF(LEFT(H31,4)="JK04","BUDGAM",IF(LEFT(H31,4)="JK03","ANANTNAG",IF(LEFT(H31,4)="JK05","BARAMULLA",IF(LEFT(H31,4)="25BH","BHARAT",IF(LEFT(H31,4)="JK12","POONCH",IF(LEFT(H31,4)="JK18","KULGAM",IF(LEFT(H31,4)="JK22","SHOPIAN",IF(LEFT(H31,4)="T102","TEMP",IF(LEFT(H31,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="0"/>
         <v>SRINAGAR</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I31" s="6">
         <v>45962</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K31" s="5"/>
-      <c r="L31" s="6"/>
+        <v>75</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L31" s="6">
+        <v>45964</v>
+      </c>
       <c r="M31" s="5" t="s">
         <v>23</v>
       </c>
@@ -3051,38 +3193,34 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5" t="str">
-        <f>IF(LEFT(H32,4)="JK13","PULWAMA",IF(LEFT(H32,4)="JK01","SRINAGAR",IF(LEFT(H32,4)="JK04","BUDGAM",IF(LEFT(H32,4)="JK03","ANANTNAG",IF(LEFT(H32,4)="JK05","BARAMULLA",IF(LEFT(H32,4)="25BH","BHARAT",IF(LEFT(H32,4)="JK12","POONCH",IF(LEFT(H32,4)="JK18","KULGAM",IF(LEFT(H32,4)="JK22","SHOPIAN",IF(LEFT(H32,4)="T102","TEMP",IF(LEFT(H32,4)="","NEW","NA")))))))))))</f>
-        <v>TEMP</v>
+        <f t="shared" si="0"/>
+        <v>SRINAGAR</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="I32" s="6">
         <v>45962</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" s="6">
-        <v>45962</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="K32" s="5"/>
+      <c r="L32" s="6"/>
       <c r="M32" s="5" t="s">
         <v>23</v>
       </c>
@@ -3092,34 +3230,34 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="str">
-        <f>IF(LEFT(H33,4)="JK13","PULWAMA",IF(LEFT(H33,4)="JK01","SRINAGAR",IF(LEFT(H33,4)="JK04","BUDGAM",IF(LEFT(H33,4)="JK03","ANANTNAG",IF(LEFT(H33,4)="JK05","BARAMULLA",IF(LEFT(H33,4)="25BH","BHARAT",IF(LEFT(H33,4)="JK12","POONCH",IF(LEFT(H33,4)="JK18","KULGAM",IF(LEFT(H33,4)="JK22","SHOPIAN",IF(LEFT(H33,4)="T102","TEMP",IF(LEFT(H33,4)="","NEW","NA")))))))))))</f>
-        <v>BARAMULLA</v>
+        <f t="shared" si="0"/>
+        <v>TEMP</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I33" s="6">
         <v>45962</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="L33" s="6">
         <v>45962</v>
@@ -3133,238 +3271,242 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5" t="str">
-        <f>IF(LEFT(H34,4)="JK13","PULWAMA",IF(LEFT(H34,4)="JK01","SRINAGAR",IF(LEFT(H34,4)="JK04","BUDGAM",IF(LEFT(H34,4)="JK03","ANANTNAG",IF(LEFT(H34,4)="JK05","BARAMULLA",IF(LEFT(H34,4)="25BH","BHARAT",IF(LEFT(H34,4)="JK12","POONCH",IF(LEFT(H34,4)="JK18","KULGAM",IF(LEFT(H34,4)="JK22","SHOPIAN",IF(LEFT(H34,4)="T102","TEMP",IF(LEFT(H34,4)="","NEW","NA")))))))))))</f>
-        <v>PULWAMA</v>
+        <f t="shared" ref="G34:G56" si="1">IF(LEFT(H34,4)="JK13","PULWAMA",IF(LEFT(H34,4)="JK01","SRINAGAR",IF(LEFT(H34,4)="JK04","BUDGAM",IF(LEFT(H34,4)="JK03","ANANTNAG",IF(LEFT(H34,4)="JK05","BARAMULLA",IF(LEFT(H34,4)="25BH","BHARAT",IF(LEFT(H34,4)="JK12","POONCH",IF(LEFT(H34,4)="JK18","KULGAM",IF(LEFT(H34,4)="JK22","SHOPIAN",IF(LEFT(H34,4)="T102","TEMP",IF(LEFT(H34,4)="","NEW","NA")))))))))))</f>
+        <v>BARAMULLA</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="I34" s="6">
-        <v>45965</v>
+        <v>45962</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K34" s="14"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L34" s="6">
+        <v>45962</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N34" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5" t="str">
-        <f>IF(LEFT(H35,4)="JK13","PULWAMA",IF(LEFT(H35,4)="JK01","SRINAGAR",IF(LEFT(H35,4)="JK04","BUDGAM",IF(LEFT(H35,4)="JK03","ANANTNAG",IF(LEFT(H35,4)="JK05","BARAMULLA",IF(LEFT(H35,4)="25BH","BHARAT",IF(LEFT(H35,4)="JK12","POONCH",IF(LEFT(H35,4)="JK18","KULGAM",IF(LEFT(H35,4)="JK22","SHOPIAN",IF(LEFT(H35,4)="T102","TEMP",IF(LEFT(H35,4)="","NEW","NA")))))))))))</f>
-        <v>SRINAGAR</v>
+        <f t="shared" si="1"/>
+        <v>PULWAMA</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I35" s="6">
         <v>45965</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L35" s="6">
-        <v>45967</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="K35" s="5"/>
+      <c r="L35" s="6"/>
       <c r="M35" s="5"/>
       <c r="N35" s="4"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5" t="str">
-        <f>IF(LEFT(H36,4)="JK13","PULWAMA",IF(LEFT(H36,4)="JK01","SRINAGAR",IF(LEFT(H36,4)="JK04","BUDGAM",IF(LEFT(H36,4)="JK03","ANANTNAG",IF(LEFT(H36,4)="JK05","BARAMULLA",IF(LEFT(H36,4)="25BH","BHARAT",IF(LEFT(H36,4)="JK12","POONCH",IF(LEFT(H36,4)="JK18","KULGAM",IF(LEFT(H36,4)="JK22","SHOPIAN",IF(LEFT(H36,4)="T102","TEMP",IF(LEFT(H36,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="1"/>
         <v>SRINAGAR</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I36" s="6">
         <v>45965</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K36" s="5"/>
-      <c r="L36" s="6"/>
+        <v>107</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="L36" s="6">
+        <v>45967</v>
+      </c>
       <c r="M36" s="5"/>
       <c r="N36" s="4"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5" t="str">
-        <f>IF(LEFT(H37,4)="JK13","PULWAMA",IF(LEFT(H37,4)="JK01","SRINAGAR",IF(LEFT(H37,4)="JK04","BUDGAM",IF(LEFT(H37,4)="JK03","ANANTNAG",IF(LEFT(H37,4)="JK05","BARAMULLA",IF(LEFT(H37,4)="25BH","BHARAT",IF(LEFT(H37,4)="JK12","POONCH",IF(LEFT(H37,4)="JK18","KULGAM",IF(LEFT(H37,4)="JK22","SHOPIAN",IF(LEFT(H37,4)="T102","TEMP",IF(LEFT(H37,4)="","NEW","NA")))))))))))</f>
-        <v>KULGAM</v>
+        <f t="shared" si="1"/>
+        <v>SRINAGAR</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="I37" s="6">
-        <v>45966</v>
+        <v>45965</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>139</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="K37" s="5"/>
       <c r="L37" s="6"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="4"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5" t="str">
-        <f>IF(LEFT(H38,4)="JK13","PULWAMA",IF(LEFT(H38,4)="JK01","SRINAGAR",IF(LEFT(H38,4)="JK04","BUDGAM",IF(LEFT(H38,4)="JK03","ANANTNAG",IF(LEFT(H38,4)="JK05","BARAMULLA",IF(LEFT(H38,4)="25BH","BHARAT",IF(LEFT(H38,4)="JK12","POONCH",IF(LEFT(H38,4)="JK18","KULGAM",IF(LEFT(H38,4)="JK22","SHOPIAN",IF(LEFT(H38,4)="T102","TEMP",IF(LEFT(H38,4)="","NEW","NA")))))))))))</f>
-        <v>BUDGAM</v>
+        <f t="shared" si="1"/>
+        <v>KULGAM</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I38" s="6">
         <v>45966</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="L38" s="6">
-        <v>45966</v>
-      </c>
-      <c r="M38" s="5"/>
-      <c r="N38" s="4"/>
+        <v>139</v>
+      </c>
+      <c r="L38" s="6"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5" t="str">
-        <f>IF(LEFT(H39,4)="JK13","PULWAMA",IF(LEFT(H39,4)="JK01","SRINAGAR",IF(LEFT(H39,4)="JK04","BUDGAM",IF(LEFT(H39,4)="JK03","ANANTNAG",IF(LEFT(H39,4)="JK05","BARAMULLA",IF(LEFT(H39,4)="25BH","BHARAT",IF(LEFT(H39,4)="JK12","POONCH",IF(LEFT(H39,4)="JK18","KULGAM",IF(LEFT(H39,4)="JK22","SHOPIAN",IF(LEFT(H39,4)="T102","TEMP",IF(LEFT(H39,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="1"/>
         <v>BUDGAM</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I39" s="6">
         <v>45966</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="K39" s="5"/>
-      <c r="L39" s="6"/>
+        <v>142</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="L39" s="6">
+        <v>45966</v>
+      </c>
       <c r="M39" s="5"/>
       <c r="N39" s="4"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>39</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>180</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B40" s="5"/>
       <c r="C40" s="5" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>177</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="F40" s="5"/>
       <c r="G40" s="5" t="str">
-        <f>IF(LEFT(H40,4)="JK13","PULWAMA",IF(LEFT(H40,4)="JK01","SRINAGAR",IF(LEFT(H40,4)="JK04","BUDGAM",IF(LEFT(H40,4)="JK03","ANANTNAG",IF(LEFT(H40,4)="JK05","BARAMULLA",IF(LEFT(H40,4)="25BH","BHARAT",IF(LEFT(H40,4)="JK12","POONCH",IF(LEFT(H40,4)="JK18","KULGAM",IF(LEFT(H40,4)="JK22","SHOPIAN",IF(LEFT(H40,4)="T102","TEMP",IF(LEFT(H40,4)="","NEW","NA")))))))))))</f>
-        <v>PULWAMA</v>
+        <f t="shared" si="1"/>
+        <v>BUDGAM</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I40" s="6">
         <v>45966</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>32</v>
+        <v>179</v>
       </c>
       <c r="K40" s="5"/>
       <c r="L40" s="6"/>
@@ -3373,35 +3515,35 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G41" s="5" t="str">
-        <f>IF(LEFT(H41,4)="JK13","PULWAMA",IF(LEFT(H41,4)="JK01","SRINAGAR",IF(LEFT(H41,4)="JK04","BUDGAM",IF(LEFT(H41,4)="JK03","ANANTNAG",IF(LEFT(H41,4)="JK05","BARAMULLA",IF(LEFT(H41,4)="25BH","BHARAT",IF(LEFT(H41,4)="JK12","POONCH",IF(LEFT(H41,4)="JK18","KULGAM",IF(LEFT(H41,4)="JK22","SHOPIAN",IF(LEFT(H41,4)="T102","TEMP",IF(LEFT(H41,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="1"/>
         <v>PULWAMA</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="I41" s="6">
-        <v>45967</v>
+        <v>45966</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
       <c r="K41" s="5"/>
       <c r="L41" s="6"/>
@@ -3410,16 +3552,16 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>31</v>
@@ -3428,11 +3570,11 @@
         <v>178</v>
       </c>
       <c r="G42" s="5" t="str">
-        <f>IF(LEFT(H42,4)="JK13","PULWAMA",IF(LEFT(H42,4)="JK01","SRINAGAR",IF(LEFT(H42,4)="JK04","BUDGAM",IF(LEFT(H42,4)="JK03","ANANTNAG",IF(LEFT(H42,4)="JK05","BARAMULLA",IF(LEFT(H42,4)="25BH","BHARAT",IF(LEFT(H42,4)="JK12","POONCH",IF(LEFT(H42,4)="JK18","KULGAM",IF(LEFT(H42,4)="JK22","SHOPIAN",IF(LEFT(H42,4)="T102","TEMP",IF(LEFT(H42,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="1"/>
         <v>PULWAMA</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I42" s="6">
         <v>45967</v>
@@ -3440,120 +3582,128 @@
       <c r="J42" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="K42" s="5"/>
-      <c r="L42" s="6"/>
+      <c r="K42" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="L42" s="6">
+        <v>45971</v>
+      </c>
       <c r="M42" s="5"/>
       <c r="N42" s="4"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G43" s="5" t="str">
-        <f>IF(LEFT(H43,4)="JK13","PULWAMA",IF(LEFT(H43,4)="JK01","SRINAGAR",IF(LEFT(H43,4)="JK04","BUDGAM",IF(LEFT(H43,4)="JK03","ANANTNAG",IF(LEFT(H43,4)="JK05","BARAMULLA",IF(LEFT(H43,4)="25BH","BHARAT",IF(LEFT(H43,4)="JK12","POONCH",IF(LEFT(H43,4)="JK18","KULGAM",IF(LEFT(H43,4)="JK22","SHOPIAN",IF(LEFT(H43,4)="T102","TEMP",IF(LEFT(H43,4)="","NEW","NA")))))))))))</f>
-        <v>SRINAGAR</v>
+        <f t="shared" si="1"/>
+        <v>PULWAMA</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="I43" s="6">
         <v>45967</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>189</v>
+        <v>276</v>
       </c>
       <c r="L43" s="6">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="M43" s="5"/>
       <c r="N43" s="4"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G44" s="5" t="str">
-        <f>IF(LEFT(H44,4)="JK13","PULWAMA",IF(LEFT(H44,4)="JK01","SRINAGAR",IF(LEFT(H44,4)="JK04","BUDGAM",IF(LEFT(H44,4)="JK03","ANANTNAG",IF(LEFT(H44,4)="JK05","BARAMULLA",IF(LEFT(H44,4)="25BH","BHARAT",IF(LEFT(H44,4)="JK12","POONCH",IF(LEFT(H44,4)="JK18","KULGAM",IF(LEFT(H44,4)="JK22","SHOPIAN",IF(LEFT(H44,4)="T102","TEMP",IF(LEFT(H44,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="1"/>
         <v>SRINAGAR</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="I44" s="6">
         <v>45967</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="K44" s="5"/>
-      <c r="L44" s="6"/>
+        <v>75</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="L44" s="6">
+        <v>45968</v>
+      </c>
       <c r="M44" s="5"/>
       <c r="N44" s="4"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="G45" s="5" t="str">
-        <f>IF(LEFT(H45,4)="JK13","PULWAMA",IF(LEFT(H45,4)="JK01","SRINAGAR",IF(LEFT(H45,4)="JK04","BUDGAM",IF(LEFT(H45,4)="JK03","ANANTNAG",IF(LEFT(H45,4)="JK05","BARAMULLA",IF(LEFT(H45,4)="25BH","BHARAT",IF(LEFT(H45,4)="JK12","POONCH",IF(LEFT(H45,4)="JK18","KULGAM",IF(LEFT(H45,4)="JK22","SHOPIAN",IF(LEFT(H45,4)="T102","TEMP",IF(LEFT(H45,4)="","NEW","NA")))))))))))</f>
-        <v>POONCH</v>
+        <f t="shared" si="1"/>
+        <v>SRINAGAR</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I45" s="6">
-        <v>45968</v>
+        <v>45967</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="K45" s="5"/>
       <c r="L45" s="6"/>
@@ -3562,106 +3712,118 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>196</v>
+        <v>31</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G46" s="5" t="str">
-        <f>IF(LEFT(H46,4)="JK13","PULWAMA",IF(LEFT(H46,4)="JK01","SRINAGAR",IF(LEFT(H46,4)="JK04","BUDGAM",IF(LEFT(H46,4)="JK03","ANANTNAG",IF(LEFT(H46,4)="JK05","BARAMULLA",IF(LEFT(H46,4)="25BH","BHARAT",IF(LEFT(H46,4)="JK12","POONCH",IF(LEFT(H46,4)="JK18","KULGAM",IF(LEFT(H46,4)="JK22","SHOPIAN",IF(LEFT(H46,4)="T102","TEMP",IF(LEFT(H46,4)="","NEW","NA")))))))))))</f>
-        <v>SRINAGAR</v>
+        <f t="shared" si="1"/>
+        <v>POONCH</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I46" s="6">
         <v>45968</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="K46" s="5"/>
-      <c r="L46" s="6"/>
+        <v>198</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="L46" s="6">
+        <v>45971</v>
+      </c>
       <c r="M46" s="5"/>
       <c r="N46" s="4"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>12</v>
+        <v>196</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="G47" s="5" t="str">
-        <f>IF(LEFT(H47,4)="JK13","PULWAMA",IF(LEFT(H47,4)="JK01","SRINAGAR",IF(LEFT(H47,4)="JK04","BUDGAM",IF(LEFT(H47,4)="JK03","ANANTNAG",IF(LEFT(H47,4)="JK05","BARAMULLA",IF(LEFT(H47,4)="25BH","BHARAT",IF(LEFT(H47,4)="JK12","POONCH",IF(LEFT(H47,4)="JK18","KULGAM",IF(LEFT(H47,4)="JK22","SHOPIAN",IF(LEFT(H47,4)="T102","TEMP",IF(LEFT(H47,4)="","NEW","NA")))))))))))</f>
+        <f t="shared" si="1"/>
         <v>SRINAGAR</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I47" s="6">
         <v>45968</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="K47" s="5"/>
-      <c r="L47" s="6"/>
+        <v>197</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="L47" s="6">
+        <v>45971</v>
+      </c>
       <c r="M47" s="5"/>
       <c r="N47" s="4"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="G48" s="5" t="str">
-        <f>IF(LEFT(H48,4)="JK13","PULWAMA",IF(LEFT(H48,4)="JK01","SRINAGAR",IF(LEFT(H48,4)="JK04","BUDGAM",IF(LEFT(H48,4)="JK03","ANANTNAG",IF(LEFT(H48,4)="JK05","BARAMULLA",IF(LEFT(H48,4)="25BH","BHARAT",IF(LEFT(H48,4)="JK12","POONCH",IF(LEFT(H48,4)="JK18","KULGAM",IF(LEFT(H48,4)="JK22","SHOPIAN",IF(LEFT(H48,4)="T102","TEMP",IF(LEFT(H48,4)="","NEW","NA")))))))))))</f>
-        <v>NEW</v>
-      </c>
-      <c r="H48" s="5"/>
+        <f t="shared" si="1"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>205</v>
+      </c>
       <c r="I48" s="6">
         <v>45968</v>
       </c>
-      <c r="J48" s="5"/>
+      <c r="J48" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="K48" s="5"/>
       <c r="L48" s="6"/>
       <c r="M48" s="5"/>
@@ -3669,34 +3831,34 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>31</v>
+        <v>215</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>224</v>
+        <v>177</v>
       </c>
       <c r="G49" s="5" t="str">
-        <f>IF(LEFT(H49,4)="JK13","PULWAMA",IF(LEFT(H49,4)="JK01","SRINAGAR",IF(LEFT(H49,4)="JK04","BUDGAM",IF(LEFT(H49,4)="JK03","ANANTNAG",IF(LEFT(H49,4)="JK05","BARAMULLA",IF(LEFT(H49,4)="25BH","BHARAT",IF(LEFT(H49,4)="JK12","POONCH",IF(LEFT(H49,4)="JK18","KULGAM",IF(LEFT(H49,4)="JK22","SHOPIAN",IF(LEFT(H49,4)="T102","TEMP",IF(LEFT(H49,4)="","NEW","NA")))))))))))</f>
-        <v>NEW</v>
-      </c>
-      <c r="H49" s="5"/>
+        <f t="shared" si="1"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>236</v>
+      </c>
       <c r="I49" s="6">
-        <v>45969</v>
-      </c>
-      <c r="J49" s="5" t="s">
-        <v>222</v>
-      </c>
+        <v>45968</v>
+      </c>
+      <c r="J49" s="5"/>
       <c r="K49" s="5"/>
       <c r="L49" s="6"/>
       <c r="M49" s="5"/>
@@ -3704,34 +3866,34 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>217</v>
+        <v>259</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>221</v>
+        <v>261</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="G50" s="5" t="str">
-        <f>IF(LEFT(H50,4)="JK13","PULWAMA",IF(LEFT(H50,4)="JK01","SRINAGAR",IF(LEFT(H50,4)="JK04","BUDGAM",IF(LEFT(H50,4)="JK03","ANANTNAG",IF(LEFT(H50,4)="JK05","BARAMULLA",IF(LEFT(H50,4)="25BH","BHARAT",IF(LEFT(H50,4)="JK12","POONCH",IF(LEFT(H50,4)="JK18","KULGAM",IF(LEFT(H50,4)="JK22","SHOPIAN",IF(LEFT(H50,4)="T102","TEMP",IF(LEFT(H50,4)="","NEW","NA")))))))))))</f>
-        <v>NEW</v>
-      </c>
-      <c r="H50" s="5"/>
+        <f t="shared" si="1"/>
+        <v>POONCH</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>262</v>
+      </c>
       <c r="I50" s="6">
-        <v>45969</v>
-      </c>
-      <c r="J50" s="5" t="s">
-        <v>223</v>
-      </c>
+        <v>45968</v>
+      </c>
+      <c r="J50" s="5"/>
       <c r="K50" s="5"/>
       <c r="L50" s="6"/>
       <c r="M50" s="5"/>
@@ -3739,17 +3901,36 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
-        <v>50</v>
-      </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="5"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="G51" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="I51" s="6">
+        <v>45969</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>222</v>
+      </c>
       <c r="K51" s="5"/>
       <c r="L51" s="6"/>
       <c r="M51" s="5"/>
@@ -3757,17 +3938,36 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
-        <v>51</v>
-      </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="5"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G52" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="I52" s="6">
+        <v>45969</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>223</v>
+      </c>
       <c r="K52" s="5"/>
       <c r="L52" s="6"/>
       <c r="M52" s="5"/>
@@ -3777,14 +3977,31 @@
       <c r="A53" s="5">
         <v>52</v>
       </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="6"/>
+      <c r="B53" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G53" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>BUDGAM</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="I53" s="6">
+        <v>45969</v>
+      </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="6"/>
@@ -3795,15 +4012,34 @@
       <c r="A54" s="5">
         <v>53</v>
       </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="5"/>
+      <c r="B54" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G54" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>SRINAGAR</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="I54" s="6">
+        <v>45969</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="K54" s="5"/>
       <c r="L54" s="6"/>
       <c r="M54" s="5"/>
@@ -3813,15 +4049,34 @@
       <c r="A55" s="5">
         <v>54</v>
       </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="5"/>
+      <c r="B55" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G55" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="I55" s="6">
+        <v>45969</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="K55" s="5"/>
       <c r="L55" s="6"/>
       <c r="M55" s="5"/>
@@ -3829,17 +4084,36 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>55</v>
-      </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G56" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>SHOPIAN</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I56" s="6">
+        <v>45971</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>234</v>
+      </c>
       <c r="K56" s="5"/>
       <c r="L56" s="6"/>
       <c r="M56" s="5"/>
@@ -3849,15 +4123,34 @@
       <c r="A57" s="5">
         <v>56</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="5"/>
+      <c r="B57" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G57" s="5" t="str">
+        <f t="shared" ref="G57:G59" si="2">IF(LEFT(H57,4)="JK13","PULWAMA",IF(LEFT(H57,4)="JK01","SRINAGAR",IF(LEFT(H57,4)="JK04","BUDGAM",IF(LEFT(H57,4)="JK03","ANANTNAG",IF(LEFT(H57,4)="JK05","BARAMULLA",IF(LEFT(H57,4)="25BH","BHARAT",IF(LEFT(H57,4)="JK12","POONCH",IF(LEFT(H57,4)="JK18","KULGAM",IF(LEFT(H57,4)="JK22","SHOPIAN",IF(LEFT(H57,4)="T102","TEMP",IF(LEFT(H57,4)="","NEW","NA")))))))))))</f>
+        <v>KULGAM</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="I57" s="6">
+        <v>45971</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="K57" s="5"/>
       <c r="L57" s="6"/>
       <c r="M57" s="5"/>
@@ -3867,15 +4160,34 @@
       <c r="A58" s="5">
         <v>57</v>
       </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="5"/>
+      <c r="B58" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G58" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>SHOPIAN</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="I58" s="6">
+        <v>45971</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="K58" s="5"/>
       <c r="L58" s="6"/>
       <c r="M58" s="5"/>
@@ -3885,15 +4197,34 @@
       <c r="A59" s="5">
         <v>58</v>
       </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="5"/>
+      <c r="B59" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G59" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>KULGAM</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="I59" s="14">
+        <v>45971</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="K59" s="5"/>
       <c r="L59" s="6"/>
       <c r="M59" s="5"/>
@@ -3910,7 +4241,7 @@
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
-      <c r="I60" s="6"/>
+      <c r="I60" s="5"/>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
       <c r="L60" s="6"/>
@@ -3928,7 +4259,7 @@
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
-      <c r="I61" s="6"/>
+      <c r="I61" s="5"/>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
       <c r="L61" s="6"/>
@@ -3946,7 +4277,7 @@
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
-      <c r="I62" s="6"/>
+      <c r="I62" s="5"/>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
       <c r="L62" s="6"/>
@@ -3964,7 +4295,7 @@
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
-      <c r="I63" s="6"/>
+      <c r="I63" s="5"/>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
       <c r="L63" s="6"/>
@@ -3982,7 +4313,7 @@
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
-      <c r="I64" s="6"/>
+      <c r="I64" s="5"/>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
       <c r="L64" s="6"/>

--- a/RegistrationsFile.xlsx
+++ b/RegistrationsFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30B5D9A-B785-4371-8C92-33CCD4CAF739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46CDBEF-F6C8-4039-8FD2-029BEDB1C26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="541" xr2:uid="{13BF68A9-1632-47C2-86C0-81DADC7FF2BD}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="320">
   <si>
     <t>MODEL</t>
   </si>
@@ -862,6 +862,135 @@
   </si>
   <si>
     <t>RC GIVEN TO IQBAL HABIB</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSJ665481</t>
+  </si>
+  <si>
+    <t>AJAZ AHMAD DAR</t>
+  </si>
+  <si>
+    <t>JK13K1572</t>
+  </si>
+  <si>
+    <t>ASIF AFZAL</t>
+  </si>
+  <si>
+    <t>JK25100975400804</t>
+  </si>
+  <si>
+    <t>JK18E1356</t>
+  </si>
+  <si>
+    <t>MBHHWB13SSJB15932</t>
+  </si>
+  <si>
+    <t>MAHJOOR AHMAD NAJAR</t>
+  </si>
+  <si>
+    <t>BALENO ZETA</t>
+  </si>
+  <si>
+    <t>JK25102087909618</t>
+  </si>
+  <si>
+    <t>PDF SENT TO ASIF / MANINDER</t>
+  </si>
+  <si>
+    <t>JK25111152513327</t>
+  </si>
+  <si>
+    <t>JK25111162524093</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSJ668108</t>
+  </si>
+  <si>
+    <t>FAIZAN BASHIR MAGRAY</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSK479441</t>
+  </si>
+  <si>
+    <t>SONAYA AKHTER</t>
+  </si>
+  <si>
+    <t>IGNIS DELTA AGS</t>
+  </si>
+  <si>
+    <t>25BH7824P</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSK682356</t>
+  </si>
+  <si>
+    <t>TERSAM LAL</t>
+  </si>
+  <si>
+    <t>RC GIVEN TO MUNEER</t>
+  </si>
+  <si>
+    <t>JK03Q5551</t>
+  </si>
+  <si>
+    <t>JK13K2209</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSC465541</t>
+  </si>
+  <si>
+    <t>UZEMA JAN</t>
+  </si>
+  <si>
+    <t>JK25111142575605</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSJ476514</t>
+  </si>
+  <si>
+    <t>JK25111152603233</t>
+  </si>
+  <si>
+    <t>MURTIZA AKBAR</t>
+  </si>
+  <si>
+    <t>MBHHWB13SSKB37449</t>
+  </si>
+  <si>
+    <t>KIFAYAT ULLAH NAIK</t>
+  </si>
+  <si>
+    <t>JK25111192621804</t>
+  </si>
+  <si>
+    <t>SAJAD WANI</t>
+  </si>
+  <si>
+    <t>AMIR RASOOL</t>
+  </si>
+  <si>
+    <t>JK25111122621513</t>
+  </si>
+  <si>
+    <t>MA3NFG81SSG473441</t>
+  </si>
+  <si>
+    <t>AFTAB AHMED DAR</t>
+  </si>
+  <si>
+    <t>ABDUL RASHID MAGRAY</t>
+  </si>
+  <si>
+    <t>MBHKWD13SSH638616</t>
+  </si>
+  <si>
+    <t>JK25111122662689</t>
+  </si>
+  <si>
+    <t>JK22D2948</t>
+  </si>
+  <si>
+    <t>JK13K2225</t>
   </si>
 </sst>
 </file>
@@ -872,7 +1001,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d/mmm/yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd/mmm/yy;@"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1006,6 +1135,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1360,7 +1495,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1396,6 +1531,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1617,10 +1753,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97E63F84-BDFB-4C38-B1FD-28318E0D1D3F}" name="Table13" displayName="Table13" ref="A1:N105" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:N105" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N105">
-    <sortCondition ref="I1:I105"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97E63F84-BDFB-4C38-B1FD-28318E0D1D3F}" name="Table13" displayName="Table13" ref="A1:N104" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:N104" xr:uid="{73F7850A-6273-469C-B9BC-531FCF933FF2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N104">
+    <sortCondition ref="I1:I104"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{DEBB3640-E433-4779-93BC-95B8FB492623}" name="S.NO" dataDxfId="13"/>
@@ -1991,7 +2127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE94C64E-9B39-47CE-ACCD-DD5031A70035}">
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
@@ -2242,42 +2378,42 @@
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="5"/>
+      <c r="B7" s="5" t="s">
+        <v>281</v>
+      </c>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>277</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>27</v>
+        <v>278</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>202</v>
+      </c>
       <c r="G7" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+        <v>PULWAMA</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>25</v>
+        <v>279</v>
       </c>
       <c r="I7" s="6">
-        <v>45941</v>
+        <v>45939</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>26</v>
+        <v>280</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>26</v>
+        <v>287</v>
       </c>
       <c r="L7" s="6">
-        <v>45962</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" s="4">
-        <v>45973</v>
-      </c>
+        <v>45972</v>
+      </c>
+      <c r="M7" s="5"/>
+      <c r="N7" s="4"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
@@ -2285,128 +2421,132 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>PULWAMA</v>
+        <v>SRINAGAR</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="I8" s="6">
         <v>45941</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="6">
+        <v>45962</v>
+      </c>
       <c r="M8" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N8" s="4">
-        <v>45962</v>
+        <v>45973</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>51</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>244</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
-        <v>240</v>
+        <v>29</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>242</v>
+        <v>30</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>203</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="F9" s="5"/>
       <c r="G9" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+        <v>PULWAMA</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>243</v>
+        <v>65</v>
       </c>
       <c r="I9" s="6">
-        <v>45943</v>
+        <v>45941</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="L9" s="6">
-        <v>45971</v>
-      </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="K9" s="5"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>8</v>
-      </c>
-      <c r="B10" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>244</v>
+      </c>
       <c r="C10" s="5" t="s">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>43</v>
+        <v>242</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F10" s="5"/>
+        <v>241</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>203</v>
+      </c>
       <c r="G10" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>PULWAMA</v>
+        <v>SRINAGAR</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>124</v>
+        <v>243</v>
       </c>
       <c r="I10" s="6">
-        <v>45944</v>
+        <v>45943</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>32</v>
+        <v>197</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>127</v>
+        <v>245</v>
       </c>
       <c r="L10" s="6">
-        <v>45966</v>
+        <v>45971</v>
       </c>
       <c r="M10" s="5"/>
       <c r="N10" s="4"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="str">
@@ -2414,277 +2554,281 @@
         <v>PULWAMA</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="I11" s="6">
-        <v>45946</v>
+        <v>45944</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="L11" s="6">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="4"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>10</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>230</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>227</v>
+        <v>84</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>228</v>
+        <v>83</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>229</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F12" s="5"/>
       <c r="G12" s="5" t="str">
         <f t="shared" si="0"/>
         <v>PULWAMA</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="I12" s="6">
         <v>45946</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="L12" s="6">
-        <v>45971</v>
+        <v>45964</v>
       </c>
       <c r="M12" s="5"/>
       <c r="N12" s="4"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>11</v>
-      </c>
-      <c r="B13" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>230</v>
+      </c>
       <c r="C13" s="5" t="s">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>149</v>
+        <v>228</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F13" s="5"/>
+        <v>215</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>229</v>
+      </c>
       <c r="G13" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>SHOPIAN</v>
+        <v>PULWAMA</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="I13" s="6">
-        <v>45948</v>
+        <v>45946</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="L13" s="6">
-        <v>45966</v>
+        <v>45971</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" s="4"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+        <v>SHOPIAN</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="I14" s="6">
-        <v>45953</v>
-      </c>
-      <c r="J14" s="5"/>
+        <v>45948</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="K14" s="5" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="L14" s="6">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" s="4"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>13</v>
-      </c>
-      <c r="B15" s="5"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>286</v>
+      </c>
       <c r="C15" s="5" t="s">
-        <v>121</v>
+        <v>283</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>122</v>
+        <v>284</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="5"/>
+        <v>285</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>177</v>
+      </c>
       <c r="G15" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+        <v>KULGAM</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>123</v>
+        <v>282</v>
       </c>
       <c r="I15" s="6">
-        <v>45953</v>
+        <v>45950</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>26</v>
+        <v>280</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>26</v>
+        <v>287</v>
       </c>
       <c r="L15" s="6">
-        <v>45965</v>
+        <v>45972</v>
       </c>
       <c r="M15" s="5"/>
       <c r="N15" s="4"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>ANANTNAG</v>
+        <v>SRINAGAR</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="I16" s="6">
         <v>45953</v>
       </c>
-      <c r="J16" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="J16" s="5"/>
       <c r="K16" s="5" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="L16" s="6">
-        <v>45966</v>
+        <v>45964</v>
       </c>
       <c r="M16" s="5"/>
       <c r="N16" s="4"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>PULWAMA</v>
+        <v>SRINAGAR</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="I17" s="6">
-        <v>45954</v>
+        <v>45953</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="L17" s="6">
-        <v>45966</v>
+        <v>45965</v>
       </c>
       <c r="M17" s="5"/>
       <c r="N17" s="4"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>PULWAMA</v>
+        <v>ANANTNAG</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="I18" s="6">
-        <v>45954</v>
+        <v>45953</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>14</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="L18" s="6">
         <v>45966</v>
@@ -2694,14 +2838,14 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>5</v>
@@ -2709,115 +2853,113 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+        <v>PULWAMA</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="I19" s="6">
-        <v>45958</v>
+        <v>45954</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="L19" s="6">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="M19" s="5"/>
       <c r="N19" s="4"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>59</v>
+        <v>153</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+        <v>PULWAMA</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>58</v>
+        <v>154</v>
       </c>
       <c r="I20" s="6">
-        <v>45959</v>
+        <v>45954</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>61</v>
+        <v>159</v>
       </c>
       <c r="L20" s="6">
-        <v>45962</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N20" s="4">
-        <v>45959</v>
-      </c>
+        <v>45966</v>
+      </c>
+      <c r="M20" s="5"/>
+      <c r="N20" s="4"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
-        <v>186</v>
+        <v>109</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>184</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F21" s="5"/>
       <c r="G21" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>BHARAT</v>
+        <v>SRINAGAR</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>188</v>
+        <v>108</v>
       </c>
       <c r="I21" s="6">
-        <v>45959</v>
+        <v>45958</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="K21" s="5"/>
-      <c r="L21" s="6"/>
+        <v>111</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="L21" s="6">
+        <v>45965</v>
+      </c>
       <c r="M21" s="5"/>
       <c r="N21" s="4"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="str">
@@ -2825,101 +2967,97 @@
         <v>SRINAGAR</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="I22" s="6">
-        <v>45960</v>
+        <v>45959</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="L22" s="6">
-        <v>45961</v>
+        <v>45962</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N22" s="4">
-        <v>45960</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>73</v>
+        <v>186</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="5"/>
+      <c r="F23" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="G23" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>BUDGAM</v>
+        <v>BHARAT</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>72</v>
+        <v>188</v>
       </c>
       <c r="I23" s="6">
-        <v>45960</v>
+        <v>45959</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L23" s="6">
-        <v>45964</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N23" s="4">
-        <v>45960</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="K23" s="5"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="4"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
-        <v>118</v>
+        <v>296</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>119</v>
+        <v>297</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F24" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>203</v>
+      </c>
       <c r="G24" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+        <v>BHARAT</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="I24" s="6">
-        <v>45960</v>
+        <v>295</v>
+      </c>
+      <c r="I24" s="14">
+        <v>45959</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>26</v>
+        <v>298</v>
       </c>
       <c r="L24" s="6">
-        <v>45965</v>
+        <v>45972</v>
       </c>
       <c r="M24" s="5"/>
       <c r="N24" s="4"/>
@@ -2930,10 +3068,10 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>5</v>
@@ -2941,28 +3079,28 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>ANANTNAG</v>
+        <v>SRINAGAR</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I25" s="6">
+        <v>45960</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="6">
         <v>45961</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L25" s="6">
-        <v>45964</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N25" s="4">
-        <v>45961</v>
+        <v>45960</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2971,10 +3109,10 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>12</v>
@@ -2982,24 +3120,28 @@
       <c r="F26" s="5"/>
       <c r="G26" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>ANANTNAG</v>
+        <v>BUDGAM</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="I26" s="6">
-        <v>45961</v>
+        <v>45960</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K26" s="5"/>
-      <c r="L26" s="6"/>
+        <v>75</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L26" s="6">
+        <v>45964</v>
+      </c>
       <c r="M26" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N26" s="4">
-        <v>45961</v>
+        <v>45960</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -3008,36 +3150,36 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>KULGAM</v>
+        <v>SRINAGAR</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="I27" s="6">
-        <v>45961</v>
+        <v>45960</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K27" s="5"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N27" s="4">
-        <v>45962</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="6">
+        <v>45965</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="4"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
@@ -3045,30 +3187,34 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5" t="s">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>PULWAMA</v>
+        <v>ANANTNAG</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="I28" s="6">
         <v>45961</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K28" s="5"/>
-      <c r="L28" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L28" s="6">
+        <v>45964</v>
+      </c>
       <c r="M28" s="5" t="s">
         <v>23</v>
       </c>
@@ -3082,13 +3228,13 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5" t="str">
@@ -3096,7 +3242,7 @@
         <v>ANANTNAG</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="I29" s="6">
         <v>45961</v>
@@ -3104,14 +3250,14 @@
       <c r="J29" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L29" s="6">
-        <v>45966</v>
-      </c>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N29" s="4">
+        <v>45961</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
@@ -3119,36 +3265,36 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>144</v>
+        <v>33</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>146</v>
+        <v>31</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>BHARAT</v>
+        <v>KULGAM</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="I30" s="6">
         <v>45961</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="6">
-        <v>45966</v>
-      </c>
-      <c r="M30" s="5"/>
-      <c r="N30" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="K30" s="5"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N30" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
@@ -3156,39 +3302,35 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+        <v>PULWAMA</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I31" s="6">
-        <v>45962</v>
+        <v>45961</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="L31" s="6">
-        <v>45964</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="K31" s="5"/>
+      <c r="L31" s="6"/>
       <c r="M31" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N31" s="4">
-        <v>45962</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -3197,36 +3339,36 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>SRINAGAR</v>
+        <v>ANANTNAG</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="I32" s="6">
-        <v>45962</v>
+        <v>45961</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K32" s="5"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N32" s="4">
-        <v>45962</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L32" s="6">
+        <v>45966</v>
+      </c>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
@@ -3234,24 +3376,24 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
-        <v>53</v>
+        <v>144</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>TEMP</v>
+        <v>BHARAT</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>52</v>
+        <v>147</v>
       </c>
       <c r="I33" s="6">
-        <v>45962</v>
+        <v>45961</v>
       </c>
       <c r="J33" s="5" t="s">
         <v>26</v>
@@ -3260,14 +3402,10 @@
         <v>26</v>
       </c>
       <c r="L33" s="6">
-        <v>45962</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N33" s="4">
-        <v>45962</v>
-      </c>
+        <v>45966</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="4"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
@@ -3275,33 +3413,33 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5" t="str">
-        <f t="shared" ref="G34:G56" si="1">IF(LEFT(H34,4)="JK13","PULWAMA",IF(LEFT(H34,4)="JK01","SRINAGAR",IF(LEFT(H34,4)="JK04","BUDGAM",IF(LEFT(H34,4)="JK03","ANANTNAG",IF(LEFT(H34,4)="JK05","BARAMULLA",IF(LEFT(H34,4)="25BH","BHARAT",IF(LEFT(H34,4)="JK12","POONCH",IF(LEFT(H34,4)="JK18","KULGAM",IF(LEFT(H34,4)="JK22","SHOPIAN",IF(LEFT(H34,4)="T102","TEMP",IF(LEFT(H34,4)="","NEW","NA")))))))))))</f>
-        <v>BARAMULLA</v>
+        <f t="shared" ref="G34:G65" si="1">IF(LEFT(H34,4)="JK13","PULWAMA",IF(LEFT(H34,4)="JK01","SRINAGAR",IF(LEFT(H34,4)="JK04","BUDGAM",IF(LEFT(H34,4)="JK03","ANANTNAG",IF(LEFT(H34,4)="JK05","BARAMULLA",IF(LEFT(H34,4)="25BH","BHARAT",IF(LEFT(H34,4)="JK12","POONCH",IF(LEFT(H34,4)="JK18","KULGAM",IF(LEFT(H34,4)="JK22","SHOPIAN",IF(LEFT(H34,4)="T102","TEMP",IF(LEFT(H34,4)="","NEW","NA")))))))))))</f>
+        <v>SRINAGAR</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I34" s="6">
         <v>45962</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="L34" s="6">
-        <v>45962</v>
+        <v>45964</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>23</v>
@@ -3316,32 +3454,36 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>PULWAMA</v>
+        <v>SRINAGAR</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="I35" s="6">
-        <v>45965</v>
+        <v>45962</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="K35" s="5"/>
       <c r="L35" s="6"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="4"/>
+      <c r="M35" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N35" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
@@ -3349,36 +3491,40 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>SRINAGAR</v>
+        <v>TEMP</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="I36" s="6">
-        <v>45965</v>
+        <v>45962</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>162</v>
+        <v>26</v>
       </c>
       <c r="L36" s="6">
-        <v>45967</v>
-      </c>
-      <c r="M36" s="5"/>
-      <c r="N36" s="4"/>
+        <v>45962</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N36" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
@@ -3386,32 +3532,40 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>SRINAGAR</v>
+        <v>BARAMULLA</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="I37" s="6">
-        <v>45965</v>
+        <v>45962</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K37" s="5"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L37" s="6">
+        <v>45962</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N37" s="4">
+        <v>45962</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
@@ -3419,29 +3573,32 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>KULGAM</v>
+        <v>PULWAMA</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="I38" s="6">
-        <v>45966</v>
+        <v>45965</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>139</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="K38" s="5"/>
       <c r="L38" s="6"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="4"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
@@ -3449,33 +3606,33 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>BUDGAM</v>
+        <v>SRINAGAR</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="I39" s="6">
-        <v>45966</v>
+        <v>45965</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L39" s="6">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="4"/>
@@ -3486,27 +3643,27 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>BUDGAM</v>
+        <v>SRINAGAR</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>155</v>
+        <v>106</v>
       </c>
       <c r="I40" s="6">
-        <v>45966</v>
+        <v>45965</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>179</v>
+        <v>32</v>
       </c>
       <c r="K40" s="5"/>
       <c r="L40" s="6"/>
@@ -3517,76 +3674,65 @@
       <c r="A41" s="5">
         <v>39</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>180</v>
-      </c>
+      <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>177</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F41" s="5"/>
       <c r="G41" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>PULWAMA</v>
+        <v>KULGAM</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="I41" s="6">
         <v>45966</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K41" s="5"/>
+        <v>139</v>
+      </c>
       <c r="L41" s="6"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="4"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>40</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>169</v>
-      </c>
+      <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>178</v>
-      </c>
+      <c r="F42" s="5"/>
       <c r="G42" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>PULWAMA</v>
+        <v>BUDGAM</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="I42" s="6">
-        <v>45967</v>
+        <v>45966</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>276</v>
+        <v>161</v>
       </c>
       <c r="L42" s="6">
-        <v>45971</v>
+        <v>45966</v>
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="4"/>
@@ -3595,40 +3741,32 @@
       <c r="A43" s="5">
         <v>41</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>170</v>
-      </c>
+      <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>178</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="F43" s="5"/>
       <c r="G43" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>PULWAMA</v>
+        <v>BUDGAM</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="I43" s="6">
-        <v>45967</v>
+        <v>45966</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="L43" s="6">
-        <v>45971</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="K43" s="5"/>
+      <c r="L43" s="6"/>
       <c r="M43" s="5"/>
       <c r="N43" s="4"/>
     </row>
@@ -3637,39 +3775,35 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>177</v>
       </c>
       <c r="G44" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>SRINAGAR</v>
+        <v>PULWAMA</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="I44" s="6">
-        <v>45967</v>
+        <v>45966</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="K44" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="L44" s="6">
-        <v>45968</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="K44" s="5"/>
+      <c r="L44" s="6"/>
       <c r="M44" s="5"/>
       <c r="N44" s="4"/>
     </row>
@@ -3678,35 +3812,39 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G45" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>SRINAGAR</v>
+        <v>PULWAMA</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>207</v>
+        <v>171</v>
       </c>
       <c r="I45" s="6">
         <v>45967</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="K45" s="5"/>
-      <c r="L45" s="6"/>
+        <v>167</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="L45" s="6">
+        <v>45971</v>
+      </c>
       <c r="M45" s="5"/>
       <c r="N45" s="4"/>
     </row>
@@ -3715,35 +3853,35 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="G46" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>POONCH</v>
+        <v>PULWAMA</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>206</v>
+        <v>172</v>
       </c>
       <c r="I46" s="6">
-        <v>45968</v>
+        <v>45967</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>235</v>
+        <v>276</v>
       </c>
       <c r="L46" s="6">
         <v>45971</v>
@@ -3756,38 +3894,38 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>196</v>
+        <v>31</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="G47" s="5" t="str">
         <f t="shared" si="1"/>
         <v>SRINAGAR</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="I47" s="6">
+        <v>45967</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="L47" s="6">
         <v>45968</v>
-      </c>
-      <c r="J47" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="K47" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="L47" s="6">
-        <v>45971</v>
       </c>
       <c r="M47" s="5"/>
       <c r="N47" s="4"/>
@@ -3797,16 +3935,16 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>184</v>
@@ -3816,13 +3954,13 @@
         <v>SRINAGAR</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I48" s="6">
-        <v>45968</v>
+        <v>45967</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="K48" s="5"/>
       <c r="L48" s="6"/>
@@ -3834,102 +3972,114 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>215</v>
+        <v>31</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="G49" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>SRINAGAR</v>
+        <v>POONCH</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="I49" s="6">
         <v>45968</v>
       </c>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="6"/>
+      <c r="J49" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="L49" s="6">
+        <v>45971</v>
+      </c>
       <c r="M49" s="5"/>
       <c r="N49" s="4"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>259</v>
+        <v>195</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>261</v>
+        <v>193</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>31</v>
+        <v>196</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="G50" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>POONCH</v>
+        <v>SRINAGAR</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>262</v>
+        <v>204</v>
       </c>
       <c r="I50" s="6">
         <v>45968</v>
       </c>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="6"/>
+      <c r="J50" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="L50" s="6">
+        <v>45971</v>
+      </c>
       <c r="M50" s="5"/>
       <c r="N50" s="4"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="G51" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>PULWAMA</v>
+        <v>SRINAGAR</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="I51" s="6">
-        <v>45969</v>
+        <v>45968</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>222</v>
+        <v>107</v>
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="6"/>
@@ -3938,36 +4088,34 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>31</v>
+        <v>215</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="G52" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>PULWAMA</v>
+        <v>SRINAGAR</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I52" s="6">
-        <v>45969</v>
-      </c>
-      <c r="J52" s="5" t="s">
-        <v>223</v>
-      </c>
+        <v>45968</v>
+      </c>
+      <c r="J52" s="5"/>
       <c r="K52" s="5"/>
       <c r="L52" s="6"/>
       <c r="M52" s="5"/>
@@ -3975,32 +4123,32 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="G53" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>BUDGAM</v>
+        <v>POONCH</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I53" s="6">
-        <v>45969</v>
+        <v>45968</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
@@ -4010,35 +4158,35 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>253</v>
+        <v>31</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="G54" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>SRINAGAR</v>
+        <v>PULWAMA</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="I54" s="6">
         <v>45969</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>167</v>
+        <v>222</v>
       </c>
       <c r="K54" s="5"/>
       <c r="L54" s="6"/>
@@ -4047,35 +4195,35 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>255</v>
+        <v>217</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>256</v>
+        <v>219</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="G55" s="5" t="str">
         <f t="shared" si="1"/>
         <v>PULWAMA</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="I55" s="6">
         <v>45969</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>167</v>
+        <v>223</v>
       </c>
       <c r="K55" s="5"/>
       <c r="L55" s="6"/>
@@ -4084,72 +4232,76 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>203</v>
       </c>
       <c r="G56" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>SHOPIAN</v>
+        <v>BUDGAM</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="I56" s="6">
-        <v>45971</v>
+        <v>45969</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="K56" s="5"/>
-      <c r="L56" s="6"/>
+        <v>107</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="L56" s="6">
+        <v>45972</v>
+      </c>
       <c r="M56" s="5"/>
       <c r="N56" s="4"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>5</v>
+        <v>253</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="G57" s="5" t="str">
-        <f t="shared" ref="G57:G59" si="2">IF(LEFT(H57,4)="JK13","PULWAMA",IF(LEFT(H57,4)="JK01","SRINAGAR",IF(LEFT(H57,4)="JK04","BUDGAM",IF(LEFT(H57,4)="JK03","ANANTNAG",IF(LEFT(H57,4)="JK05","BARAMULLA",IF(LEFT(H57,4)="25BH","BHARAT",IF(LEFT(H57,4)="JK12","POONCH",IF(LEFT(H57,4)="JK18","KULGAM",IF(LEFT(H57,4)="JK22","SHOPIAN",IF(LEFT(H57,4)="T102","TEMP",IF(LEFT(H57,4)="","NEW","NA")))))))))))</f>
-        <v>KULGAM</v>
+        <f t="shared" si="1"/>
+        <v>SRINAGAR</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="I57" s="6">
-        <v>45971</v>
+        <v>45969</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>26</v>
+        <v>167</v>
       </c>
       <c r="K57" s="5"/>
       <c r="L57" s="6"/>
@@ -4158,32 +4310,32 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="G58" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>SHOPIAN</v>
+        <f t="shared" si="1"/>
+        <v>PULWAMA</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="I58" s="6">
-        <v>45971</v>
+        <v>45969</v>
       </c>
       <c r="J58" s="5" t="s">
         <v>167</v>
@@ -4195,35 +4347,35 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>203</v>
       </c>
       <c r="G59" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>KULGAM</v>
+        <f t="shared" si="1"/>
+        <v>SHOPIAN</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="I59" s="14">
+        <v>237</v>
+      </c>
+      <c r="I59" s="6">
         <v>45971</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>8</v>
+        <v>234</v>
       </c>
       <c r="K59" s="5"/>
       <c r="L59" s="6"/>
@@ -4232,17 +4384,36 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
-        <v>59</v>
-      </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G60" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>KULGAM</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="I60" s="6">
+        <v>45971</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="K60" s="5"/>
       <c r="L60" s="6"/>
       <c r="M60" s="5"/>
@@ -4250,17 +4421,36 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
-        <v>60</v>
-      </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G61" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>SHOPIAN</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="I61" s="6">
+        <v>45971</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="K61" s="5"/>
       <c r="L61" s="6"/>
       <c r="M61" s="5"/>
@@ -4268,17 +4458,36 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
-        <v>61</v>
-      </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
+        <v>60</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G62" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>KULGAM</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="I62" s="6">
+        <v>45971</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="K62" s="5"/>
       <c r="L62" s="6"/>
       <c r="M62" s="5"/>
@@ -4286,17 +4495,36 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
-        <v>62</v>
-      </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
+        <v>61</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G63" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>ANANTNAG</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="I63" s="6">
+        <v>45972</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="K63" s="5"/>
       <c r="L63" s="6"/>
       <c r="M63" s="5"/>
@@ -4304,17 +4532,36 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
-        <v>63</v>
-      </c>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
+        <v>62</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="G64" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="I64" s="6">
+        <v>45972</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="K64" s="5"/>
       <c r="L64" s="6"/>
       <c r="M64" s="5"/>
@@ -4324,15 +4571,34 @@
       <c r="A65" s="5">
         <v>64</v>
       </c>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="5"/>
+      <c r="B65" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G65" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>SHOPIAN</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="I65" s="6">
+        <v>45972</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>310</v>
+      </c>
       <c r="K65" s="5"/>
       <c r="L65" s="6"/>
       <c r="M65" s="5"/>
@@ -4342,15 +4608,34 @@
       <c r="A66" s="5">
         <v>65</v>
       </c>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="5"/>
+      <c r="B66" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G66" s="5" t="str">
+        <f t="shared" ref="G66:G96" si="2">IF(LEFT(H66,4)="JK13","PULWAMA",IF(LEFT(H66,4)="JK01","SRINAGAR",IF(LEFT(H66,4)="JK04","BUDGAM",IF(LEFT(H66,4)="JK03","ANANTNAG",IF(LEFT(H66,4)="JK05","BARAMULLA",IF(LEFT(H66,4)="25BH","BHARAT",IF(LEFT(H66,4)="JK12","POONCH",IF(LEFT(H66,4)="JK18","KULGAM",IF(LEFT(H66,4)="JK22","SHOPIAN",IF(LEFT(H66,4)="T102","TEMP",IF(LEFT(H66,4)="","NEW","NA")))))))))))</f>
+        <v>PULWAMA</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I66" s="6">
+        <v>45972</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>311</v>
+      </c>
       <c r="K66" s="5"/>
       <c r="L66" s="6"/>
       <c r="M66" s="5"/>
@@ -4360,15 +4645,30 @@
       <c r="A67" s="5">
         <v>66</v>
       </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
+      <c r="B67" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
+      <c r="G67" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H67" s="5"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="5"/>
+      <c r="I67" s="6">
+        <v>45972</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>310</v>
+      </c>
       <c r="K67" s="5"/>
       <c r="L67" s="6"/>
       <c r="M67" s="5"/>
@@ -4376,17 +4676,32 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
-        <v>67</v>
-      </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
+        <v>68</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
+      <c r="G68" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H68" s="5"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="5"/>
+      <c r="I68" s="6">
+        <v>45972</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="K68" s="5"/>
       <c r="L68" s="6"/>
       <c r="M68" s="5"/>
@@ -4394,16 +4709,29 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
-        <v>68</v>
-      </c>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
+        <v>69</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>196</v>
+      </c>
       <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
+      <c r="G69" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H69" s="5"/>
-      <c r="I69" s="6"/>
+      <c r="I69" s="6">
+        <v>45972</v>
+      </c>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
       <c r="L69" s="6"/>
@@ -4412,14 +4740,17 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
+      <c r="G70" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H70" s="5"/>
       <c r="I70" s="6"/>
       <c r="J70" s="5"/>
@@ -4430,14 +4761,17 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
+      <c r="G71" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H71" s="5"/>
       <c r="I71" s="6"/>
       <c r="J71" s="5"/>
@@ -4448,14 +4782,17 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
+      <c r="G72" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H72" s="5"/>
       <c r="I72" s="6"/>
       <c r="J72" s="5"/>
@@ -4466,14 +4803,17 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
+      <c r="G73" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H73" s="5"/>
       <c r="I73" s="6"/>
       <c r="J73" s="5"/>
@@ -4484,14 +4824,17 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
+      <c r="G74" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H74" s="5"/>
       <c r="I74" s="6"/>
       <c r="J74" s="5"/>
@@ -4502,14 +4845,17 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
+      <c r="G75" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H75" s="5"/>
       <c r="I75" s="6"/>
       <c r="J75" s="5"/>
@@ -4520,14 +4866,17 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
+      <c r="G76" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H76" s="5"/>
       <c r="I76" s="6"/>
       <c r="J76" s="5"/>
@@ -4538,14 +4887,17 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
+      <c r="G77" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H77" s="5"/>
       <c r="I77" s="6"/>
       <c r="J77" s="5"/>
@@ -4556,14 +4908,17 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
+      <c r="G78" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H78" s="5"/>
       <c r="I78" s="6"/>
       <c r="J78" s="5"/>
@@ -4574,14 +4929,17 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
+      <c r="G79" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H79" s="5"/>
       <c r="I79" s="6"/>
       <c r="J79" s="5"/>
@@ -4592,14 +4950,17 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
-      <c r="G80" s="5"/>
+      <c r="G80" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H80" s="5"/>
       <c r="I80" s="6"/>
       <c r="J80" s="5"/>
@@ -4610,14 +4971,17 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
       <c r="F81" s="5"/>
-      <c r="G81" s="5"/>
+      <c r="G81" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H81" s="5"/>
       <c r="I81" s="6"/>
       <c r="J81" s="5"/>
@@ -4628,14 +4992,17 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
-      <c r="G82" s="5"/>
+      <c r="G82" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H82" s="5"/>
       <c r="I82" s="6"/>
       <c r="J82" s="5"/>
@@ -4646,14 +5013,17 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
-      <c r="G83" s="5"/>
+      <c r="G83" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H83" s="5"/>
       <c r="I83" s="6"/>
       <c r="J83" s="5"/>
@@ -4664,14 +5034,17 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
-      <c r="G84" s="5"/>
+      <c r="G84" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H84" s="5"/>
       <c r="I84" s="6"/>
       <c r="J84" s="5"/>
@@ -4682,14 +5055,17 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
-      <c r="G85" s="5"/>
+      <c r="G85" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H85" s="5"/>
       <c r="I85" s="6"/>
       <c r="J85" s="5"/>
@@ -4700,14 +5076,17 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
-      <c r="G86" s="5"/>
+      <c r="G86" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H86" s="5"/>
       <c r="I86" s="6"/>
       <c r="J86" s="5"/>
@@ -4718,14 +5097,17 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
-      <c r="G87" s="5"/>
+      <c r="G87" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H87" s="5"/>
       <c r="I87" s="6"/>
       <c r="J87" s="5"/>
@@ -4736,14 +5118,17 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
-      <c r="G88" s="5"/>
+      <c r="G88" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H88" s="5"/>
       <c r="I88" s="6"/>
       <c r="J88" s="5"/>
@@ -4754,14 +5139,17 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
-      <c r="G89" s="5"/>
+      <c r="G89" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H89" s="5"/>
       <c r="I89" s="6"/>
       <c r="J89" s="5"/>
@@ -4772,14 +5160,17 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
+      <c r="G90" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H90" s="5"/>
       <c r="I90" s="6"/>
       <c r="J90" s="5"/>
@@ -4790,14 +5181,17 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
+      <c r="G91" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H91" s="5"/>
       <c r="I91" s="6"/>
       <c r="J91" s="5"/>
@@ -4808,14 +5202,17 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
-      <c r="G92" s="5"/>
+      <c r="G92" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H92" s="5"/>
       <c r="I92" s="6"/>
       <c r="J92" s="5"/>
@@ -4826,14 +5223,17 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
+      <c r="G93" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H93" s="5"/>
       <c r="I93" s="6"/>
       <c r="J93" s="5"/>
@@ -4844,14 +5244,17 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
-      <c r="G94" s="5"/>
+      <c r="G94" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H94" s="5"/>
       <c r="I94" s="6"/>
       <c r="J94" s="5"/>
@@ -4862,14 +5265,17 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
+      <c r="G95" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H95" s="5"/>
       <c r="I95" s="6"/>
       <c r="J95" s="5"/>
@@ -4880,14 +5286,17 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
+      <c r="G96" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>NEW</v>
+      </c>
       <c r="H96" s="5"/>
       <c r="I96" s="6"/>
       <c r="J96" s="5"/>
@@ -4898,14 +5307,17 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
+      <c r="G97" s="5" t="str">
+        <f t="shared" ref="G97:G104" si="3">IF(LEFT(H97,4)="JK13","PULWAMA",IF(LEFT(H97,4)="JK01","SRINAGAR",IF(LEFT(H97,4)="JK04","BUDGAM",IF(LEFT(H97,4)="JK03","ANANTNAG",IF(LEFT(H97,4)="JK05","BARAMULLA",IF(LEFT(H97,4)="25BH","BHARAT",IF(LEFT(H97,4)="JK12","POONCH",IF(LEFT(H97,4)="JK18","KULGAM",IF(LEFT(H97,4)="JK22","SHOPIAN",IF(LEFT(H97,4)="T102","TEMP",IF(LEFT(H97,4)="","NEW","NA")))))))))))</f>
+        <v>NEW</v>
+      </c>
       <c r="H97" s="5"/>
       <c r="I97" s="6"/>
       <c r="J97" s="5"/>
@@ -4916,14 +5328,17 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
+      <c r="G98" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>NEW</v>
+      </c>
       <c r="H98" s="5"/>
       <c r="I98" s="6"/>
       <c r="J98" s="5"/>
@@ -4934,14 +5349,17 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
+      <c r="G99" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>NEW</v>
+      </c>
       <c r="H99" s="5"/>
       <c r="I99" s="6"/>
       <c r="J99" s="5"/>
@@ -4952,14 +5370,17 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
       <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
+      <c r="G100" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>NEW</v>
+      </c>
       <c r="H100" s="5"/>
       <c r="I100" s="6"/>
       <c r="J100" s="5"/>
@@ -4970,14 +5391,17 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
+      <c r="G101" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>NEW</v>
+      </c>
       <c r="H101" s="5"/>
       <c r="I101" s="6"/>
       <c r="J101" s="5"/>
@@ -4988,14 +5412,17 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
-      <c r="G102" s="5"/>
+      <c r="G102" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>NEW</v>
+      </c>
       <c r="H102" s="5"/>
       <c r="I102" s="6"/>
       <c r="J102" s="5"/>
@@ -5006,14 +5433,17 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
-      <c r="G103" s="5"/>
+      <c r="G103" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>NEW</v>
+      </c>
       <c r="H103" s="5"/>
       <c r="I103" s="6"/>
       <c r="J103" s="5"/>
@@ -5024,32 +5454,17 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B104" s="5"/>
-      <c r="C104" s="5"/>
-      <c r="D104" s="5"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
-      <c r="G104" s="5"/>
-      <c r="H104" s="5"/>
-      <c r="I104" s="6"/>
-      <c r="J104" s="5"/>
-      <c r="K104" s="5"/>
-      <c r="L104" s="6"/>
-      <c r="M104" s="5"/>
-      <c r="N104" s="4"/>
+      <c r="G104" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>NEW</v>
+      </c>
+      <c r="H104"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105" s="5">
-        <v>104</v>
-      </c>
-      <c r="B105" s="5"/>
-      <c r="G105" s="5"/>
-      <c r="H105"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="M106" t="s">
+      <c r="M105" t="s">
         <v>44</v>
       </c>
     </row>
